--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9248,6 +9248,2765 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121698324</v>
+      </c>
+      <c r="B73" t="n">
+        <v>94731</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>210</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgöthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6609597</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>121698315</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgöthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6609597</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>gammal olikåldrig sumpskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>121698287</v>
+      </c>
+      <c r="B75" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgöthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>471215</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6609537</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121698319</v>
+      </c>
+      <c r="B76" t="n">
+        <v>100379</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgöthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6609608</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121698313</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgöthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>471329</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6609593</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog i branter</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>grov granskog i V-sluttning</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121697845</v>
+      </c>
+      <c r="B78" t="n">
+        <v>74714</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>308</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötyhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>471285</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6609641</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121699935</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>471202</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6609664</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121699590</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötyhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>471269</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6609685</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121699679</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötyhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>471222</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6609540</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121703309</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>471356</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6609501</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121699951</v>
+      </c>
+      <c r="B83" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>471193</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6609666</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121703311</v>
+      </c>
+      <c r="B84" t="n">
+        <v>100379</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>471356</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6609501</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>121703406</v>
+      </c>
+      <c r="B85" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>471349</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6609458</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121703368</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91661</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>471347</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6609455</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121699581</v>
+      </c>
+      <c r="B87" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötyhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>471279</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6609661</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121700010</v>
+      </c>
+      <c r="B88" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>471160</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6609566</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>121699973</v>
+      </c>
+      <c r="B89" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>471176</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6609640</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>121703365</v>
+      </c>
+      <c r="B90" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>471347</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6609455</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>121699757</v>
+      </c>
+      <c r="B91" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötyhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>471208</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6609733</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>svämzon längs bäck/surdråg</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>121703425</v>
+      </c>
+      <c r="B92" t="n">
+        <v>100379</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>471353</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6609457</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121699965</v>
+      </c>
+      <c r="B93" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>471186</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6609658</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121703399</v>
+      </c>
+      <c r="B94" t="n">
+        <v>100379</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>471349</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6609458</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121703428</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>471353</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6609457</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12007,6 +12007,244 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>121712106</v>
+      </c>
+      <c r="B96" t="n">
+        <v>94527</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6609597</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk och klibbal</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>121709723</v>
+      </c>
+      <c r="B97" t="n">
+        <v>100379</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>471351</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6609528</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>V-sluttning</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698319</v>
+        <v>121698315</v>
       </c>
       <c r="B73" t="n">
-        <v>100379</v>
+        <v>97059</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9266,30 +9266,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9298,10 +9294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R73" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9345,6 +9341,16 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>gammal olikåldrig sumpskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9361,7 +9367,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698313</v>
+        <v>121698287</v>
       </c>
       <c r="B74" t="n">
         <v>97059</v>
@@ -9405,10 +9411,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471329</v>
+        <v>471215</v>
       </c>
       <c r="R74" t="n">
-        <v>6609593</v>
+        <v>6609537</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9455,12 +9461,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9478,10 +9484,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698324</v>
+        <v>121698313</v>
       </c>
       <c r="B75" t="n">
-        <v>94731</v>
+        <v>97059</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9494,38 +9500,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>224361</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9534,10 +9528,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471319</v>
+        <v>471329</v>
       </c>
       <c r="R75" t="n">
-        <v>6609597</v>
+        <v>6609593</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9584,32 +9578,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9620,7 +9594,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9767,10 +9741,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698287</v>
+        <v>121698319</v>
       </c>
       <c r="B77" t="n">
-        <v>97059</v>
+        <v>100379</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9783,26 +9757,30 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9811,10 +9789,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471215</v>
+        <v>471316</v>
       </c>
       <c r="R77" t="n">
-        <v>6609537</v>
+        <v>6609608</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9859,16 +9837,6 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
@@ -9877,17 +9845,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698315</v>
+        <v>121698324</v>
       </c>
       <c r="B78" t="n">
-        <v>97059</v>
+        <v>94731</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9900,26 +9868,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>224361</v>
+        <v>210</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9983,7 +9963,27 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10001,7 +10001,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703311</v>
+        <v>121703399</v>
       </c>
       <c r="B79" t="n">
         <v>100379</v>
@@ -10042,17 +10042,21 @@
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471356</v>
+        <v>471349</v>
       </c>
       <c r="R79" t="n">
-        <v>6609501</v>
+        <v>6609458</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10104,7 +10108,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10122,10 +10126,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121699973</v>
+        <v>121703368</v>
       </c>
       <c r="B80" t="n">
-        <v>94527</v>
+        <v>91661</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10138,27 +10142,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2813</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10166,10 +10169,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471176</v>
+        <v>471347</v>
       </c>
       <c r="R80" t="n">
-        <v>6609640</v>
+        <v>6609455</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10210,18 +10213,17 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10232,14 +10234,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121699581</v>
+        <v>121703406</v>
       </c>
       <c r="B81" t="n">
         <v>94527</v>
@@ -10283,10 +10285,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471279</v>
+        <v>471349</v>
       </c>
       <c r="R81" t="n">
-        <v>6609661</v>
+        <v>6609458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10333,22 +10335,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10359,14 +10351,14 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703406</v>
+        <v>121703365</v>
       </c>
       <c r="B82" t="n">
         <v>94527</v>
@@ -10410,10 +10402,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471349</v>
+        <v>471347</v>
       </c>
       <c r="R82" t="n">
-        <v>6609458</v>
+        <v>6609455</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10454,7 +10446,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10483,10 +10474,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121700010</v>
+        <v>121699679</v>
       </c>
       <c r="B83" t="n">
-        <v>92004</v>
+        <v>97067</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10499,45 +10490,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471160</v>
+        <v>471222</v>
       </c>
       <c r="R83" t="n">
-        <v>6609566</v>
+        <v>6609540</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10584,12 +10572,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10600,17 +10583,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121699965</v>
+        <v>121699935</v>
       </c>
       <c r="B84" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10623,21 +10606,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10651,10 +10634,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471186</v>
+        <v>471202</v>
       </c>
       <c r="R84" t="n">
-        <v>6609658</v>
+        <v>6609664</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10706,7 +10689,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10717,17 +10700,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121703368</v>
+        <v>121703425</v>
       </c>
       <c r="B85" t="n">
-        <v>91661</v>
+        <v>100379</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10740,26 +10723,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10767,10 +10755,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471347</v>
+        <v>471353</v>
       </c>
       <c r="R85" t="n">
-        <v>6609455</v>
+        <v>6609457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10811,6 +10799,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10839,7 +10828,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121699590</v>
+        <v>121703309</v>
       </c>
       <c r="B86" t="n">
         <v>97067</v>
@@ -10883,10 +10872,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471269</v>
+        <v>471356</v>
       </c>
       <c r="R86" t="n">
-        <v>6609685</v>
+        <v>6609501</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10933,7 +10922,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10951,10 +10945,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699935</v>
+        <v>121700010</v>
       </c>
       <c r="B87" t="n">
-        <v>97067</v>
+        <v>92004</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10967,27 +10961,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10995,10 +10996,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471202</v>
+        <v>471160</v>
       </c>
       <c r="R87" t="n">
-        <v>6609664</v>
+        <v>6609566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11045,12 +11046,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11068,10 +11069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121703399</v>
+        <v>121699581</v>
       </c>
       <c r="B88" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11084,46 +11085,38 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471349</v>
+        <v>471279</v>
       </c>
       <c r="R88" t="n">
-        <v>6609458</v>
+        <v>6609661</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11170,12 +11163,22 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11193,7 +11196,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699757</v>
+        <v>121699965</v>
       </c>
       <c r="B89" t="n">
         <v>94527</v>
@@ -11237,10 +11240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471208</v>
+        <v>471186</v>
       </c>
       <c r="R89" t="n">
-        <v>6609733</v>
+        <v>6609658</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11285,9 +11288,14 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11305,7 +11313,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699951</v>
+        <v>121699973</v>
       </c>
       <c r="B90" t="n">
         <v>94527</v>
@@ -11349,10 +11357,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471193</v>
+        <v>471176</v>
       </c>
       <c r="R90" t="n">
-        <v>6609666</v>
+        <v>6609640</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11399,7 +11407,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
@@ -11539,10 +11547,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121703365</v>
+        <v>121703311</v>
       </c>
       <c r="B92" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11555,26 +11563,30 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -11583,10 +11595,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471347</v>
+        <v>471356</v>
       </c>
       <c r="R92" t="n">
-        <v>6609455</v>
+        <v>6609501</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11627,6 +11639,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11637,7 +11650,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11648,17 +11661,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121699679</v>
+        <v>121699951</v>
       </c>
       <c r="B93" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11671,42 +11684,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471222</v>
+        <v>471193</v>
       </c>
       <c r="R93" t="n">
-        <v>6609540</v>
+        <v>6609666</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11753,7 +11762,12 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11771,7 +11785,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121703309</v>
+        <v>121699590</v>
       </c>
       <c r="B94" t="n">
         <v>97067</v>
@@ -11815,10 +11829,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471356</v>
+        <v>471269</v>
       </c>
       <c r="R94" t="n">
-        <v>6609501</v>
+        <v>6609685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11865,12 +11879,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11888,10 +11897,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121703425</v>
+        <v>121699757</v>
       </c>
       <c r="B95" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11904,30 +11913,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11936,10 +11941,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471353</v>
+        <v>471208</v>
       </c>
       <c r="R95" t="n">
-        <v>6609457</v>
+        <v>6609733</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11984,14 +11989,9 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698315</v>
+        <v>121698319</v>
       </c>
       <c r="B73" t="n">
-        <v>97059</v>
+        <v>100379</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9266,26 +9266,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9294,10 +9298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471319</v>
+        <v>471316</v>
       </c>
       <c r="R73" t="n">
-        <v>6609597</v>
+        <v>6609608</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9341,16 +9345,6 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>gammal olikåldrig sumpskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9367,7 +9361,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698287</v>
+        <v>121698315</v>
       </c>
       <c r="B74" t="n">
         <v>97059</v>
@@ -9411,10 +9405,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471215</v>
+        <v>471319</v>
       </c>
       <c r="R74" t="n">
-        <v>6609537</v>
+        <v>6609597</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9461,12 +9455,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9477,14 +9471,14 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698313</v>
+        <v>121698287</v>
       </c>
       <c r="B75" t="n">
         <v>97059</v>
@@ -9528,10 +9522,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471329</v>
+        <v>471215</v>
       </c>
       <c r="R75" t="n">
-        <v>6609593</v>
+        <v>6609537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9578,12 +9572,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9741,10 +9735,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698319</v>
+        <v>121698324</v>
       </c>
       <c r="B77" t="n">
-        <v>100379</v>
+        <v>94731</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9757,28 +9751,36 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -9789,10 +9791,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R77" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9836,6 +9838,36 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9852,10 +9884,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698324</v>
+        <v>121698313</v>
       </c>
       <c r="B78" t="n">
-        <v>94731</v>
+        <v>97059</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9868,38 +9900,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>210</v>
+        <v>224361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9908,10 +9928,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471319</v>
+        <v>471329</v>
       </c>
       <c r="R78" t="n">
-        <v>6609597</v>
+        <v>6609593</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9958,32 +9978,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703399</v>
+        <v>121699951</v>
       </c>
       <c r="B79" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10017,46 +10017,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471349</v>
+        <v>471193</v>
       </c>
       <c r="R79" t="n">
-        <v>6609458</v>
+        <v>6609666</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10108,7 +10100,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10119,17 +10111,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121703368</v>
+        <v>121700010</v>
       </c>
       <c r="B80" t="n">
-        <v>91661</v>
+        <v>92004</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10142,25 +10134,33 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -10169,10 +10169,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471347</v>
+        <v>471160</v>
       </c>
       <c r="R80" t="n">
-        <v>6609455</v>
+        <v>6609566</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10213,17 +10213,18 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10241,10 +10242,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703406</v>
+        <v>121699935</v>
       </c>
       <c r="B81" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10257,21 +10258,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10285,10 +10286,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471349</v>
+        <v>471202</v>
       </c>
       <c r="R81" t="n">
-        <v>6609458</v>
+        <v>6609664</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10340,7 +10341,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10351,17 +10352,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703365</v>
+        <v>121703399</v>
       </c>
       <c r="B82" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10374,38 +10375,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471347</v>
+        <v>471349</v>
       </c>
       <c r="R82" t="n">
-        <v>6609455</v>
+        <v>6609458</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10446,6 +10455,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10467,17 +10477,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121699679</v>
+        <v>121703428</v>
       </c>
       <c r="B83" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10490,42 +10500,38 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471222</v>
+        <v>471353</v>
       </c>
       <c r="R83" t="n">
-        <v>6609540</v>
+        <v>6609457</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10572,7 +10578,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10590,10 +10601,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121699935</v>
+        <v>121703365</v>
       </c>
       <c r="B84" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10606,21 +10617,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10634,10 +10645,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471202</v>
+        <v>471347</v>
       </c>
       <c r="R84" t="n">
-        <v>6609664</v>
+        <v>6609455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10678,7 +10689,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10689,7 +10699,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10700,17 +10710,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121703425</v>
+        <v>121699757</v>
       </c>
       <c r="B85" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10723,30 +10733,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -10755,10 +10761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471353</v>
+        <v>471208</v>
       </c>
       <c r="R85" t="n">
-        <v>6609457</v>
+        <v>6609733</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10803,14 +10809,9 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10821,17 +10822,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121703309</v>
+        <v>121703311</v>
       </c>
       <c r="B86" t="n">
-        <v>97067</v>
+        <v>100379</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10844,26 +10845,30 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -10945,10 +10950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121700010</v>
+        <v>121699679</v>
       </c>
       <c r="B87" t="n">
-        <v>92004</v>
+        <v>97067</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10961,45 +10966,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471160</v>
+        <v>471222</v>
       </c>
       <c r="R87" t="n">
-        <v>6609566</v>
+        <v>6609540</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11046,12 +11048,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11062,7 +11059,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11196,7 +11193,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699965</v>
+        <v>121699973</v>
       </c>
       <c r="B89" t="n">
         <v>94527</v>
@@ -11240,10 +11237,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471186</v>
+        <v>471176</v>
       </c>
       <c r="R89" t="n">
-        <v>6609658</v>
+        <v>6609640</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11290,7 +11287,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
@@ -11313,7 +11310,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699973</v>
+        <v>121699965</v>
       </c>
       <c r="B90" t="n">
         <v>94527</v>
@@ -11357,10 +11354,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471176</v>
+        <v>471186</v>
       </c>
       <c r="R90" t="n">
-        <v>6609640</v>
+        <v>6609658</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11407,7 +11404,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
@@ -11430,10 +11427,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121703428</v>
+        <v>121703368</v>
       </c>
       <c r="B91" t="n">
-        <v>94527</v>
+        <v>91661</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11446,27 +11443,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2813</v>
+        <v>4769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11474,10 +11470,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471353</v>
+        <v>471347</v>
       </c>
       <c r="R91" t="n">
-        <v>6609457</v>
+        <v>6609455</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11518,7 +11514,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11540,17 +11535,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121703311</v>
+        <v>121703406</v>
       </c>
       <c r="B92" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11563,30 +11558,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -11595,10 +11586,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471356</v>
+        <v>471349</v>
       </c>
       <c r="R92" t="n">
-        <v>6609501</v>
+        <v>6609458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11650,7 +11641,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11661,17 +11652,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121699951</v>
+        <v>121703309</v>
       </c>
       <c r="B93" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11684,21 +11675,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11712,10 +11703,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471193</v>
+        <v>471356</v>
       </c>
       <c r="R93" t="n">
-        <v>6609666</v>
+        <v>6609501</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11767,7 +11758,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11778,17 +11769,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121699590</v>
+        <v>121703425</v>
       </c>
       <c r="B94" t="n">
-        <v>97067</v>
+        <v>100379</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11801,26 +11792,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -11829,10 +11824,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471269</v>
+        <v>471353</v>
       </c>
       <c r="R94" t="n">
-        <v>6609685</v>
+        <v>6609457</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11879,7 +11874,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121699757</v>
+        <v>121699590</v>
       </c>
       <c r="B95" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11913,21 +11913,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471208</v>
+        <v>471269</v>
       </c>
       <c r="R95" t="n">
-        <v>6609733</v>
+        <v>6609685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11989,9 +11989,9 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>svämzon längs bäck/surdråg</t>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12002,17 +12002,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121709723</v>
+        <v>121712106</v>
       </c>
       <c r="B96" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12025,30 +12025,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12057,10 +12053,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471351</v>
+        <v>471319</v>
       </c>
       <c r="R96" t="n">
-        <v>6609528</v>
+        <v>6609597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12107,12 +12103,12 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>V-sluttning</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12123,17 +12119,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121712106</v>
+        <v>121709723</v>
       </c>
       <c r="B97" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12146,26 +12142,30 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471319</v>
+        <v>471351</v>
       </c>
       <c r="R97" t="n">
-        <v>6609597</v>
+        <v>6609528</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk och klibbal</t>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -10950,10 +10950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699679</v>
+        <v>121699581</v>
       </c>
       <c r="B87" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10966,42 +10966,38 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471222</v>
+        <v>471279</v>
       </c>
       <c r="R87" t="n">
-        <v>6609540</v>
+        <v>6609661</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11048,7 +11044,22 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11059,14 +11070,14 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121699581</v>
+        <v>121699973</v>
       </c>
       <c r="B88" t="n">
         <v>94527</v>
@@ -11110,10 +11121,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471279</v>
+        <v>471176</v>
       </c>
       <c r="R88" t="n">
-        <v>6609661</v>
+        <v>6609640</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11160,22 +11171,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11186,17 +11187,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699973</v>
+        <v>121699679</v>
       </c>
       <c r="B89" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11209,38 +11210,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471176</v>
+        <v>471222</v>
       </c>
       <c r="R89" t="n">
-        <v>6609640</v>
+        <v>6609540</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11287,12 +11292,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699965</v>
+        <v>121703368</v>
       </c>
       <c r="B90" t="n">
-        <v>94527</v>
+        <v>91661</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11326,27 +11326,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2813</v>
+        <v>4769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11354,10 +11353,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471186</v>
+        <v>471347</v>
       </c>
       <c r="R90" t="n">
-        <v>6609658</v>
+        <v>6609455</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11398,7 +11397,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11409,7 +11407,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11420,17 +11418,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121703368</v>
+        <v>121699965</v>
       </c>
       <c r="B91" t="n">
-        <v>91661</v>
+        <v>94527</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11443,26 +11441,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11470,10 +11469,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471347</v>
+        <v>471186</v>
       </c>
       <c r="R91" t="n">
-        <v>6609455</v>
+        <v>6609658</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11514,6 +11513,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698319</v>
+        <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>100379</v>
+        <v>97059</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9266,30 +9266,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9298,10 +9294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471316</v>
+        <v>471215</v>
       </c>
       <c r="R73" t="n">
-        <v>6609608</v>
+        <v>6609537</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9346,6 +9342,16 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
@@ -9354,14 +9360,14 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698315</v>
+        <v>121698313</v>
       </c>
       <c r="B74" t="n">
         <v>97059</v>
@@ -9405,10 +9411,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471319</v>
+        <v>471329</v>
       </c>
       <c r="R74" t="n">
-        <v>6609597</v>
+        <v>6609593</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9455,12 +9461,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9471,17 +9477,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698287</v>
+        <v>121698319</v>
       </c>
       <c r="B75" t="n">
-        <v>97059</v>
+        <v>100379</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9494,26 +9500,30 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9522,10 +9532,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471215</v>
+        <v>471316</v>
       </c>
       <c r="R75" t="n">
-        <v>6609537</v>
+        <v>6609608</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9570,16 +9580,6 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
-        </is>
-      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
@@ -9588,17 +9588,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121697845</v>
+        <v>121698324</v>
       </c>
       <c r="B76" t="n">
-        <v>74714</v>
+        <v>94731</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9607,34 +9607,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9642,10 +9651,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471285</v>
+        <v>471319</v>
       </c>
       <c r="R76" t="n">
-        <v>6609641</v>
+        <v>6609597</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9712,12 +9721,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9735,10 +9744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698324</v>
+        <v>121697845</v>
       </c>
       <c r="B77" t="n">
-        <v>94731</v>
+        <v>74714</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9747,43 +9756,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471319</v>
+        <v>471285</v>
       </c>
       <c r="R77" t="n">
-        <v>6609597</v>
+        <v>6609641</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9861,12 +9861,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698313</v>
+        <v>121698315</v>
       </c>
       <c r="B78" t="n">
         <v>97059</v>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471329</v>
+        <v>471319</v>
       </c>
       <c r="R78" t="n">
-        <v>6609593</v>
+        <v>6609597</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121699951</v>
+        <v>121703425</v>
       </c>
       <c r="B79" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10017,26 +10017,30 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -10045,10 +10049,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471193</v>
+        <v>471353</v>
       </c>
       <c r="R79" t="n">
-        <v>6609666</v>
+        <v>6609457</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10100,7 +10104,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10111,17 +10115,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121700010</v>
+        <v>121703309</v>
       </c>
       <c r="B80" t="n">
-        <v>92004</v>
+        <v>97067</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10134,34 +10138,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10169,10 +10166,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471160</v>
+        <v>471356</v>
       </c>
       <c r="R80" t="n">
-        <v>6609566</v>
+        <v>6609501</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10219,12 +10216,12 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10242,10 +10239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121699935</v>
+        <v>121703428</v>
       </c>
       <c r="B81" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10258,21 +10255,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10286,10 +10283,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471202</v>
+        <v>471353</v>
       </c>
       <c r="R81" t="n">
-        <v>6609664</v>
+        <v>6609457</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10341,7 +10338,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10352,17 +10349,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703399</v>
+        <v>121699935</v>
       </c>
       <c r="B82" t="n">
-        <v>100379</v>
+        <v>97067</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10375,46 +10372,38 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471349</v>
+        <v>471202</v>
       </c>
       <c r="R82" t="n">
-        <v>6609458</v>
+        <v>6609664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10466,7 +10455,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10484,10 +10473,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121703428</v>
+        <v>121703399</v>
       </c>
       <c r="B83" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10500,38 +10489,46 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471353</v>
+        <v>471349</v>
       </c>
       <c r="R83" t="n">
-        <v>6609457</v>
+        <v>6609458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10594,14 +10591,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121703365</v>
+        <v>121699951</v>
       </c>
       <c r="B84" t="n">
         <v>94527</v>
@@ -10645,10 +10642,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471347</v>
+        <v>471193</v>
       </c>
       <c r="R84" t="n">
-        <v>6609455</v>
+        <v>6609666</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10689,6 +10686,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10699,7 +10697,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10717,7 +10715,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121699757</v>
+        <v>121699965</v>
       </c>
       <c r="B85" t="n">
         <v>94527</v>
@@ -10761,10 +10759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471208</v>
+        <v>471186</v>
       </c>
       <c r="R85" t="n">
-        <v>6609733</v>
+        <v>6609658</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10809,9 +10807,14 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10829,10 +10832,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121703311</v>
+        <v>121703406</v>
       </c>
       <c r="B86" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10845,30 +10848,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -10877,10 +10876,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471356</v>
+        <v>471349</v>
       </c>
       <c r="R86" t="n">
-        <v>6609501</v>
+        <v>6609458</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10932,7 +10931,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10943,17 +10942,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699581</v>
+        <v>121703311</v>
       </c>
       <c r="B87" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10966,26 +10965,30 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -10994,10 +10997,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471279</v>
+        <v>471356</v>
       </c>
       <c r="R87" t="n">
-        <v>6609661</v>
+        <v>6609501</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11044,22 +11047,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11077,10 +11070,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121699973</v>
+        <v>121699679</v>
       </c>
       <c r="B88" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11093,38 +11086,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471176</v>
+        <v>471222</v>
       </c>
       <c r="R88" t="n">
-        <v>6609640</v>
+        <v>6609540</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11171,12 +11168,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11194,10 +11186,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699679</v>
+        <v>121699581</v>
       </c>
       <c r="B89" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11210,42 +11202,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471222</v>
+        <v>471279</v>
       </c>
       <c r="R89" t="n">
-        <v>6609540</v>
+        <v>6609661</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11292,7 +11280,22 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11303,17 +11306,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121703368</v>
+        <v>121699757</v>
       </c>
       <c r="B90" t="n">
-        <v>91661</v>
+        <v>94527</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11326,26 +11329,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11353,10 +11357,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471347</v>
+        <v>471208</v>
       </c>
       <c r="R90" t="n">
-        <v>6609455</v>
+        <v>6609733</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11397,17 +11401,13 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11418,14 +11418,14 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699965</v>
+        <v>121703365</v>
       </c>
       <c r="B91" t="n">
         <v>94527</v>
@@ -11469,10 +11469,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471186</v>
+        <v>471347</v>
       </c>
       <c r="R91" t="n">
-        <v>6609658</v>
+        <v>6609455</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11513,7 +11513,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11524,7 +11523,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11542,10 +11541,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121703406</v>
+        <v>121699590</v>
       </c>
       <c r="B92" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11558,21 +11557,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11586,10 +11585,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471349</v>
+        <v>471269</v>
       </c>
       <c r="R92" t="n">
-        <v>6609458</v>
+        <v>6609685</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11636,12 +11635,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11652,17 +11646,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121703309</v>
+        <v>121703368</v>
       </c>
       <c r="B93" t="n">
-        <v>97067</v>
+        <v>91661</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11675,27 +11669,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11703,10 +11696,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471356</v>
+        <v>471347</v>
       </c>
       <c r="R93" t="n">
-        <v>6609501</v>
+        <v>6609455</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11747,7 +11740,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11758,7 +11750,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11776,10 +11768,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121703425</v>
+        <v>121699973</v>
       </c>
       <c r="B94" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11792,30 +11784,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -11824,10 +11812,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471353</v>
+        <v>471176</v>
       </c>
       <c r="R94" t="n">
-        <v>6609457</v>
+        <v>6609640</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11874,12 +11862,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11890,17 +11878,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121699590</v>
+        <v>121700010</v>
       </c>
       <c r="B95" t="n">
-        <v>97067</v>
+        <v>92004</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11913,27 +11901,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11941,10 +11936,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471269</v>
+        <v>471160</v>
       </c>
       <c r="R95" t="n">
-        <v>6609685</v>
+        <v>6609566</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11991,7 +11986,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12009,10 +12009,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121712106</v>
+        <v>121709723</v>
       </c>
       <c r="B96" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12025,26 +12025,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12053,10 +12057,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471319</v>
+        <v>471351</v>
       </c>
       <c r="R96" t="n">
-        <v>6609597</v>
+        <v>6609528</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12103,12 +12107,12 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk och klibbal</t>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12119,17 +12123,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121709723</v>
+        <v>121712106</v>
       </c>
       <c r="B97" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12142,30 +12146,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471351</v>
+        <v>471319</v>
       </c>
       <c r="R97" t="n">
-        <v>6609528</v>
+        <v>6609597</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>V-sluttning</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,7 +9250,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698287</v>
+        <v>121698313</v>
       </c>
       <c r="B73" t="n">
         <v>97059</v>
@@ -9294,10 +9294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471215</v>
+        <v>471329</v>
       </c>
       <c r="R73" t="n">
-        <v>6609537</v>
+        <v>6609593</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9367,10 +9367,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698313</v>
+        <v>121697845</v>
       </c>
       <c r="B74" t="n">
-        <v>97059</v>
+        <v>74714</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9379,31 +9379,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9411,10 +9414,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471329</v>
+        <v>471285</v>
       </c>
       <c r="R74" t="n">
-        <v>6609593</v>
+        <v>6609641</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9461,12 +9464,32 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9477,17 +9500,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698319</v>
+        <v>121698324</v>
       </c>
       <c r="B75" t="n">
-        <v>100379</v>
+        <v>94731</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9500,28 +9523,36 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -9532,10 +9563,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R75" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9579,6 +9610,36 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9595,10 +9656,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121698324</v>
+        <v>121698319</v>
       </c>
       <c r="B76" t="n">
-        <v>94731</v>
+        <v>100379</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9611,36 +9672,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -9651,10 +9704,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471319</v>
+        <v>471316</v>
       </c>
       <c r="R76" t="n">
-        <v>6609597</v>
+        <v>6609608</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9698,36 +9751,6 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9744,10 +9767,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121697845</v>
+        <v>121698315</v>
       </c>
       <c r="B77" t="n">
-        <v>74714</v>
+        <v>97059</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9756,34 +9779,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>224361</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9791,10 +9811,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471285</v>
+        <v>471319</v>
       </c>
       <c r="R77" t="n">
-        <v>6609641</v>
+        <v>6609597</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9846,27 +9866,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698315</v>
+        <v>121698287</v>
       </c>
       <c r="B78" t="n">
         <v>97059</v>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471319</v>
+        <v>471215</v>
       </c>
       <c r="R78" t="n">
-        <v>6609597</v>
+        <v>6609537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9994,14 +9994,14 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703425</v>
+        <v>121703399</v>
       </c>
       <c r="B79" t="n">
         <v>100379</v>
@@ -10042,17 +10042,21 @@
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471353</v>
+        <v>471349</v>
       </c>
       <c r="R79" t="n">
-        <v>6609457</v>
+        <v>6609458</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10122,10 +10126,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121703309</v>
+        <v>121699973</v>
       </c>
       <c r="B80" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10138,21 +10142,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10166,10 +10170,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471356</v>
+        <v>471176</v>
       </c>
       <c r="R80" t="n">
-        <v>6609501</v>
+        <v>6609640</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10216,12 +10220,12 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10232,17 +10236,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703428</v>
+        <v>121699935</v>
       </c>
       <c r="B81" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10255,21 +10259,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10283,10 +10287,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471353</v>
+        <v>471202</v>
       </c>
       <c r="R81" t="n">
-        <v>6609457</v>
+        <v>6609664</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10338,7 +10342,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10349,17 +10353,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121699935</v>
+        <v>121703428</v>
       </c>
       <c r="B82" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10372,21 +10376,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10400,10 +10404,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471202</v>
+        <v>471353</v>
       </c>
       <c r="R82" t="n">
-        <v>6609664</v>
+        <v>6609457</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10455,7 +10459,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10466,17 +10470,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121703399</v>
+        <v>121703368</v>
       </c>
       <c r="B83" t="n">
-        <v>100379</v>
+        <v>91661</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10489,46 +10493,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471349</v>
+        <v>471347</v>
       </c>
       <c r="R83" t="n">
-        <v>6609458</v>
+        <v>6609455</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10569,7 +10564,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10598,7 +10592,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121699951</v>
+        <v>121703365</v>
       </c>
       <c r="B84" t="n">
         <v>94527</v>
@@ -10642,10 +10636,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471193</v>
+        <v>471347</v>
       </c>
       <c r="R84" t="n">
-        <v>6609666</v>
+        <v>6609455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10686,7 +10680,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10697,7 +10690,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10715,10 +10708,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121699965</v>
+        <v>121703311</v>
       </c>
       <c r="B85" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10731,26 +10724,30 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -10759,10 +10756,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471186</v>
+        <v>471356</v>
       </c>
       <c r="R85" t="n">
-        <v>6609658</v>
+        <v>6609501</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10814,7 +10811,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10825,17 +10822,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121703406</v>
+        <v>121703309</v>
       </c>
       <c r="B86" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10848,21 +10845,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10876,10 +10873,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471349</v>
+        <v>471356</v>
       </c>
       <c r="R86" t="n">
-        <v>6609458</v>
+        <v>6609501</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10931,7 +10928,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10942,17 +10939,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121703311</v>
+        <v>121699581</v>
       </c>
       <c r="B87" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10965,30 +10962,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -10997,10 +10990,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471356</v>
+        <v>471279</v>
       </c>
       <c r="R87" t="n">
-        <v>6609501</v>
+        <v>6609661</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11047,12 +11040,22 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11070,7 +11073,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121699679</v>
+        <v>121699590</v>
       </c>
       <c r="B88" t="n">
         <v>97067</v>
@@ -11107,21 +11110,17 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471222</v>
+        <v>471269</v>
       </c>
       <c r="R88" t="n">
-        <v>6609540</v>
+        <v>6609685</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11168,7 +11167,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11179,14 +11178,14 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699581</v>
+        <v>121699757</v>
       </c>
       <c r="B89" t="n">
         <v>94527</v>
@@ -11230,10 +11229,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471279</v>
+        <v>471208</v>
       </c>
       <c r="R89" t="n">
-        <v>6609661</v>
+        <v>6609733</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11278,24 +11277,9 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11306,17 +11290,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699757</v>
+        <v>121703425</v>
       </c>
       <c r="B90" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11329,26 +11313,30 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -11357,10 +11345,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471208</v>
+        <v>471353</v>
       </c>
       <c r="R90" t="n">
-        <v>6609733</v>
+        <v>6609457</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11405,9 +11393,14 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11418,14 +11411,14 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121703365</v>
+        <v>121699951</v>
       </c>
       <c r="B91" t="n">
         <v>94527</v>
@@ -11469,10 +11462,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471347</v>
+        <v>471193</v>
       </c>
       <c r="R91" t="n">
-        <v>6609455</v>
+        <v>6609666</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11513,6 +11506,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11523,7 +11517,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11541,10 +11535,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121699590</v>
+        <v>121700010</v>
       </c>
       <c r="B92" t="n">
-        <v>97067</v>
+        <v>92004</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11557,27 +11551,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11585,10 +11586,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471269</v>
+        <v>471160</v>
       </c>
       <c r="R92" t="n">
-        <v>6609685</v>
+        <v>6609566</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11635,7 +11636,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11653,10 +11659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121703368</v>
+        <v>121699965</v>
       </c>
       <c r="B93" t="n">
-        <v>91661</v>
+        <v>94527</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11669,26 +11675,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11696,10 +11703,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471347</v>
+        <v>471186</v>
       </c>
       <c r="R93" t="n">
-        <v>6609455</v>
+        <v>6609658</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11740,6 +11747,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11750,7 +11758,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11761,17 +11769,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121699973</v>
+        <v>121699679</v>
       </c>
       <c r="B94" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11784,38 +11792,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471176</v>
+        <v>471222</v>
       </c>
       <c r="R94" t="n">
-        <v>6609640</v>
+        <v>6609540</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11862,12 +11874,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11885,10 +11892,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121700010</v>
+        <v>121703406</v>
       </c>
       <c r="B95" t="n">
-        <v>92004</v>
+        <v>94527</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11901,34 +11908,27 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>2813</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471160</v>
+        <v>471349</v>
       </c>
       <c r="R95" t="n">
-        <v>6609566</v>
+        <v>6609458</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11986,12 +11986,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12002,17 +12002,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121709723</v>
+        <v>121712106</v>
       </c>
       <c r="B96" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12025,30 +12025,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12057,10 +12053,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471351</v>
+        <v>471319</v>
       </c>
       <c r="R96" t="n">
-        <v>6609528</v>
+        <v>6609597</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12107,12 +12103,12 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>V-sluttning</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12123,17 +12119,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121712106</v>
+        <v>121709723</v>
       </c>
       <c r="B97" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12146,26 +12142,30 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471319</v>
+        <v>471351</v>
       </c>
       <c r="R97" t="n">
-        <v>6609597</v>
+        <v>6609528</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk och klibbal</t>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698313</v>
+        <v>121697845</v>
       </c>
       <c r="B73" t="n">
-        <v>97059</v>
+        <v>74714</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9262,31 +9262,34 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9294,10 +9297,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471329</v>
+        <v>471285</v>
       </c>
       <c r="R73" t="n">
-        <v>6609593</v>
+        <v>6609641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9344,12 +9347,32 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9360,17 +9383,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121697845</v>
+        <v>121698319</v>
       </c>
       <c r="B74" t="n">
-        <v>74714</v>
+        <v>100379</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9379,34 +9402,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9414,10 +9438,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471285</v>
+        <v>471316</v>
       </c>
       <c r="R74" t="n">
-        <v>6609641</v>
+        <v>6609608</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9461,36 +9485,6 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9656,10 +9650,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121698319</v>
+        <v>121698315</v>
       </c>
       <c r="B76" t="n">
-        <v>100379</v>
+        <v>97059</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9672,30 +9666,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -9704,10 +9694,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R76" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9751,6 +9741,16 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>gammal olikåldrig sumpskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9767,7 +9767,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698315</v>
+        <v>121698287</v>
       </c>
       <c r="B77" t="n">
         <v>97059</v>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471319</v>
+        <v>471215</v>
       </c>
       <c r="R77" t="n">
-        <v>6609597</v>
+        <v>6609537</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9861,12 +9861,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9877,14 +9877,14 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698287</v>
+        <v>121698313</v>
       </c>
       <c r="B78" t="n">
         <v>97059</v>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471215</v>
+        <v>471329</v>
       </c>
       <c r="R78" t="n">
-        <v>6609537</v>
+        <v>6609593</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703399</v>
+        <v>121703365</v>
       </c>
       <c r="B79" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10017,46 +10017,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471349</v>
+        <v>471347</v>
       </c>
       <c r="R79" t="n">
-        <v>6609458</v>
+        <v>6609455</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10097,7 +10089,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -10119,17 +10110,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121699973</v>
+        <v>121699935</v>
       </c>
       <c r="B80" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10142,21 +10133,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10170,10 +10161,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471176</v>
+        <v>471202</v>
       </c>
       <c r="R80" t="n">
-        <v>6609640</v>
+        <v>6609664</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10220,12 +10211,12 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10236,17 +10227,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121699935</v>
+        <v>121703368</v>
       </c>
       <c r="B81" t="n">
-        <v>97067</v>
+        <v>91661</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10259,27 +10250,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10287,10 +10277,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471202</v>
+        <v>471347</v>
       </c>
       <c r="R81" t="n">
-        <v>6609664</v>
+        <v>6609455</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10331,7 +10321,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10342,7 +10331,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10360,10 +10349,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703428</v>
+        <v>121703309</v>
       </c>
       <c r="B82" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10376,21 +10365,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10404,10 +10393,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471353</v>
+        <v>471356</v>
       </c>
       <c r="R82" t="n">
-        <v>6609457</v>
+        <v>6609501</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10459,7 +10448,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10470,17 +10459,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121703368</v>
+        <v>121699951</v>
       </c>
       <c r="B83" t="n">
-        <v>91661</v>
+        <v>94527</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10493,26 +10482,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10520,10 +10510,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471347</v>
+        <v>471193</v>
       </c>
       <c r="R83" t="n">
-        <v>6609455</v>
+        <v>6609666</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10564,6 +10554,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10574,7 +10565,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10585,17 +10576,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121703365</v>
+        <v>121699679</v>
       </c>
       <c r="B84" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10608,38 +10599,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471347</v>
+        <v>471222</v>
       </c>
       <c r="R84" t="n">
-        <v>6609455</v>
+        <v>6609540</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10680,17 +10675,13 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10708,10 +10699,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121703311</v>
+        <v>121700010</v>
       </c>
       <c r="B85" t="n">
-        <v>100379</v>
+        <v>92004</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10724,31 +10715,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10756,10 +10750,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471356</v>
+        <v>471160</v>
       </c>
       <c r="R85" t="n">
-        <v>6609501</v>
+        <v>6609566</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10806,12 +10800,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10829,7 +10823,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121703309</v>
+        <v>121699590</v>
       </c>
       <c r="B86" t="n">
         <v>97067</v>
@@ -10873,10 +10867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471356</v>
+        <v>471269</v>
       </c>
       <c r="R86" t="n">
-        <v>6609501</v>
+        <v>6609685</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10923,12 +10917,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11073,10 +11062,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121699590</v>
+        <v>121703428</v>
       </c>
       <c r="B88" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11089,21 +11078,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11117,10 +11106,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471269</v>
+        <v>471353</v>
       </c>
       <c r="R88" t="n">
-        <v>6609685</v>
+        <v>6609457</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11167,7 +11156,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11178,17 +11172,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699757</v>
+        <v>121703399</v>
       </c>
       <c r="B89" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11201,38 +11195,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471208</v>
+        <v>471349</v>
       </c>
       <c r="R89" t="n">
-        <v>6609733</v>
+        <v>6609458</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11277,9 +11279,14 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11290,14 +11297,14 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121703425</v>
+        <v>121703311</v>
       </c>
       <c r="B90" t="n">
         <v>100379</v>
@@ -11345,10 +11352,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471353</v>
+        <v>471356</v>
       </c>
       <c r="R90" t="n">
-        <v>6609457</v>
+        <v>6609501</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11400,7 +11407,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11418,7 +11425,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699951</v>
+        <v>121699757</v>
       </c>
       <c r="B91" t="n">
         <v>94527</v>
@@ -11462,10 +11469,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471193</v>
+        <v>471208</v>
       </c>
       <c r="R91" t="n">
-        <v>6609666</v>
+        <v>6609733</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11510,14 +11517,9 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11535,10 +11537,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121700010</v>
+        <v>121699965</v>
       </c>
       <c r="B92" t="n">
-        <v>92004</v>
+        <v>94527</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11551,34 +11553,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>2813</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11586,10 +11581,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471160</v>
+        <v>471186</v>
       </c>
       <c r="R92" t="n">
-        <v>6609566</v>
+        <v>6609658</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11636,12 +11631,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11652,14 +11647,14 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121699965</v>
+        <v>121703406</v>
       </c>
       <c r="B93" t="n">
         <v>94527</v>
@@ -11703,10 +11698,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471186</v>
+        <v>471349</v>
       </c>
       <c r="R93" t="n">
-        <v>6609658</v>
+        <v>6609458</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11758,7 +11753,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11776,10 +11771,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121699679</v>
+        <v>121699973</v>
       </c>
       <c r="B94" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11792,42 +11787,38 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471222</v>
+        <v>471176</v>
       </c>
       <c r="R94" t="n">
-        <v>6609540</v>
+        <v>6609640</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11874,7 +11865,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11892,10 +11888,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121703406</v>
+        <v>121703425</v>
       </c>
       <c r="B95" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11908,26 +11904,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471349</v>
+        <v>471353</v>
       </c>
       <c r="R95" t="n">
-        <v>6609458</v>
+        <v>6609457</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12002,17 +12002,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121712106</v>
+        <v>121709723</v>
       </c>
       <c r="B96" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12025,26 +12025,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12053,10 +12057,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471319</v>
+        <v>471351</v>
       </c>
       <c r="R96" t="n">
-        <v>6609597</v>
+        <v>6609528</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12103,12 +12107,12 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk och klibbal</t>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12119,17 +12123,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121709723</v>
+        <v>121712106</v>
       </c>
       <c r="B97" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12142,30 +12146,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471351</v>
+        <v>471319</v>
       </c>
       <c r="R97" t="n">
-        <v>6609528</v>
+        <v>6609597</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>V-sluttning</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -10823,10 +10823,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121699590</v>
+        <v>121699581</v>
       </c>
       <c r="B86" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10839,21 +10839,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471269</v>
+        <v>471279</v>
       </c>
       <c r="R86" t="n">
-        <v>6609685</v>
+        <v>6609661</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10918,6 +10918,21 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10935,10 +10950,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699581</v>
+        <v>121699590</v>
       </c>
       <c r="B87" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10951,21 +10966,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10979,10 +10994,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471279</v>
+        <v>471269</v>
       </c>
       <c r="R87" t="n">
-        <v>6609661</v>
+        <v>6609685</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11030,21 +11045,6 @@
       <c r="AH87" t="inlineStr">
         <is>
           <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121697845</v>
+        <v>121698315</v>
       </c>
       <c r="B73" t="n">
-        <v>74714</v>
+        <v>97059</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9262,34 +9262,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>308</v>
+        <v>224361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9297,10 +9294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471285</v>
+        <v>471319</v>
       </c>
       <c r="R73" t="n">
-        <v>6609641</v>
+        <v>6609597</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9352,27 +9349,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9390,10 +9367,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698319</v>
+        <v>121698313</v>
       </c>
       <c r="B74" t="n">
-        <v>100379</v>
+        <v>97059</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9406,30 +9383,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9438,10 +9411,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471316</v>
+        <v>471329</v>
       </c>
       <c r="R74" t="n">
-        <v>6609608</v>
+        <v>6609593</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9486,6 +9459,16 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog i branter</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>grov granskog i V-sluttning</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
@@ -9494,17 +9477,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698324</v>
+        <v>121698319</v>
       </c>
       <c r="B75" t="n">
-        <v>94731</v>
+        <v>100379</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9517,36 +9500,28 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -9557,10 +9532,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471319</v>
+        <v>471316</v>
       </c>
       <c r="R75" t="n">
-        <v>6609597</v>
+        <v>6609608</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9604,36 +9579,6 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9650,10 +9595,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121698315</v>
+        <v>121697845</v>
       </c>
       <c r="B76" t="n">
-        <v>97059</v>
+        <v>74714</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9662,31 +9607,34 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9694,10 +9642,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471319</v>
+        <v>471285</v>
       </c>
       <c r="R76" t="n">
-        <v>6609597</v>
+        <v>6609641</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9749,7 +9697,27 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9767,10 +9735,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698287</v>
+        <v>121698324</v>
       </c>
       <c r="B77" t="n">
-        <v>97059</v>
+        <v>94731</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9783,26 +9751,38 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224361</v>
+        <v>210</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9811,10 +9791,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471215</v>
+        <v>471319</v>
       </c>
       <c r="R77" t="n">
-        <v>6609537</v>
+        <v>6609597</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9861,12 +9841,32 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9877,14 +9877,14 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698313</v>
+        <v>121698287</v>
       </c>
       <c r="B78" t="n">
         <v>97059</v>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471329</v>
+        <v>471215</v>
       </c>
       <c r="R78" t="n">
-        <v>6609593</v>
+        <v>6609537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703365</v>
+        <v>121703309</v>
       </c>
       <c r="B79" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10017,21 +10017,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471347</v>
+        <v>471356</v>
       </c>
       <c r="R79" t="n">
-        <v>6609455</v>
+        <v>6609501</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10089,6 +10089,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -10099,7 +10100,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10110,14 +10111,14 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121699935</v>
+        <v>121699679</v>
       </c>
       <c r="B80" t="n">
         <v>97067</v>
@@ -10154,17 +10155,21 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471202</v>
+        <v>471222</v>
       </c>
       <c r="R80" t="n">
-        <v>6609664</v>
+        <v>6609540</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10211,12 +10216,7 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10227,17 +10227,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703368</v>
+        <v>121703428</v>
       </c>
       <c r="B81" t="n">
-        <v>91661</v>
+        <v>94527</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10250,26 +10250,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10277,10 +10278,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471347</v>
+        <v>471353</v>
       </c>
       <c r="R81" t="n">
-        <v>6609455</v>
+        <v>6609457</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10321,6 +10322,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10342,17 +10344,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703309</v>
+        <v>121703368</v>
       </c>
       <c r="B82" t="n">
-        <v>97067</v>
+        <v>91661</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10365,27 +10367,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10393,10 +10394,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471356</v>
+        <v>471347</v>
       </c>
       <c r="R82" t="n">
-        <v>6609501</v>
+        <v>6609455</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10437,7 +10438,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10466,7 +10466,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121699951</v>
+        <v>121703406</v>
       </c>
       <c r="B83" t="n">
         <v>94527</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471193</v>
+        <v>471349</v>
       </c>
       <c r="R83" t="n">
-        <v>6609666</v>
+        <v>6609458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10583,10 +10583,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121699679</v>
+        <v>121699951</v>
       </c>
       <c r="B84" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10599,42 +10599,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471222</v>
+        <v>471193</v>
       </c>
       <c r="R84" t="n">
-        <v>6609540</v>
+        <v>6609666</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10681,7 +10677,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10823,7 +10824,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121699581</v>
+        <v>121703365</v>
       </c>
       <c r="B86" t="n">
         <v>94527</v>
@@ -10867,10 +10868,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471279</v>
+        <v>471347</v>
       </c>
       <c r="R86" t="n">
-        <v>6609661</v>
+        <v>6609455</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10911,28 +10912,17 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10943,17 +10933,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699590</v>
+        <v>121699581</v>
       </c>
       <c r="B87" t="n">
-        <v>97067</v>
+        <v>94527</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10966,21 +10956,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10994,10 +10984,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471269</v>
+        <v>471279</v>
       </c>
       <c r="R87" t="n">
-        <v>6609685</v>
+        <v>6609661</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11045,6 +11035,21 @@
       <c r="AH87" t="inlineStr">
         <is>
           <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11062,10 +11067,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121703428</v>
+        <v>121703399</v>
       </c>
       <c r="B88" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11078,38 +11083,46 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471353</v>
+        <v>471349</v>
       </c>
       <c r="R88" t="n">
-        <v>6609457</v>
+        <v>6609458</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11172,17 +11185,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121703399</v>
+        <v>121699965</v>
       </c>
       <c r="B89" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11195,46 +11208,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471349</v>
+        <v>471186</v>
       </c>
       <c r="R89" t="n">
-        <v>6609458</v>
+        <v>6609658</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11286,7 +11291,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11297,17 +11302,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121703311</v>
+        <v>121699935</v>
       </c>
       <c r="B90" t="n">
-        <v>100379</v>
+        <v>97067</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11320,30 +11325,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -11352,10 +11353,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471356</v>
+        <v>471202</v>
       </c>
       <c r="R90" t="n">
-        <v>6609501</v>
+        <v>6609664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11407,7 +11408,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11425,10 +11426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699757</v>
+        <v>121699590</v>
       </c>
       <c r="B91" t="n">
-        <v>94527</v>
+        <v>97067</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11441,21 +11442,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11469,10 +11470,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471208</v>
+        <v>471269</v>
       </c>
       <c r="R91" t="n">
-        <v>6609733</v>
+        <v>6609685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11517,9 +11518,9 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>svämzon längs bäck/surdråg</t>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11530,17 +11531,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121699965</v>
+        <v>121703311</v>
       </c>
       <c r="B92" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11553,26 +11554,30 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -11581,10 +11586,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471186</v>
+        <v>471356</v>
       </c>
       <c r="R92" t="n">
-        <v>6609658</v>
+        <v>6609501</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11636,7 +11641,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11647,17 +11652,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121703406</v>
+        <v>121703425</v>
       </c>
       <c r="B93" t="n">
-        <v>94527</v>
+        <v>100379</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11670,26 +11675,30 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -11698,10 +11707,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471349</v>
+        <v>471353</v>
       </c>
       <c r="R93" t="n">
-        <v>6609458</v>
+        <v>6609457</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11764,14 +11773,14 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121699973</v>
+        <v>121699757</v>
       </c>
       <c r="B94" t="n">
         <v>94527</v>
@@ -11815,10 +11824,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471176</v>
+        <v>471208</v>
       </c>
       <c r="R94" t="n">
-        <v>6609640</v>
+        <v>6609733</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11863,14 +11872,9 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11888,10 +11892,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121703425</v>
+        <v>121699973</v>
       </c>
       <c r="B95" t="n">
-        <v>100379</v>
+        <v>94527</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11904,30 +11908,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471353</v>
+        <v>471176</v>
       </c>
       <c r="R95" t="n">
-        <v>6609457</v>
+        <v>6609640</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11986,12 +11986,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Josefina Jansson, Michael Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698315</v>
+        <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>97059</v>
+        <v>97077</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9294,10 +9294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471319</v>
+        <v>471215</v>
       </c>
       <c r="R73" t="n">
-        <v>6609597</v>
+        <v>6609537</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9360,17 +9360,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698313</v>
+        <v>121698319</v>
       </c>
       <c r="B74" t="n">
-        <v>97059</v>
+        <v>100397</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9383,26 +9383,30 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9411,10 +9415,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471329</v>
+        <v>471316</v>
       </c>
       <c r="R74" t="n">
-        <v>6609593</v>
+        <v>6609608</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9459,16 +9463,6 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog i branter</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>grov granskog i V-sluttning</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
@@ -9477,17 +9471,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698319</v>
+        <v>121698315</v>
       </c>
       <c r="B75" t="n">
-        <v>100379</v>
+        <v>97077</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9500,30 +9494,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9532,10 +9522,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R75" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9579,6 +9569,16 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>gammal olikåldrig sumpskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9598,7 +9598,7 @@
         <v>121697845</v>
       </c>
       <c r="B76" t="n">
-        <v>74714</v>
+        <v>74727</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698324</v>
+        <v>121698313</v>
       </c>
       <c r="B77" t="n">
-        <v>94731</v>
+        <v>97077</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9751,38 +9751,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>210</v>
+        <v>224361</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -9791,10 +9779,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471319</v>
+        <v>471329</v>
       </c>
       <c r="R77" t="n">
-        <v>6609597</v>
+        <v>6609593</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9841,32 +9829,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9877,17 +9845,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698287</v>
+        <v>121698324</v>
       </c>
       <c r="B78" t="n">
-        <v>97059</v>
+        <v>94749</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9900,26 +9868,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>224361</v>
+        <v>210</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9928,10 +9908,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471215</v>
+        <v>471319</v>
       </c>
       <c r="R78" t="n">
-        <v>6609537</v>
+        <v>6609597</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9978,12 +9958,32 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703309</v>
+        <v>121699951</v>
       </c>
       <c r="B79" t="n">
-        <v>97067</v>
+        <v>94545</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10017,21 +10017,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471356</v>
+        <v>471193</v>
       </c>
       <c r="R79" t="n">
-        <v>6609501</v>
+        <v>6609666</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10111,17 +10111,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121699679</v>
+        <v>121703309</v>
       </c>
       <c r="B80" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10155,21 +10155,17 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471222</v>
+        <v>471356</v>
       </c>
       <c r="R80" t="n">
-        <v>6609540</v>
+        <v>6609501</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10216,7 +10212,12 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10227,17 +10228,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703428</v>
+        <v>121699757</v>
       </c>
       <c r="B81" t="n">
-        <v>94527</v>
+        <v>94545</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10278,10 +10279,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471353</v>
+        <v>471208</v>
       </c>
       <c r="R81" t="n">
-        <v>6609457</v>
+        <v>6609733</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10326,14 +10327,9 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10351,10 +10347,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703368</v>
+        <v>121703311</v>
       </c>
       <c r="B82" t="n">
-        <v>91661</v>
+        <v>100397</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10367,26 +10363,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10394,10 +10395,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471347</v>
+        <v>471356</v>
       </c>
       <c r="R82" t="n">
-        <v>6609455</v>
+        <v>6609501</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10438,6 +10439,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10448,7 +10450,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10466,10 +10468,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121703406</v>
+        <v>121703425</v>
       </c>
       <c r="B83" t="n">
-        <v>94527</v>
+        <v>100397</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10482,26 +10484,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -10510,10 +10516,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471349</v>
+        <v>471353</v>
       </c>
       <c r="R83" t="n">
-        <v>6609458</v>
+        <v>6609457</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10576,17 +10582,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121699951</v>
+        <v>121703365</v>
       </c>
       <c r="B84" t="n">
-        <v>94527</v>
+        <v>94545</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10627,10 +10633,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471193</v>
+        <v>471347</v>
       </c>
       <c r="R84" t="n">
-        <v>6609666</v>
+        <v>6609455</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10671,7 +10677,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10682,7 +10687,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10703,7 +10708,7 @@
         <v>121700010</v>
       </c>
       <c r="B85" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10824,10 +10829,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121703365</v>
+        <v>121703399</v>
       </c>
       <c r="B86" t="n">
-        <v>94527</v>
+        <v>100397</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10840,38 +10845,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471347</v>
+        <v>471349</v>
       </c>
       <c r="R86" t="n">
-        <v>6609455</v>
+        <v>6609458</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10912,6 +10925,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10933,17 +10947,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699581</v>
+        <v>121703406</v>
       </c>
       <c r="B87" t="n">
-        <v>94527</v>
+        <v>94545</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10984,10 +10998,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471279</v>
+        <v>471349</v>
       </c>
       <c r="R87" t="n">
-        <v>6609661</v>
+        <v>6609458</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11034,22 +11048,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11060,17 +11064,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121703399</v>
+        <v>121699965</v>
       </c>
       <c r="B88" t="n">
-        <v>100379</v>
+        <v>94545</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11083,46 +11087,38 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471349</v>
+        <v>471186</v>
       </c>
       <c r="R88" t="n">
-        <v>6609458</v>
+        <v>6609658</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11174,7 +11170,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11185,17 +11181,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699965</v>
+        <v>121699973</v>
       </c>
       <c r="B89" t="n">
-        <v>94527</v>
+        <v>94545</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11236,10 +11232,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471186</v>
+        <v>471176</v>
       </c>
       <c r="R89" t="n">
-        <v>6609658</v>
+        <v>6609640</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11286,7 +11282,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
@@ -11312,7 +11308,7 @@
         <v>121699935</v>
       </c>
       <c r="B90" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11426,10 +11422,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699590</v>
+        <v>121699581</v>
       </c>
       <c r="B91" t="n">
-        <v>97067</v>
+        <v>94545</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11442,21 +11438,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11470,10 +11466,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471269</v>
+        <v>471279</v>
       </c>
       <c r="R91" t="n">
-        <v>6609685</v>
+        <v>6609661</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11521,6 +11517,21 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11538,10 +11549,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121703311</v>
+        <v>121703428</v>
       </c>
       <c r="B92" t="n">
-        <v>100379</v>
+        <v>94545</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11554,30 +11565,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -11586,10 +11593,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471356</v>
+        <v>471353</v>
       </c>
       <c r="R92" t="n">
-        <v>6609501</v>
+        <v>6609457</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11641,7 +11648,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11652,17 +11659,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121703425</v>
+        <v>121699590</v>
       </c>
       <c r="B93" t="n">
-        <v>100379</v>
+        <v>97085</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11675,30 +11682,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -11707,10 +11710,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471353</v>
+        <v>471269</v>
       </c>
       <c r="R93" t="n">
-        <v>6609457</v>
+        <v>6609685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11757,12 +11760,7 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11780,10 +11778,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121699757</v>
+        <v>121703368</v>
       </c>
       <c r="B94" t="n">
-        <v>94527</v>
+        <v>91675</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11796,27 +11794,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>4769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11824,10 +11821,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471208</v>
+        <v>471347</v>
       </c>
       <c r="R94" t="n">
-        <v>6609733</v>
+        <v>6609455</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11868,13 +11865,17 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11885,17 +11886,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121699973</v>
+        <v>121699679</v>
       </c>
       <c r="B95" t="n">
-        <v>94527</v>
+        <v>97085</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11908,38 +11909,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471176</v>
+        <v>471222</v>
       </c>
       <c r="R95" t="n">
-        <v>6609640</v>
+        <v>6609540</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11986,12 +11991,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12012,7 +12012,7 @@
         <v>121709723</v>
       </c>
       <c r="B96" t="n">
-        <v>100379</v>
+        <v>100397</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Josefina Jansson, Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -12133,7 +12133,7 @@
         <v>121712106</v>
       </c>
       <c r="B97" t="n">
-        <v>94527</v>
+        <v>94545</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -11305,10 +11305,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699935</v>
+        <v>121699581</v>
       </c>
       <c r="B90" t="n">
-        <v>97085</v>
+        <v>94545</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11321,21 +11321,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11349,10 +11349,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471202</v>
+        <v>471279</v>
       </c>
       <c r="R90" t="n">
-        <v>6609664</v>
+        <v>6609661</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11399,12 +11399,22 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11422,10 +11432,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699581</v>
+        <v>121699935</v>
       </c>
       <c r="B91" t="n">
-        <v>94545</v>
+        <v>97085</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11438,21 +11448,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11466,10 +11476,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471279</v>
+        <v>471202</v>
       </c>
       <c r="R91" t="n">
-        <v>6609661</v>
+        <v>6609664</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11516,22 +11526,12 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -11305,10 +11305,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699581</v>
+        <v>121699935</v>
       </c>
       <c r="B90" t="n">
-        <v>94545</v>
+        <v>97085</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11321,21 +11321,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11349,10 +11349,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471279</v>
+        <v>471202</v>
       </c>
       <c r="R90" t="n">
-        <v>6609661</v>
+        <v>6609664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11399,22 +11399,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11432,10 +11422,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699935</v>
+        <v>121699581</v>
       </c>
       <c r="B91" t="n">
-        <v>97085</v>
+        <v>94545</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11448,21 +11438,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11476,10 +11466,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471202</v>
+        <v>471279</v>
       </c>
       <c r="R91" t="n">
-        <v>6609664</v>
+        <v>6609661</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11526,12 +11516,22 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9595,10 +9595,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121697845</v>
+        <v>121698313</v>
       </c>
       <c r="B76" t="n">
-        <v>74727</v>
+        <v>97077</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9607,34 +9607,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>224361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9642,10 +9639,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471285</v>
+        <v>471329</v>
       </c>
       <c r="R76" t="n">
-        <v>6609641</v>
+        <v>6609593</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9692,32 +9689,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9728,17 +9705,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121698313</v>
+        <v>121697845</v>
       </c>
       <c r="B77" t="n">
-        <v>97077</v>
+        <v>74727</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9747,31 +9724,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9779,10 +9759,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471329</v>
+        <v>471285</v>
       </c>
       <c r="R77" t="n">
-        <v>6609593</v>
+        <v>6609641</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9829,12 +9809,32 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96252252</v>
+        <v>96251799</v>
       </c>
       <c r="B26" t="n">
-        <v>95511</v>
+        <v>90319</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221944</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471259.8086330662</v>
+        <v>471259.4027788527</v>
       </c>
       <c r="R26" t="n">
-        <v>6609416.56388958</v>
+        <v>6609429.72073366</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>fuktig blandskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96251799</v>
+        <v>96252447</v>
       </c>
       <c r="B27" t="n">
-        <v>90319</v>
+        <v>88953</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3714,38 +3714,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>5754</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471259.4027788527</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R27" t="n">
-        <v>6609429.72073366</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3801,7 +3810,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>fuktig blandskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3823,14 +3832,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96252447</v>
+        <v>95956831</v>
       </c>
       <c r="B28" t="n">
-        <v>88953</v>
+        <v>57308</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3839,46 +3848,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5754</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471259.8086330662</v>
+        <v>471225</v>
       </c>
       <c r="R28" t="n">
-        <v>6609416.56388958</v>
+        <v>6609590</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3902,22 +3902,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3931,7 +3921,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3953,37 +3943,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95956831</v>
+        <v>95956815</v>
       </c>
       <c r="B29" t="n">
-        <v>57308</v>
+        <v>90319</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3993,10 +3983,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471225</v>
+        <v>471178.5493512115</v>
       </c>
       <c r="R29" t="n">
-        <v>6609590</v>
+        <v>6609657.489466893</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4026,9 +4016,19 @@
           <t>2021-09-06</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4064,10 +4064,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95956815</v>
+        <v>96251636</v>
       </c>
       <c r="B30" t="n">
-        <v>90319</v>
+        <v>99398</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471178.5493512115</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R30" t="n">
-        <v>6609657.489466893</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4185,7 +4185,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96251636</v>
+        <v>96251635</v>
       </c>
       <c r="B31" t="n">
         <v>99398</v>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471309.9309650694</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R31" t="n">
-        <v>6609410.108756405</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96251635</v>
+        <v>95972655</v>
       </c>
       <c r="B32" t="n">
-        <v>99398</v>
+        <v>89652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4318,25 +4318,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>73</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4346,13 +4346,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471259.8086330662</v>
+        <v>471296.9326695912</v>
       </c>
       <c r="R32" t="n">
-        <v>6609416.56388958</v>
+        <v>6609631.792281208</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95972655</v>
+        <v>96251810</v>
       </c>
       <c r="B33" t="n">
-        <v>89652</v>
+        <v>90319</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4439,25 +4439,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471296.9326695912</v>
+        <v>471318.0003416255</v>
       </c>
       <c r="R33" t="n">
-        <v>6609631.792281208</v>
+        <v>6609404.987824169</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96251810</v>
+        <v>96251752</v>
       </c>
       <c r="B34" t="n">
-        <v>90319</v>
+        <v>101680</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4564,21 +4564,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471318.0003416255</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R34" t="n">
-        <v>6609404.987824169</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96251752</v>
+        <v>96251807</v>
       </c>
       <c r="B35" t="n">
-        <v>101680</v>
+        <v>90319</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471259.8086330662</v>
+        <v>471247.6348481966</v>
       </c>
       <c r="R35" t="n">
-        <v>6609416.56388958</v>
+        <v>6609415.139556407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96251807</v>
+        <v>96251672</v>
       </c>
       <c r="B36" t="n">
-        <v>90319</v>
+        <v>101120</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4806,21 +4806,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>222002</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471247.6348481966</v>
+        <v>471368.0221119327</v>
       </c>
       <c r="R36" t="n">
-        <v>6609415.139556407</v>
+        <v>6609451.655002752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96251672</v>
+        <v>95956813</v>
       </c>
       <c r="B37" t="n">
-        <v>101120</v>
+        <v>90319</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4927,21 +4927,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471368.0221119327</v>
+        <v>471211.8506313803</v>
       </c>
       <c r="R37" t="n">
-        <v>6609451.655002752</v>
+        <v>6609572.750275725</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5032,10 +5032,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95956813</v>
+        <v>96251671</v>
       </c>
       <c r="B38" t="n">
-        <v>90319</v>
+        <v>101120</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5048,21 +5048,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>222002</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471211.8506313803</v>
+        <v>471313.2387810608</v>
       </c>
       <c r="R38" t="n">
-        <v>6609572.750275725</v>
+        <v>6609444.991354768</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5153,7 +5153,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96251671</v>
+        <v>96251670</v>
       </c>
       <c r="B39" t="n">
         <v>101120</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471313.2387810608</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R39" t="n">
-        <v>6609444.991354768</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96251670</v>
+        <v>96251798</v>
       </c>
       <c r="B40" t="n">
-        <v>101120</v>
+        <v>90319</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5290,21 +5290,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471309.9309650694</v>
+        <v>471148.7887846382</v>
       </c>
       <c r="R40" t="n">
-        <v>6609410.108756405</v>
+        <v>6609741.188059531</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96251798</v>
+        <v>96251808</v>
       </c>
       <c r="B41" t="n">
         <v>90319</v>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471148.7887846382</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R41" t="n">
-        <v>6609741.188059531</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96251808</v>
+        <v>95956814</v>
       </c>
       <c r="B42" t="n">
         <v>90319</v>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471259.8086330662</v>
+        <v>471202.4547789301</v>
       </c>
       <c r="R42" t="n">
-        <v>6609416.56388958</v>
+        <v>6609668.940877154</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>95956814</v>
+        <v>96251812</v>
       </c>
       <c r="B43" t="n">
         <v>90319</v>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471202.4547789301</v>
+        <v>471368.0221119327</v>
       </c>
       <c r="R43" t="n">
-        <v>6609668.940877154</v>
+        <v>6609451.655002752</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96251812</v>
+        <v>96251753</v>
       </c>
       <c r="B44" t="n">
-        <v>90319</v>
+        <v>101680</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471368.0221119327</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R44" t="n">
-        <v>6609451.655002752</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96251753</v>
+        <v>96252446</v>
       </c>
       <c r="B45" t="n">
-        <v>101680</v>
+        <v>88953</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5891,25 +5891,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>5754</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471309.9309650694</v>
+        <v>471269.1746462852</v>
       </c>
       <c r="R45" t="n">
-        <v>6609410.108756405</v>
+        <v>6609448.364473196</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96252446</v>
+        <v>96252613</v>
       </c>
       <c r="B46" t="n">
-        <v>88953</v>
+        <v>90671</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6016,21 +6016,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471269.1746462852</v>
+        <v>471340.9286586023</v>
       </c>
       <c r="R46" t="n">
-        <v>6609448.364473196</v>
+        <v>6609553.54842629</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6121,7 +6121,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>96252613</v>
+        <v>95956974</v>
       </c>
       <c r="B47" t="n">
         <v>90671</v>
@@ -6154,20 +6154,29 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471340.9286586023</v>
+        <v>471224.6511069508</v>
       </c>
       <c r="R47" t="n">
-        <v>6609553.54842629</v>
+        <v>6609589.852244456</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6191,7 +6200,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6201,7 +6210,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6220,7 +6229,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6242,10 +6251,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>95956974</v>
+        <v>96251811</v>
       </c>
       <c r="B48" t="n">
-        <v>90671</v>
+        <v>90319</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6254,50 +6263,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471224.6511069508</v>
+        <v>471313.2387810608</v>
       </c>
       <c r="R48" t="n">
-        <v>6609589.852244456</v>
+        <v>6609444.991354768</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96251811</v>
+        <v>96251948</v>
       </c>
       <c r="B49" t="n">
-        <v>90319</v>
+        <v>100515</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6384,25 +6384,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>223246</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471313.2387810608</v>
+        <v>471259.4027788527</v>
       </c>
       <c r="R49" t="n">
-        <v>6609444.991354768</v>
+        <v>6609429.72073366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>fuktig blandskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6493,10 +6493,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96251948</v>
+        <v>96251809</v>
       </c>
       <c r="B50" t="n">
-        <v>100515</v>
+        <v>90319</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6505,25 +6505,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223246</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>471259.4027788527</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R50" t="n">
-        <v>6609429.72073366</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>fuktig blandskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6614,10 +6614,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96251809</v>
+        <v>87904463</v>
       </c>
       <c r="B51" t="n">
-        <v>90319</v>
+        <v>98431</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6630,21 +6630,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6654,13 +6654,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>471309.9309650694</v>
+        <v>471339.6404136405</v>
       </c>
       <c r="R51" t="n">
-        <v>6609410.108756405</v>
+        <v>6609517.639566744</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>källpåverkad granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96252253</v>
+        <v>87904428</v>
       </c>
       <c r="B52" t="n">
-        <v>95511</v>
+        <v>95521</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6751,23 +6751,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221944</v>
+        <v>224363</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6775,13 +6771,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>471324.7866378406</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R52" t="n">
-        <v>6609563.283939824</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6805,7 +6801,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -6815,7 +6811,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -6834,7 +6830,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6856,10 +6852,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>87904463</v>
+        <v>87904488</v>
       </c>
       <c r="B53" t="n">
-        <v>98431</v>
+        <v>96313</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6872,23 +6868,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222771</v>
+        <v>223609</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6896,10 +6888,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471339.6404136405</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R53" t="n">
-        <v>6609517.639566744</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6950,12 +6942,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>källpåverkad granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6977,10 +6970,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>87904428</v>
+        <v>87904660</v>
       </c>
       <c r="B54" t="n">
-        <v>95521</v>
+        <v>98520</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6993,19 +6986,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7013,10 +7010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471315.03151316</v>
+        <v>471246.9145555807</v>
       </c>
       <c r="R54" t="n">
-        <v>6609612.935878632</v>
+        <v>6609387.319721107</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7072,7 +7069,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7094,10 +7091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>87904488</v>
+        <v>87904436</v>
       </c>
       <c r="B55" t="n">
-        <v>96313</v>
+        <v>95514</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7110,16 +7107,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>223609</v>
+        <v>224361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Vanlig lopplummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
+          <t>Huperzia selago subsp. selago</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -7184,7 +7181,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7212,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>87904660</v>
+        <v>88202319</v>
       </c>
       <c r="B56" t="n">
-        <v>98520</v>
+        <v>94653</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7228,21 +7224,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>2563</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geocalyx graveolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schrad.) Nees</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7252,10 +7248,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>471246.9145555807</v>
+        <v>471321.5221799276</v>
       </c>
       <c r="R56" t="n">
-        <v>6609387.319721107</v>
+        <v>6609600.238987684</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7282,7 +7278,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7292,7 +7288,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7311,7 +7307,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>örtrik sumpskog</t>
+          <t>sumpig granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7333,10 +7329,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>87904436</v>
+        <v>87904450</v>
       </c>
       <c r="B57" t="n">
-        <v>95514</v>
+        <v>101680</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7349,19 +7345,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>224361</v>
+        <v>222412</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig lopplummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Huperzia selago subsp. selago</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471315.03151316</v>
+        <v>471200.7479510409</v>
       </c>
       <c r="R57" t="n">
-        <v>6609612.935878632</v>
+        <v>6609644.671690273</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7450,10 +7450,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>88202319</v>
+        <v>87904451</v>
       </c>
       <c r="B58" t="n">
-        <v>94653</v>
+        <v>101680</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7466,21 +7466,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2563</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471321.5221799276</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R58" t="n">
-        <v>6609600.238987684</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>sumpig granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>87904450</v>
+        <v>87904658</v>
       </c>
       <c r="B59" t="n">
-        <v>101680</v>
+        <v>98520</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7587,21 +7587,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471200.7479510409</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R59" t="n">
-        <v>6609644.671690273</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7692,10 +7692,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>87904451</v>
+        <v>87904659</v>
       </c>
       <c r="B60" t="n">
-        <v>101680</v>
+        <v>98520</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7813,10 +7813,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>87904658</v>
+        <v>88202411</v>
       </c>
       <c r="B61" t="n">
-        <v>98520</v>
+        <v>95521</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7829,23 +7829,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7853,10 +7849,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471315.03151316</v>
+        <v>471150.8234233134</v>
       </c>
       <c r="R61" t="n">
-        <v>6609612.935878632</v>
+        <v>6609742.184129979</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7883,7 +7879,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -7893,7 +7889,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -7912,7 +7908,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7934,10 +7930,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>87904659</v>
+        <v>87904409</v>
       </c>
       <c r="B62" t="n">
-        <v>98520</v>
+        <v>99398</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7950,21 +7946,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8055,7 +8051,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>88202411</v>
+        <v>87904430</v>
       </c>
       <c r="B63" t="n">
         <v>95521</v>
@@ -8091,10 +8087,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471150.8234233134</v>
+        <v>471200.7479510409</v>
       </c>
       <c r="R63" t="n">
-        <v>6609742.184129979</v>
+        <v>6609644.671690273</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8121,7 +8117,7 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -8131,7 +8127,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8150,7 +8146,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8172,10 +8168,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>87904409</v>
+        <v>87904452</v>
       </c>
       <c r="B64" t="n">
-        <v>99398</v>
+        <v>101680</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8188,21 +8184,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8212,10 +8208,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471262.8491675095</v>
+        <v>471246.9145555807</v>
       </c>
       <c r="R64" t="n">
-        <v>6609416.540566096</v>
+        <v>6609387.319721107</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8271,7 +8267,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8293,10 +8289,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>87904430</v>
+        <v>88202399</v>
       </c>
       <c r="B65" t="n">
-        <v>95521</v>
+        <v>96251</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8309,19 +8305,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>224363</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8329,10 +8329,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471200.7479510409</v>
+        <v>471150.8234233134</v>
       </c>
       <c r="R65" t="n">
-        <v>6609644.671690273</v>
+        <v>6609742.184129979</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>87904452</v>
+        <v>87904440</v>
       </c>
       <c r="B66" t="n">
-        <v>101680</v>
+        <v>101120</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8426,16 +8426,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471246.9145555807</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R66" t="n">
-        <v>6609387.319721107</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>örtrik sumpskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>88202399</v>
+        <v>87904429</v>
       </c>
       <c r="B67" t="n">
-        <v>96251</v>
+        <v>95521</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8547,23 +8547,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>224363</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8571,10 +8567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471150.8234233134</v>
+        <v>471261.6791215731</v>
       </c>
       <c r="R67" t="n">
-        <v>6609742.184129979</v>
+        <v>6609660.391988517</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8601,7 +8597,7 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -8611,7 +8607,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -8630,7 +8626,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8652,10 +8648,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>87904440</v>
+        <v>87904408</v>
       </c>
       <c r="B68" t="n">
-        <v>101120</v>
+        <v>99398</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8668,21 +8664,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222002</v>
+        <v>221235</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8692,10 +8688,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471262.8491675095</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R68" t="n">
-        <v>6609416.540566096</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8773,10 +8769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>87904429</v>
+        <v>87904464</v>
       </c>
       <c r="B69" t="n">
-        <v>95521</v>
+        <v>98431</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8789,19 +8785,23 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>224363</v>
+        <v>222771</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8809,10 +8809,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471261.6791215731</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R69" t="n">
-        <v>6609660.391988517</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87904408</v>
+        <v>88202343</v>
       </c>
       <c r="B70" t="n">
-        <v>99398</v>
+        <v>96313</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8906,23 +8906,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221235</v>
+        <v>223609</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8930,10 +8926,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471315.03151316</v>
+        <v>471288.2950552536</v>
       </c>
       <c r="R70" t="n">
-        <v>6609612.935878632</v>
+        <v>6609628.823163424</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8960,7 +8956,7 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -8970,7 +8966,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -8984,12 +8980,13 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9011,10 +9008,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>87904464</v>
+        <v>121698315</v>
       </c>
       <c r="B71" t="n">
-        <v>98431</v>
+        <v>97079</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9027,37 +9024,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222771</v>
+        <v>224361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471262.8491675095</v>
+        <v>471319</v>
       </c>
       <c r="R71" t="n">
-        <v>6609416.540566096</v>
+        <v>6609597</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9081,22 +9082,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9105,37 +9096,39 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>88202343</v>
+        <v>121698319</v>
       </c>
       <c r="B72" t="n">
-        <v>96313</v>
+        <v>100399</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9148,33 +9141,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223609</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471288.2950552536</v>
+        <v>471316</v>
       </c>
       <c r="R72" t="n">
-        <v>6609628.823163424</v>
+        <v>6609608</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9198,22 +9203,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9226,34 +9221,25 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>fuktig barrskog</t>
-        </is>
-      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698287</v>
+        <v>121698313</v>
       </c>
       <c r="B73" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9294,10 +9280,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471215</v>
+        <v>471329</v>
       </c>
       <c r="R73" t="n">
-        <v>6609537</v>
+        <v>6609593</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9344,12 +9330,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9367,10 +9353,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698319</v>
+        <v>121698324</v>
       </c>
       <c r="B74" t="n">
-        <v>100397</v>
+        <v>94751</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9383,28 +9369,36 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -9415,10 +9409,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R74" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9462,6 +9456,36 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9478,10 +9502,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698315</v>
+        <v>121697845</v>
       </c>
       <c r="B75" t="n">
-        <v>97077</v>
+        <v>74729</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9490,31 +9514,34 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9522,10 +9549,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471319</v>
+        <v>471285</v>
       </c>
       <c r="R75" t="n">
-        <v>6609597</v>
+        <v>6609641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9577,7 +9604,27 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9595,10 +9642,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121698313</v>
+        <v>121698287</v>
       </c>
       <c r="B76" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9639,10 +9686,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471329</v>
+        <v>471215</v>
       </c>
       <c r="R76" t="n">
-        <v>6609593</v>
+        <v>6609537</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9689,12 +9736,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>grov granskog i V-sluttning</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9712,10 +9759,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121697845</v>
+        <v>121703406</v>
       </c>
       <c r="B77" t="n">
-        <v>74727</v>
+        <v>94547</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9724,34 +9771,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>2813</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9759,10 +9803,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471285</v>
+        <v>471349</v>
       </c>
       <c r="R77" t="n">
-        <v>6609641</v>
+        <v>6609458</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9809,32 +9853,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9845,17 +9869,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121698324</v>
+        <v>121699951</v>
       </c>
       <c r="B78" t="n">
-        <v>94749</v>
+        <v>94547</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9868,38 +9892,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9908,10 +9920,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471319</v>
+        <v>471193</v>
       </c>
       <c r="R78" t="n">
-        <v>6609597</v>
+        <v>6609666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9958,32 +9970,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9994,17 +9986,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121699951</v>
+        <v>121699965</v>
       </c>
       <c r="B79" t="n">
-        <v>94545</v>
+        <v>94547</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10045,10 +10037,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471193</v>
+        <v>471186</v>
       </c>
       <c r="R79" t="n">
-        <v>6609666</v>
+        <v>6609658</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10118,10 +10110,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121703309</v>
+        <v>121703368</v>
       </c>
       <c r="B80" t="n">
-        <v>97085</v>
+        <v>91677</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10134,27 +10126,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10162,10 +10153,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471356</v>
+        <v>471347</v>
       </c>
       <c r="R80" t="n">
-        <v>6609501</v>
+        <v>6609455</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10206,7 +10197,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10217,7 +10207,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10235,10 +10225,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121699757</v>
+        <v>121703311</v>
       </c>
       <c r="B81" t="n">
-        <v>94545</v>
+        <v>100399</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10251,26 +10241,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10279,10 +10273,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471208</v>
+        <v>471356</v>
       </c>
       <c r="R81" t="n">
-        <v>6609733</v>
+        <v>6609501</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10327,9 +10321,14 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10340,17 +10339,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703311</v>
+        <v>121699581</v>
       </c>
       <c r="B82" t="n">
-        <v>100397</v>
+        <v>94547</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10363,30 +10362,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -10395,10 +10390,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471356</v>
+        <v>471279</v>
       </c>
       <c r="R82" t="n">
-        <v>6609501</v>
+        <v>6609661</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10445,12 +10440,22 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10468,10 +10473,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121703425</v>
+        <v>121703365</v>
       </c>
       <c r="B83" t="n">
-        <v>100397</v>
+        <v>94547</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10484,30 +10489,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -10516,10 +10517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471353</v>
+        <v>471347</v>
       </c>
       <c r="R83" t="n">
-        <v>6609457</v>
+        <v>6609455</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10560,7 +10561,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10582,17 +10582,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121703365</v>
+        <v>121703309</v>
       </c>
       <c r="B84" t="n">
-        <v>94545</v>
+        <v>97087</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10605,21 +10605,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10633,10 +10633,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471347</v>
+        <v>471356</v>
       </c>
       <c r="R84" t="n">
-        <v>6609455</v>
+        <v>6609501</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10677,6 +10677,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10687,7 +10688,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10698,7 +10699,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10708,7 +10709,7 @@
         <v>121700010</v>
       </c>
       <c r="B85" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10829,10 +10830,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121703399</v>
+        <v>121699757</v>
       </c>
       <c r="B86" t="n">
-        <v>100397</v>
+        <v>94547</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10845,46 +10846,38 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471349</v>
+        <v>471208</v>
       </c>
       <c r="R86" t="n">
-        <v>6609458</v>
+        <v>6609733</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10929,14 +10922,9 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10947,17 +10935,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121703406</v>
+        <v>121703428</v>
       </c>
       <c r="B87" t="n">
-        <v>94545</v>
+        <v>94547</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10998,10 +10986,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471349</v>
+        <v>471353</v>
       </c>
       <c r="R87" t="n">
-        <v>6609458</v>
+        <v>6609457</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11071,10 +11059,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121699965</v>
+        <v>121703425</v>
       </c>
       <c r="B88" t="n">
-        <v>94545</v>
+        <v>100399</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11087,26 +11075,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -11115,10 +11107,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471186</v>
+        <v>471353</v>
       </c>
       <c r="R88" t="n">
-        <v>6609658</v>
+        <v>6609457</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11170,7 +11162,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11181,17 +11173,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699973</v>
+        <v>121699590</v>
       </c>
       <c r="B89" t="n">
-        <v>94545</v>
+        <v>97087</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11204,21 +11196,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11232,10 +11224,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471176</v>
+        <v>471269</v>
       </c>
       <c r="R89" t="n">
-        <v>6609640</v>
+        <v>6609685</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11282,12 +11274,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11298,17 +11285,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699935</v>
+        <v>121699973</v>
       </c>
       <c r="B90" t="n">
-        <v>97085</v>
+        <v>94547</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11321,21 +11308,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11349,10 +11336,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471202</v>
+        <v>471176</v>
       </c>
       <c r="R90" t="n">
-        <v>6609664</v>
+        <v>6609640</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11399,12 +11386,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11415,17 +11402,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699581</v>
+        <v>121699679</v>
       </c>
       <c r="B91" t="n">
-        <v>94545</v>
+        <v>97087</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11438,38 +11425,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471279</v>
+        <v>471222</v>
       </c>
       <c r="R91" t="n">
-        <v>6609661</v>
+        <v>6609540</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11516,22 +11507,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11542,17 +11518,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121703428</v>
+        <v>121699935</v>
       </c>
       <c r="B92" t="n">
-        <v>94545</v>
+        <v>97087</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11565,21 +11541,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11593,10 +11569,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471353</v>
+        <v>471202</v>
       </c>
       <c r="R92" t="n">
-        <v>6609457</v>
+        <v>6609664</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11648,7 +11624,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11659,17 +11635,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121699590</v>
+        <v>121703399</v>
       </c>
       <c r="B93" t="n">
-        <v>97085</v>
+        <v>100399</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11682,38 +11658,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471269</v>
+        <v>471349</v>
       </c>
       <c r="R93" t="n">
-        <v>6609685</v>
+        <v>6609458</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11760,7 +11744,12 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11778,10 +11767,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121703368</v>
+        <v>121712106</v>
       </c>
       <c r="B94" t="n">
-        <v>91675</v>
+        <v>94547</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11794,26 +11783,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11821,10 +11811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471347</v>
+        <v>471319</v>
       </c>
       <c r="R94" t="n">
-        <v>6609455</v>
+        <v>6609597</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11865,17 +11855,18 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11886,17 +11877,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121699679</v>
+        <v>121709723</v>
       </c>
       <c r="B95" t="n">
-        <v>97085</v>
+        <v>100399</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11909,42 +11900,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471222</v>
+        <v>471351</v>
       </c>
       <c r="R95" t="n">
-        <v>6609540</v>
+        <v>6609528</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11991,7 +11982,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12002,248 +11998,10 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>121709723</v>
-      </c>
-      <c r="B96" t="n">
-        <v>100397</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>471351</v>
-      </c>
-      <c r="R96" t="n">
-        <v>6609528</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Hällefors</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Grythyttan</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>V-sluttning</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Michael Andersson, Josefina Jansson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>121712106</v>
-      </c>
-      <c r="B97" t="n">
-        <v>94545</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>2813</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Rhytidiadelphus subpinnatus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>471319</v>
-      </c>
-      <c r="R97" t="n">
-        <v>6609597</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Hällefors</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Grythyttan</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk och klibbal</t>
-        </is>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9008,10 +9008,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121698315</v>
+        <v>121698324</v>
       </c>
       <c r="B71" t="n">
-        <v>97079</v>
+        <v>94758</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9024,26 +9024,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>224361</v>
+        <v>210</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -9107,7 +9119,27 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9125,10 +9157,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121698319</v>
+        <v>121698287</v>
       </c>
       <c r="B72" t="n">
-        <v>100399</v>
+        <v>97086</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9141,30 +9173,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -9173,10 +9201,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471316</v>
+        <v>471215</v>
       </c>
       <c r="R72" t="n">
-        <v>6609608</v>
+        <v>6609537</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9221,6 +9249,16 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
@@ -9229,17 +9267,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698313</v>
+        <v>121698319</v>
       </c>
       <c r="B73" t="n">
-        <v>97079</v>
+        <v>100406</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9252,26 +9290,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9280,10 +9322,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471329</v>
+        <v>471316</v>
       </c>
       <c r="R73" t="n">
-        <v>6609593</v>
+        <v>6609608</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9328,16 +9370,6 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog i branter</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>grov granskog i V-sluttning</t>
-        </is>
-      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
@@ -9346,17 +9378,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698324</v>
+        <v>121698315</v>
       </c>
       <c r="B74" t="n">
-        <v>94751</v>
+        <v>97086</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9369,38 +9401,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>224361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9464,27 +9484,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9502,10 +9502,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121697845</v>
+        <v>121698313</v>
       </c>
       <c r="B75" t="n">
-        <v>74729</v>
+        <v>97086</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9514,34 +9514,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>224361</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9549,10 +9546,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471285</v>
+        <v>471329</v>
       </c>
       <c r="R75" t="n">
-        <v>6609641</v>
+        <v>6609593</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9599,32 +9596,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9635,17 +9612,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121698287</v>
+        <v>121697845</v>
       </c>
       <c r="B76" t="n">
-        <v>97079</v>
+        <v>74729</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9654,31 +9631,34 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9686,10 +9666,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471215</v>
+        <v>471285</v>
       </c>
       <c r="R76" t="n">
-        <v>6609537</v>
+        <v>6609641</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9736,12 +9716,32 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9752,17 +9752,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121703406</v>
+        <v>121699965</v>
       </c>
       <c r="B77" t="n">
-        <v>94547</v>
+        <v>94554</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471349</v>
+        <v>471186</v>
       </c>
       <c r="R77" t="n">
-        <v>6609458</v>
+        <v>6609658</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9876,10 +9876,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121699951</v>
+        <v>121699679</v>
       </c>
       <c r="B78" t="n">
-        <v>94547</v>
+        <v>97094</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9892,38 +9892,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471193</v>
+        <v>471222</v>
       </c>
       <c r="R78" t="n">
-        <v>6609666</v>
+        <v>6609540</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9970,12 +9974,7 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9993,10 +9992,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121699965</v>
+        <v>121703425</v>
       </c>
       <c r="B79" t="n">
-        <v>94547</v>
+        <v>100406</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10009,26 +10008,30 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -10037,10 +10040,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471186</v>
+        <v>471353</v>
       </c>
       <c r="R79" t="n">
-        <v>6609658</v>
+        <v>6609457</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10092,7 +10095,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10103,17 +10106,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121703368</v>
+        <v>121703311</v>
       </c>
       <c r="B80" t="n">
-        <v>91677</v>
+        <v>100406</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10126,26 +10129,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10153,10 +10161,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471347</v>
+        <v>471356</v>
       </c>
       <c r="R80" t="n">
-        <v>6609455</v>
+        <v>6609501</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10197,6 +10205,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10207,7 +10216,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10225,10 +10234,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703311</v>
+        <v>121703428</v>
       </c>
       <c r="B81" t="n">
-        <v>100399</v>
+        <v>94554</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10241,30 +10250,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -10273,10 +10278,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471356</v>
+        <v>471353</v>
       </c>
       <c r="R81" t="n">
-        <v>6609501</v>
+        <v>6609457</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10328,7 +10333,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10339,17 +10344,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121699581</v>
+        <v>121703309</v>
       </c>
       <c r="B82" t="n">
-        <v>94547</v>
+        <v>97094</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10362,21 +10367,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10390,10 +10395,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471279</v>
+        <v>471356</v>
       </c>
       <c r="R82" t="n">
-        <v>6609661</v>
+        <v>6609501</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10440,22 +10445,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10473,10 +10468,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121703365</v>
+        <v>121700010</v>
       </c>
       <c r="B83" t="n">
-        <v>94547</v>
+        <v>92021</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10489,27 +10484,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2813</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10517,10 +10519,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471347</v>
+        <v>471160</v>
       </c>
       <c r="R83" t="n">
-        <v>6609455</v>
+        <v>6609566</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10561,17 +10563,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10582,17 +10585,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121703309</v>
+        <v>121699951</v>
       </c>
       <c r="B84" t="n">
-        <v>97087</v>
+        <v>94554</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10605,21 +10608,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10633,10 +10636,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471356</v>
+        <v>471193</v>
       </c>
       <c r="R84" t="n">
-        <v>6609501</v>
+        <v>6609666</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10688,7 +10691,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10699,17 +10702,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121700010</v>
+        <v>121699590</v>
       </c>
       <c r="B85" t="n">
-        <v>92020</v>
+        <v>97094</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10722,34 +10725,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10757,10 +10753,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471160</v>
+        <v>471269</v>
       </c>
       <c r="R85" t="n">
-        <v>6609566</v>
+        <v>6609685</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10807,12 +10803,7 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10830,10 +10821,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121699757</v>
+        <v>121699935</v>
       </c>
       <c r="B86" t="n">
-        <v>94547</v>
+        <v>97094</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10846,21 +10837,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10874,10 +10865,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471208</v>
+        <v>471202</v>
       </c>
       <c r="R86" t="n">
-        <v>6609733</v>
+        <v>6609664</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10922,9 +10913,14 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10935,17 +10931,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121703428</v>
+        <v>121699581</v>
       </c>
       <c r="B87" t="n">
-        <v>94547</v>
+        <v>94554</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10986,10 +10982,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471353</v>
+        <v>471279</v>
       </c>
       <c r="R87" t="n">
-        <v>6609457</v>
+        <v>6609661</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11036,12 +11032,22 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11052,17 +11058,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121703425</v>
+        <v>121703365</v>
       </c>
       <c r="B88" t="n">
-        <v>100399</v>
+        <v>94554</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11075,30 +11081,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -11107,10 +11109,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471353</v>
+        <v>471347</v>
       </c>
       <c r="R88" t="n">
-        <v>6609457</v>
+        <v>6609455</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11151,7 +11153,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11173,17 +11174,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699590</v>
+        <v>121699973</v>
       </c>
       <c r="B89" t="n">
-        <v>97087</v>
+        <v>94554</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11196,21 +11197,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11224,10 +11225,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471269</v>
+        <v>471176</v>
       </c>
       <c r="R89" t="n">
-        <v>6609685</v>
+        <v>6609640</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11274,7 +11275,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11285,17 +11291,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121699973</v>
+        <v>121703399</v>
       </c>
       <c r="B90" t="n">
-        <v>94547</v>
+        <v>100406</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11308,38 +11314,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471176</v>
+        <v>471349</v>
       </c>
       <c r="R90" t="n">
-        <v>6609640</v>
+        <v>6609458</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11386,12 +11400,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11402,17 +11416,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121699679</v>
+        <v>121703368</v>
       </c>
       <c r="B91" t="n">
-        <v>97087</v>
+        <v>91678</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11425,42 +11439,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471222</v>
+        <v>471347</v>
       </c>
       <c r="R91" t="n">
-        <v>6609540</v>
+        <v>6609455</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11501,13 +11510,17 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11518,17 +11531,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121699935</v>
+        <v>121699757</v>
       </c>
       <c r="B92" t="n">
-        <v>97087</v>
+        <v>94554</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11541,21 +11554,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11569,10 +11582,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471202</v>
+        <v>471208</v>
       </c>
       <c r="R92" t="n">
-        <v>6609664</v>
+        <v>6609733</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11617,14 +11630,9 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11635,17 +11643,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121703399</v>
+        <v>121703406</v>
       </c>
       <c r="B93" t="n">
-        <v>100399</v>
+        <v>94554</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11658,36 +11666,28 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
@@ -11760,17 +11760,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121712106</v>
+        <v>121709723</v>
       </c>
       <c r="B94" t="n">
-        <v>94547</v>
+        <v>100406</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11783,26 +11783,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -11811,10 +11815,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471319</v>
+        <v>471351</v>
       </c>
       <c r="R94" t="n">
-        <v>6609597</v>
+        <v>6609528</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11861,12 +11865,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk och klibbal</t>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11877,17 +11881,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121709723</v>
+        <v>121712106</v>
       </c>
       <c r="B95" t="n">
-        <v>100399</v>
+        <v>94554</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11900,30 +11904,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471351</v>
+        <v>471319</v>
       </c>
       <c r="R95" t="n">
-        <v>6609528</v>
+        <v>6609597</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11982,12 +11982,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>V-sluttning</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -9008,10 +9008,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121698324</v>
+        <v>121698315</v>
       </c>
       <c r="B71" t="n">
-        <v>94758</v>
+        <v>97095</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9024,38 +9024,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>210</v>
+        <v>224361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -9119,27 +9107,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9157,10 +9125,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121698287</v>
+        <v>121697845</v>
       </c>
       <c r="B72" t="n">
-        <v>97086</v>
+        <v>74733</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9169,31 +9137,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9201,10 +9172,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471215</v>
+        <v>471285</v>
       </c>
       <c r="R72" t="n">
-        <v>6609537</v>
+        <v>6609641</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9251,12 +9222,32 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9267,17 +9258,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698319</v>
+        <v>121698324</v>
       </c>
       <c r="B73" t="n">
-        <v>100406</v>
+        <v>94767</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9290,28 +9281,36 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -9322,10 +9321,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471316</v>
+        <v>471319</v>
       </c>
       <c r="R73" t="n">
-        <v>6609608</v>
+        <v>6609597</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9369,6 +9368,36 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9385,10 +9414,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698315</v>
+        <v>121698287</v>
       </c>
       <c r="B74" t="n">
-        <v>97086</v>
+        <v>97095</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9429,10 +9458,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471319</v>
+        <v>471215</v>
       </c>
       <c r="R74" t="n">
-        <v>6609597</v>
+        <v>6609537</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9479,12 +9508,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9495,7 +9524,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9505,7 +9534,7 @@
         <v>121698313</v>
       </c>
       <c r="B75" t="n">
-        <v>97086</v>
+        <v>97095</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9619,10 +9648,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121697845</v>
+        <v>121698319</v>
       </c>
       <c r="B76" t="n">
-        <v>74729</v>
+        <v>100415</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9631,34 +9660,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9666,10 +9696,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471285</v>
+        <v>471316</v>
       </c>
       <c r="R76" t="n">
-        <v>6609641</v>
+        <v>6609608</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9713,36 +9743,6 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9759,10 +9759,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121699965</v>
+        <v>121699581</v>
       </c>
       <c r="B77" t="n">
-        <v>94554</v>
+        <v>94563</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471186</v>
+        <v>471279</v>
       </c>
       <c r="R77" t="n">
-        <v>6609658</v>
+        <v>6609661</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9853,12 +9853,22 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9869,17 +9879,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121699679</v>
+        <v>121699935</v>
       </c>
       <c r="B78" t="n">
-        <v>97094</v>
+        <v>97103</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9913,21 +9923,17 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471222</v>
+        <v>471202</v>
       </c>
       <c r="R78" t="n">
-        <v>6609540</v>
+        <v>6609664</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9974,7 +9980,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9985,7 +9996,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9995,7 +10006,7 @@
         <v>121703425</v>
       </c>
       <c r="B79" t="n">
-        <v>100406</v>
+        <v>100415</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10113,10 +10124,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121703311</v>
+        <v>121703406</v>
       </c>
       <c r="B80" t="n">
-        <v>100406</v>
+        <v>94563</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10129,30 +10140,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -10161,10 +10168,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471356</v>
+        <v>471349</v>
       </c>
       <c r="R80" t="n">
-        <v>6609501</v>
+        <v>6609458</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10216,7 +10223,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10227,17 +10234,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703428</v>
+        <v>121703399</v>
       </c>
       <c r="B81" t="n">
-        <v>94554</v>
+        <v>100415</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10250,38 +10257,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471353</v>
+        <v>471349</v>
       </c>
       <c r="R81" t="n">
-        <v>6609457</v>
+        <v>6609458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10344,17 +10359,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703309</v>
+        <v>121703428</v>
       </c>
       <c r="B82" t="n">
-        <v>97094</v>
+        <v>94563</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10367,21 +10382,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10395,10 +10410,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471356</v>
+        <v>471353</v>
       </c>
       <c r="R82" t="n">
-        <v>6609501</v>
+        <v>6609457</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10450,7 +10465,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10461,17 +10476,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121700010</v>
+        <v>121703311</v>
       </c>
       <c r="B83" t="n">
-        <v>92021</v>
+        <v>100415</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10484,34 +10499,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10519,10 +10531,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471160</v>
+        <v>471356</v>
       </c>
       <c r="R83" t="n">
-        <v>6609566</v>
+        <v>6609501</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10569,12 +10581,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10592,10 +10604,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121699951</v>
+        <v>121699590</v>
       </c>
       <c r="B84" t="n">
-        <v>94554</v>
+        <v>97103</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10608,21 +10620,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10636,10 +10648,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471193</v>
+        <v>471269</v>
       </c>
       <c r="R84" t="n">
-        <v>6609666</v>
+        <v>6609685</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10686,12 +10698,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10702,17 +10709,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121699590</v>
+        <v>121699965</v>
       </c>
       <c r="B85" t="n">
-        <v>97094</v>
+        <v>94563</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10725,21 +10732,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10753,10 +10760,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471269</v>
+        <v>471186</v>
       </c>
       <c r="R85" t="n">
-        <v>6609685</v>
+        <v>6609658</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10803,7 +10810,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10814,17 +10826,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121699935</v>
+        <v>121699679</v>
       </c>
       <c r="B86" t="n">
-        <v>97094</v>
+        <v>97103</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10858,17 +10870,21 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471202</v>
+        <v>471222</v>
       </c>
       <c r="R86" t="n">
-        <v>6609664</v>
+        <v>6609540</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10915,12 +10931,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10931,17 +10942,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699581</v>
+        <v>121700010</v>
       </c>
       <c r="B87" t="n">
-        <v>94554</v>
+        <v>92030</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10954,27 +10965,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2813</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10982,10 +11000,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471279</v>
+        <v>471160</v>
       </c>
       <c r="R87" t="n">
-        <v>6609661</v>
+        <v>6609566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11032,22 +11050,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11065,10 +11073,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121703365</v>
+        <v>121699973</v>
       </c>
       <c r="B88" t="n">
-        <v>94554</v>
+        <v>94563</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11109,10 +11117,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471347</v>
+        <v>471176</v>
       </c>
       <c r="R88" t="n">
-        <v>6609455</v>
+        <v>6609640</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11153,17 +11161,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11181,10 +11190,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121699973</v>
+        <v>121703365</v>
       </c>
       <c r="B89" t="n">
-        <v>94554</v>
+        <v>94563</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11225,10 +11234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471176</v>
+        <v>471347</v>
       </c>
       <c r="R89" t="n">
-        <v>6609640</v>
+        <v>6609455</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11269,18 +11278,17 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11298,10 +11306,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121703399</v>
+        <v>121703309</v>
       </c>
       <c r="B90" t="n">
-        <v>100406</v>
+        <v>97103</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11314,46 +11322,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471349</v>
+        <v>471356</v>
       </c>
       <c r="R90" t="n">
-        <v>6609458</v>
+        <v>6609501</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11426,7 +11426,7 @@
         <v>121703368</v>
       </c>
       <c r="B91" t="n">
-        <v>91678</v>
+        <v>91687</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>121699757</v>
       </c>
       <c r="B92" t="n">
-        <v>94554</v>
+        <v>94563</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121703406</v>
+        <v>121699951</v>
       </c>
       <c r="B93" t="n">
-        <v>94554</v>
+        <v>94563</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471349</v>
+        <v>471193</v>
       </c>
       <c r="R93" t="n">
-        <v>6609458</v>
+        <v>6609666</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
         <v>121709723</v>
       </c>
       <c r="B94" t="n">
-        <v>100406</v>
+        <v>100415</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>121712106</v>
       </c>
       <c r="B95" t="n">
-        <v>94554</v>
+        <v>94563</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>100800458</v>
+        <v>95956816</v>
       </c>
       <c r="B23" t="n">
-        <v>93235</v>
+        <v>90319</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3238,34 +3238,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tebroängen, nära vägen, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471204.9560386189</v>
+        <v>471149.7398765656</v>
       </c>
       <c r="R23" t="n">
-        <v>6609730.638476647</v>
+        <v>6609733.086802785</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3321,25 +3321,29 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granskog nära vägen</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95956816</v>
+        <v>95956812</v>
       </c>
       <c r="B24" t="n">
         <v>90319</v>
@@ -3379,10 +3383,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471149.7398765656</v>
+        <v>471224.6511069508</v>
       </c>
       <c r="R24" t="n">
-        <v>6609733.086802785</v>
+        <v>6609589.852244456</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3460,7 +3464,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95956812</v>
+        <v>96251799</v>
       </c>
       <c r="B25" t="n">
         <v>90319</v>
@@ -3500,13 +3504,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471224.6511069508</v>
+        <v>471259.4027788527</v>
       </c>
       <c r="R25" t="n">
-        <v>6609589.852244456</v>
+        <v>6609429.72073366</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3530,7 +3534,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3540,7 +3544,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3559,7 +3563,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig blandskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3581,10 +3585,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96251799</v>
+        <v>96252447</v>
       </c>
       <c r="B26" t="n">
-        <v>90319</v>
+        <v>88953</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3593,38 +3597,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>5754</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471259.4027788527</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R26" t="n">
-        <v>6609429.72073366</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3680,7 +3693,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>fuktig blandskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3702,14 +3715,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96252447</v>
+        <v>95956831</v>
       </c>
       <c r="B27" t="n">
-        <v>88953</v>
+        <v>57308</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3718,46 +3731,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5754</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471259.8086330662</v>
+        <v>471225</v>
       </c>
       <c r="R27" t="n">
-        <v>6609416.56388958</v>
+        <v>6609590</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3781,22 +3785,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3810,7 +3804,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3832,37 +3826,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95956831</v>
+        <v>95956815</v>
       </c>
       <c r="B28" t="n">
-        <v>57308</v>
+        <v>90319</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3872,10 +3866,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471225</v>
+        <v>471178.5493512115</v>
       </c>
       <c r="R28" t="n">
-        <v>6609590</v>
+        <v>6609657.489466893</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3905,9 +3899,19 @@
           <t>2021-09-06</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3943,10 +3947,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95956815</v>
+        <v>96251636</v>
       </c>
       <c r="B29" t="n">
-        <v>90319</v>
+        <v>99398</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3959,21 +3963,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3983,13 +3987,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471178.5493512115</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R29" t="n">
-        <v>6609657.489466893</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4013,7 +4017,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4023,7 +4027,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4042,7 +4046,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4064,7 +4068,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96251636</v>
+        <v>96251635</v>
       </c>
       <c r="B30" t="n">
         <v>99398</v>
@@ -4104,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471309.9309650694</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R30" t="n">
-        <v>6609410.108756405</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4185,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96251635</v>
+        <v>95972655</v>
       </c>
       <c r="B31" t="n">
-        <v>99398</v>
+        <v>89652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4197,25 +4201,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>73</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4225,13 +4229,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471259.8086330662</v>
+        <v>471296.9326695912</v>
       </c>
       <c r="R31" t="n">
-        <v>6609416.56388958</v>
+        <v>6609631.792281208</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4255,7 +4259,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4265,7 +4269,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4284,7 +4288,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4306,10 +4310,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>95972655</v>
+        <v>96251810</v>
       </c>
       <c r="B32" t="n">
-        <v>89652</v>
+        <v>90319</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4318,25 +4322,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>73</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4346,13 +4350,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471296.9326695912</v>
+        <v>471318.0003416255</v>
       </c>
       <c r="R32" t="n">
-        <v>6609631.792281208</v>
+        <v>6609404.987824169</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4376,7 +4380,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4386,7 +4390,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4405,7 +4409,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4427,10 +4431,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96251810</v>
+        <v>96251752</v>
       </c>
       <c r="B33" t="n">
-        <v>90319</v>
+        <v>101680</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4443,21 +4447,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4467,10 +4471,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471318.0003416255</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R33" t="n">
-        <v>6609404.987824169</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4548,10 +4552,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96251752</v>
+        <v>96251807</v>
       </c>
       <c r="B34" t="n">
-        <v>101680</v>
+        <v>90319</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4564,21 +4568,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4588,10 +4592,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471259.8086330662</v>
+        <v>471247.6348481966</v>
       </c>
       <c r="R34" t="n">
-        <v>6609416.56388958</v>
+        <v>6609415.139556407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4669,10 +4673,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96251807</v>
+        <v>96251672</v>
       </c>
       <c r="B35" t="n">
-        <v>90319</v>
+        <v>101120</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4685,21 +4689,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>222002</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4709,10 +4713,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471247.6348481966</v>
+        <v>471368.0221119327</v>
       </c>
       <c r="R35" t="n">
-        <v>6609415.139556407</v>
+        <v>6609451.655002752</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4768,7 +4772,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4790,10 +4794,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96251672</v>
+        <v>95956813</v>
       </c>
       <c r="B36" t="n">
-        <v>101120</v>
+        <v>90319</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4806,21 +4810,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4830,13 +4834,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471368.0221119327</v>
+        <v>471211.8506313803</v>
       </c>
       <c r="R36" t="n">
-        <v>6609451.655002752</v>
+        <v>6609572.750275725</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4860,7 +4864,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4870,7 +4874,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4889,7 +4893,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4911,10 +4915,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95956813</v>
+        <v>96251671</v>
       </c>
       <c r="B37" t="n">
-        <v>90319</v>
+        <v>101120</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4927,21 +4931,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>222002</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4951,13 +4955,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471211.8506313803</v>
+        <v>471313.2387810608</v>
       </c>
       <c r="R37" t="n">
-        <v>6609572.750275725</v>
+        <v>6609444.991354768</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4981,7 +4985,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4991,7 +4995,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5010,7 +5014,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5032,7 +5036,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96251671</v>
+        <v>96251670</v>
       </c>
       <c r="B38" t="n">
         <v>101120</v>
@@ -5072,10 +5076,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471313.2387810608</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R38" t="n">
-        <v>6609444.991354768</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5131,7 +5135,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5153,10 +5157,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96251670</v>
+        <v>96251798</v>
       </c>
       <c r="B39" t="n">
-        <v>101120</v>
+        <v>90319</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5169,21 +5173,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5193,10 +5197,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471309.9309650694</v>
+        <v>471148.7887846382</v>
       </c>
       <c r="R39" t="n">
-        <v>6609410.108756405</v>
+        <v>6609741.188059531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5252,7 +5256,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5274,7 +5278,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96251798</v>
+        <v>96251808</v>
       </c>
       <c r="B40" t="n">
         <v>90319</v>
@@ -5314,10 +5318,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471148.7887846382</v>
+        <v>471259.8086330662</v>
       </c>
       <c r="R40" t="n">
-        <v>6609741.188059531</v>
+        <v>6609416.56388958</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5377,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5395,7 +5399,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96251808</v>
+        <v>95956814</v>
       </c>
       <c r="B41" t="n">
         <v>90319</v>
@@ -5435,13 +5439,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471259.8086330662</v>
+        <v>471202.4547789301</v>
       </c>
       <c r="R41" t="n">
-        <v>6609416.56388958</v>
+        <v>6609668.940877154</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5465,7 +5469,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5475,7 +5479,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5494,7 +5498,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5516,7 +5520,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95956814</v>
+        <v>96251812</v>
       </c>
       <c r="B42" t="n">
         <v>90319</v>
@@ -5556,13 +5560,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471202.4547789301</v>
+        <v>471368.0221119327</v>
       </c>
       <c r="R42" t="n">
-        <v>6609668.940877154</v>
+        <v>6609451.655002752</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5586,7 +5590,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5596,7 +5600,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5615,7 +5619,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5637,10 +5641,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96251812</v>
+        <v>96251753</v>
       </c>
       <c r="B43" t="n">
-        <v>90319</v>
+        <v>101680</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5653,21 +5657,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5677,10 +5681,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471368.0221119327</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R43" t="n">
-        <v>6609451.655002752</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5736,7 +5740,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5758,10 +5762,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96251753</v>
+        <v>96252446</v>
       </c>
       <c r="B44" t="n">
-        <v>101680</v>
+        <v>88953</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5770,25 +5774,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>5754</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5798,10 +5802,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471309.9309650694</v>
+        <v>471269.1746462852</v>
       </c>
       <c r="R44" t="n">
-        <v>6609410.108756405</v>
+        <v>6609448.364473196</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5857,7 +5861,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5879,10 +5883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96252446</v>
+        <v>96252613</v>
       </c>
       <c r="B45" t="n">
-        <v>88953</v>
+        <v>90671</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5895,21 +5899,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5919,10 +5923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471269.1746462852</v>
+        <v>471340.9286586023</v>
       </c>
       <c r="R45" t="n">
-        <v>6609448.364473196</v>
+        <v>6609553.54842629</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5978,7 +5982,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6000,7 +6004,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96252613</v>
+        <v>95956974</v>
       </c>
       <c r="B46" t="n">
         <v>90671</v>
@@ -6033,20 +6037,29 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471340.9286586023</v>
+        <v>471224.6511069508</v>
       </c>
       <c r="R46" t="n">
-        <v>6609553.54842629</v>
+        <v>6609589.852244456</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6070,7 +6083,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6080,7 +6093,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6099,7 +6112,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6121,10 +6134,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>95956974</v>
+        <v>96251811</v>
       </c>
       <c r="B47" t="n">
-        <v>90671</v>
+        <v>90319</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6133,50 +6146,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471224.6511069508</v>
+        <v>471313.2387810608</v>
       </c>
       <c r="R47" t="n">
-        <v>6609589.852244456</v>
+        <v>6609444.991354768</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6200,7 +6204,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6210,7 +6214,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6229,7 +6233,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6251,10 +6255,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96251811</v>
+        <v>96251948</v>
       </c>
       <c r="B48" t="n">
-        <v>90319</v>
+        <v>100515</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6263,25 +6267,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>223246</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6291,10 +6295,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471313.2387810608</v>
+        <v>471259.4027788527</v>
       </c>
       <c r="R48" t="n">
-        <v>6609444.991354768</v>
+        <v>6609429.72073366</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6350,7 +6354,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>fuktig blandskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6372,10 +6376,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96251948</v>
+        <v>96251809</v>
       </c>
       <c r="B49" t="n">
-        <v>100515</v>
+        <v>90319</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6384,25 +6388,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223246</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6412,10 +6416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471259.4027788527</v>
+        <v>471309.9309650694</v>
       </c>
       <c r="R49" t="n">
-        <v>6609429.72073366</v>
+        <v>6609410.108756405</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6471,7 +6475,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>fuktig blandskog</t>
+          <t>barrblandskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6493,10 +6497,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96251809</v>
+        <v>87904463</v>
       </c>
       <c r="B50" t="n">
-        <v>90319</v>
+        <v>98431</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6509,21 +6513,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6533,13 +6537,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>471309.9309650694</v>
+        <v>471339.6404136405</v>
       </c>
       <c r="R50" t="n">
-        <v>6609410.108756405</v>
+        <v>6609517.639566744</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6563,7 +6567,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6573,7 +6577,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -6592,7 +6596,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>källpåverkad granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6614,10 +6618,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>87904463</v>
+        <v>87904428</v>
       </c>
       <c r="B51" t="n">
-        <v>98431</v>
+        <v>95521</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6630,23 +6634,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222771</v>
+        <v>224363</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>471339.6404136405</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R51" t="n">
-        <v>6609517.639566744</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>källpåverkad granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>87904428</v>
+        <v>87904488</v>
       </c>
       <c r="B52" t="n">
-        <v>95521</v>
+        <v>96313</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6751,16 +6751,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>224363</v>
+        <v>223609</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Epipactis helleborine subsp. helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -6825,6 +6825,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6852,10 +6853,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>87904488</v>
+        <v>87904660</v>
       </c>
       <c r="B53" t="n">
-        <v>96313</v>
+        <v>98520</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6868,19 +6869,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223609</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6888,10 +6893,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471315.03151316</v>
+        <v>471246.9145555807</v>
       </c>
       <c r="R53" t="n">
-        <v>6609612.935878632</v>
+        <v>6609387.319721107</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6942,13 +6947,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6970,10 +6974,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>87904660</v>
+        <v>87904436</v>
       </c>
       <c r="B54" t="n">
-        <v>98520</v>
+        <v>95514</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6986,23 +6990,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig lopplummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago subsp. selago</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471246.9145555807</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R54" t="n">
-        <v>6609387.319721107</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>örtrik sumpskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,10 +7091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>87904436</v>
+        <v>88202319</v>
       </c>
       <c r="B55" t="n">
-        <v>95514</v>
+        <v>94653</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7107,19 +7107,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>224361</v>
+        <v>2563</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vanlig lopplummer</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Huperzia selago subsp. selago</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Geocalyx graveolens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schrad.) Nees</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7127,10 +7131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471315.03151316</v>
+        <v>471321.5221799276</v>
       </c>
       <c r="R55" t="n">
-        <v>6609612.935878632</v>
+        <v>6609600.238987684</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7157,7 +7161,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7167,7 +7171,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7186,7 +7190,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>sumpig granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7212,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>88202319</v>
+        <v>87904450</v>
       </c>
       <c r="B56" t="n">
-        <v>94653</v>
+        <v>101680</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7224,21 +7228,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2563</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7248,10 +7252,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>471321.5221799276</v>
+        <v>471200.7479510409</v>
       </c>
       <c r="R56" t="n">
-        <v>6609600.238987684</v>
+        <v>6609644.671690273</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7278,7 +7282,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7288,7 +7292,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7307,7 +7311,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>sumpig granskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7329,7 +7333,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>87904450</v>
+        <v>87904451</v>
       </c>
       <c r="B57" t="n">
         <v>101680</v>
@@ -7369,10 +7373,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471200.7479510409</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R57" t="n">
-        <v>6609644.671690273</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7450,10 +7454,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>87904451</v>
+        <v>87904658</v>
       </c>
       <c r="B58" t="n">
-        <v>101680</v>
+        <v>98520</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7466,21 +7470,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7490,10 +7494,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471262.8491675095</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R58" t="n">
-        <v>6609416.540566096</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7571,7 +7575,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>87904658</v>
+        <v>87904659</v>
       </c>
       <c r="B59" t="n">
         <v>98520</v>
@@ -7611,10 +7615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471315.03151316</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R59" t="n">
-        <v>6609612.935878632</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7692,10 +7696,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>87904659</v>
+        <v>88202411</v>
       </c>
       <c r="B60" t="n">
-        <v>98520</v>
+        <v>95521</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7708,23 +7712,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>471262.8491675095</v>
+        <v>471150.8234233134</v>
       </c>
       <c r="R60" t="n">
-        <v>6609416.540566096</v>
+        <v>6609742.184129979</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7813,10 +7813,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>88202411</v>
+        <v>87904409</v>
       </c>
       <c r="B61" t="n">
-        <v>95521</v>
+        <v>99398</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7829,19 +7829,23 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>224363</v>
+        <v>221235</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7849,10 +7853,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471150.8234233134</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R61" t="n">
-        <v>6609742.184129979</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7879,7 +7883,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -7889,7 +7893,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,10 +7934,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>87904409</v>
+        <v>87904430</v>
       </c>
       <c r="B62" t="n">
-        <v>99398</v>
+        <v>95521</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7946,23 +7950,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>224363</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471262.8491675095</v>
+        <v>471200.7479510409</v>
       </c>
       <c r="R62" t="n">
-        <v>6609416.540566096</v>
+        <v>6609644.671690273</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>87904430</v>
+        <v>87904452</v>
       </c>
       <c r="B63" t="n">
-        <v>95521</v>
+        <v>101680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8067,19 +8067,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>224363</v>
+        <v>222412</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8087,10 +8091,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471200.7479510409</v>
+        <v>471246.9145555807</v>
       </c>
       <c r="R63" t="n">
-        <v>6609644.671690273</v>
+        <v>6609387.319721107</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8146,7 +8150,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8168,10 +8172,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>87904452</v>
+        <v>88202399</v>
       </c>
       <c r="B64" t="n">
-        <v>101680</v>
+        <v>96251</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8184,21 +8188,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8208,10 +8212,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471246.9145555807</v>
+        <v>471150.8234233134</v>
       </c>
       <c r="R64" t="n">
-        <v>6609387.319721107</v>
+        <v>6609742.184129979</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8238,7 +8242,7 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8248,7 +8252,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -8267,7 +8271,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>örtrik sumpskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8289,10 +8293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>88202399</v>
+        <v>87904440</v>
       </c>
       <c r="B65" t="n">
-        <v>96251</v>
+        <v>101120</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8305,21 +8309,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>222002</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8329,10 +8333,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471150.8234233134</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R65" t="n">
-        <v>6609742.184129979</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8359,7 +8363,7 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -8369,7 +8373,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -8388,7 +8392,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8410,10 +8414,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>87904440</v>
+        <v>87904429</v>
       </c>
       <c r="B66" t="n">
-        <v>101120</v>
+        <v>95521</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8426,23 +8430,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222002</v>
+        <v>224363</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471262.8491675095</v>
+        <v>471261.6791215731</v>
       </c>
       <c r="R66" t="n">
-        <v>6609416.540566096</v>
+        <v>6609660.391988517</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>87904429</v>
+        <v>87904408</v>
       </c>
       <c r="B67" t="n">
-        <v>95521</v>
+        <v>99398</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8547,19 +8547,23 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224363</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8567,10 +8571,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471261.6791215731</v>
+        <v>471315.03151316</v>
       </c>
       <c r="R67" t="n">
-        <v>6609660.391988517</v>
+        <v>6609612.935878632</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8648,10 +8652,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>87904408</v>
+        <v>87904464</v>
       </c>
       <c r="B68" t="n">
-        <v>99398</v>
+        <v>98431</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8664,21 +8668,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8688,10 +8692,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471315.03151316</v>
+        <v>471262.8491675095</v>
       </c>
       <c r="R68" t="n">
-        <v>6609612.935878632</v>
+        <v>6609416.540566096</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8769,10 +8773,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>87904464</v>
+        <v>88202343</v>
       </c>
       <c r="B69" t="n">
-        <v>98431</v>
+        <v>96313</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8785,23 +8789,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222771</v>
+        <v>223609</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8809,10 +8809,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471262.8491675095</v>
+        <v>471288.2950552536</v>
       </c>
       <c r="R69" t="n">
-        <v>6609416.540566096</v>
+        <v>6609628.823163424</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -8863,12 +8863,13 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8890,10 +8891,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>88202343</v>
+        <v>121698315</v>
       </c>
       <c r="B70" t="n">
-        <v>96313</v>
+        <v>97095</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8906,33 +8907,41 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223609</v>
+        <v>224361</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471288.2950552536</v>
+        <v>471319</v>
       </c>
       <c r="R70" t="n">
-        <v>6609628.823163424</v>
+        <v>6609597</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8956,22 +8965,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8984,34 +8983,35 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>fuktig barrskog</t>
+          <t>gammal olikåldrig sumpskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121698315</v>
+        <v>121697845</v>
       </c>
       <c r="B71" t="n">
-        <v>97095</v>
+        <v>74733</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9020,31 +9020,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>224361</v>
+        <v>308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9052,10 +9055,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471319</v>
+        <v>471285</v>
       </c>
       <c r="R71" t="n">
-        <v>6609597</v>
+        <v>6609641</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9107,7 +9110,27 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>gammal olikåldrig sumpskog</t>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9125,10 +9148,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121697845</v>
+        <v>121698324</v>
       </c>
       <c r="B72" t="n">
-        <v>74733</v>
+        <v>94767</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9137,34 +9160,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9172,10 +9204,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471285</v>
+        <v>471319</v>
       </c>
       <c r="R72" t="n">
-        <v>6609641</v>
+        <v>6609597</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9242,12 +9274,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # grov, några meter hög högstubbe # Betula pubescens</t>
+          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9265,10 +9297,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121698324</v>
+        <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>94767</v>
+        <v>97095</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9281,38 +9313,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>210</v>
+        <v>224361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9321,10 +9341,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471319</v>
+        <v>471215</v>
       </c>
       <c r="R73" t="n">
-        <v>6609597</v>
+        <v>6609537</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9371,32 +9391,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # starkt murken låga # Betula pubescens</t>
+          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9407,14 +9407,14 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121698287</v>
+        <v>121698313</v>
       </c>
       <c r="B74" t="n">
         <v>97095</v>
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471215</v>
+        <v>471329</v>
       </c>
       <c r="R74" t="n">
-        <v>6609537</v>
+        <v>6609593</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9508,12 +9508,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Granskog i branter</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>olikåldrig gammal sumpskog av gran, klibbal och glasbjörk</t>
+          <t>grov granskog i V-sluttning</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9531,10 +9531,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121698313</v>
+        <v>121698319</v>
       </c>
       <c r="B75" t="n">
-        <v>97095</v>
+        <v>100415</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9547,26 +9547,30 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9575,10 +9579,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471329</v>
+        <v>471316</v>
       </c>
       <c r="R75" t="n">
-        <v>6609593</v>
+        <v>6609608</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9623,16 +9627,6 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog i branter</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>grov granskog i V-sluttning</t>
-        </is>
-      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
@@ -9641,17 +9635,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121698319</v>
+        <v>121699581</v>
       </c>
       <c r="B76" t="n">
-        <v>100415</v>
+        <v>94563</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9664,30 +9658,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -9696,10 +9686,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471316</v>
+        <v>471279</v>
       </c>
       <c r="R76" t="n">
-        <v>6609608</v>
+        <v>6609661</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9743,6 +9733,26 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9759,10 +9769,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121699581</v>
+        <v>121699935</v>
       </c>
       <c r="B77" t="n">
-        <v>94563</v>
+        <v>97103</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9775,21 +9785,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9803,10 +9813,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471279</v>
+        <v>471202</v>
       </c>
       <c r="R77" t="n">
-        <v>6609661</v>
+        <v>6609664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9853,22 +9863,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>med inslag av glasbjörk</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
+          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121699935</v>
+        <v>121703425</v>
       </c>
       <c r="B78" t="n">
-        <v>97103</v>
+        <v>100415</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9902,26 +9902,30 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -9930,10 +9934,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471202</v>
+        <v>471353</v>
       </c>
       <c r="R78" t="n">
-        <v>6609664</v>
+        <v>6609457</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9985,7 +9989,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>intill gammal stig mot kolarkoja och intill surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10003,10 +10007,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121703425</v>
+        <v>121703406</v>
       </c>
       <c r="B79" t="n">
-        <v>100415</v>
+        <v>94563</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10019,30 +10023,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471353</v>
+        <v>471349</v>
       </c>
       <c r="R79" t="n">
-        <v>6609457</v>
+        <v>6609458</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10117,17 +10117,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121703406</v>
+        <v>121703399</v>
       </c>
       <c r="B80" t="n">
-        <v>94563</v>
+        <v>100415</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10140,28 +10140,36 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
@@ -10234,14 +10242,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121703399</v>
+        <v>121703311</v>
       </c>
       <c r="B81" t="n">
         <v>100415</v>
@@ -10282,21 +10290,17 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471349</v>
+        <v>471356</v>
       </c>
       <c r="R81" t="n">
-        <v>6609458</v>
+        <v>6609501</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10348,7 +10352,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10366,10 +10370,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121703311</v>
+        <v>121699590</v>
       </c>
       <c r="B82" t="n">
-        <v>100415</v>
+        <v>97103</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10382,30 +10386,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471356</v>
+        <v>471269</v>
       </c>
       <c r="R82" t="n">
-        <v>6609501</v>
+        <v>6609685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10464,12 +10464,7 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10487,10 +10482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121699590</v>
+        <v>121703428</v>
       </c>
       <c r="B83" t="n">
-        <v>97103</v>
+        <v>94563</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10503,21 +10498,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10531,10 +10526,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471269</v>
+        <v>471353</v>
       </c>
       <c r="R83" t="n">
-        <v>6609685</v>
+        <v>6609457</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10581,7 +10576,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10592,17 +10592,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121703428</v>
+        <v>121700010</v>
       </c>
       <c r="B84" t="n">
-        <v>94563</v>
+        <v>92030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10615,27 +10615,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2813</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10643,10 +10650,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471353</v>
+        <v>471160</v>
       </c>
       <c r="R84" t="n">
-        <v>6609457</v>
+        <v>6609566</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10693,12 +10700,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10709,17 +10716,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121700010</v>
+        <v>121699965</v>
       </c>
       <c r="B85" t="n">
-        <v>92030</v>
+        <v>94563</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10732,34 +10739,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>2813</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471160</v>
+        <v>471186</v>
       </c>
       <c r="R85" t="n">
-        <v>6609566</v>
+        <v>6609658</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10817,12 +10817,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10833,17 +10833,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121699965</v>
+        <v>121699679</v>
       </c>
       <c r="B86" t="n">
-        <v>94563</v>
+        <v>97103</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10856,38 +10856,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471186</v>
+        <v>471222</v>
       </c>
       <c r="R86" t="n">
-        <v>6609658</v>
+        <v>6609540</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10934,12 +10938,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>surdråg</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10957,10 +10956,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121699679</v>
+        <v>121699973</v>
       </c>
       <c r="B87" t="n">
-        <v>97103</v>
+        <v>94563</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10973,42 +10972,38 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471222</v>
+        <v>471176</v>
       </c>
       <c r="R87" t="n">
-        <v>6609540</v>
+        <v>6609640</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11055,7 +11050,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121699973</v>
+        <v>121703365</v>
       </c>
       <c r="B88" t="n">
         <v>94563</v>
@@ -11117,10 +11117,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471176</v>
+        <v>471347</v>
       </c>
       <c r="R88" t="n">
-        <v>6609640</v>
+        <v>6609455</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11161,18 +11161,17 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11190,10 +11189,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121703365</v>
+        <v>121703309</v>
       </c>
       <c r="B89" t="n">
-        <v>94563</v>
+        <v>97103</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11206,21 +11205,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11234,10 +11233,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471347</v>
+        <v>471356</v>
       </c>
       <c r="R89" t="n">
-        <v>6609455</v>
+        <v>6609501</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11278,6 +11277,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11299,17 +11299,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121703309</v>
+        <v>121703368</v>
       </c>
       <c r="B90" t="n">
-        <v>97103</v>
+        <v>91687</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11322,27 +11322,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11350,10 +11349,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471356</v>
+        <v>471347</v>
       </c>
       <c r="R90" t="n">
-        <v>6609501</v>
+        <v>6609455</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11394,7 +11393,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11405,7 +11403,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog i dalbotten</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11423,10 +11421,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121703368</v>
+        <v>121699757</v>
       </c>
       <c r="B91" t="n">
-        <v>91687</v>
+        <v>94563</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11439,26 +11437,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11466,10 +11465,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471347</v>
+        <v>471208</v>
       </c>
       <c r="R91" t="n">
-        <v>6609455</v>
+        <v>6609733</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11510,17 +11509,13 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>kalkgranskog i dalbotten</t>
+          <t>svämzon längs bäck/surdråg</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11531,14 +11526,14 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121699757</v>
+        <v>121699951</v>
       </c>
       <c r="B92" t="n">
         <v>94563</v>
@@ -11582,10 +11577,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471208</v>
+        <v>471193</v>
       </c>
       <c r="R92" t="n">
-        <v>6609733</v>
+        <v>6609666</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11630,9 +11625,14 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>svämzon längs bäck/surdråg</t>
+          <t>surdråg</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121699951</v>
+        <v>121709723</v>
       </c>
       <c r="B93" t="n">
-        <v>94563</v>
+        <v>100415</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11666,26 +11666,30 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -11694,10 +11698,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471193</v>
+        <v>471351</v>
       </c>
       <c r="R93" t="n">
-        <v>6609666</v>
+        <v>6609528</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11749,7 +11753,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>surdråg</t>
+          <t>V-sluttning</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11760,17 +11764,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Josefina Jansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121709723</v>
+        <v>121712106</v>
       </c>
       <c r="B94" t="n">
-        <v>100415</v>
+        <v>94563</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11783,30 +11787,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471351</v>
+        <v>471319</v>
       </c>
       <c r="R94" t="n">
-        <v>6609528</v>
+        <v>6609597</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11865,12 +11865,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>V-sluttning</t>
+          <t>med inslag av glasbjörk och klibbal</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11881,127 +11881,10 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michael Andersson, Josefina Jansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>121712106</v>
-      </c>
-      <c r="B95" t="n">
-        <v>94563</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>2813</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Rhytidiadelphus subpinnatus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>471319</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6609597</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Hällefors</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Grythyttan</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>med inslag av glasbjörk och klibbal</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11886,6 +11886,135 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>124860280</v>
+      </c>
+      <c r="B95" t="n">
+        <v>103528</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>471180</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6609743</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>invid bäck</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12015,6 +12015,148 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>125131092</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>471296</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6609358</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12157,6 +12157,1267 @@
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>125151027</v>
+      </c>
+      <c r="B97" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>471342</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6609418</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>125148997</v>
+      </c>
+      <c r="B98" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>471337</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6609424</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>125148993</v>
+      </c>
+      <c r="B99" t="n">
+        <v>101183</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>471337</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6609424</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>125151358</v>
+      </c>
+      <c r="B100" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>471434</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6609505</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>125151077</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>471343</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6609410</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>125151014</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101183</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>471342</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6609418</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>125151113</v>
+      </c>
+      <c r="B103" t="n">
+        <v>106461</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>471438</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6609330</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>125150908</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57847</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>471387</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6609362</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>125151256</v>
+      </c>
+      <c r="B105" t="n">
+        <v>102326</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>471433</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6609506</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>125151055</v>
+      </c>
+      <c r="B106" t="n">
+        <v>101183</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>471343</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6609410</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -12159,10 +12159,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151027</v>
+        <v>125151113</v>
       </c>
       <c r="B97" t="n">
-        <v>100279</v>
+        <v>106461</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12175,28 +12175,36 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12207,10 +12215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471342</v>
+        <v>471438</v>
       </c>
       <c r="R97" t="n">
-        <v>6609418</v>
+        <v>6609330</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12280,10 +12288,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125148997</v>
+        <v>125148993</v>
       </c>
       <c r="B98" t="n">
-        <v>100188</v>
+        <v>101183</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12296,26 +12304,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12325,7 +12333,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -12409,10 +12417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125148993</v>
+        <v>125151077</v>
       </c>
       <c r="B99" t="n">
-        <v>101183</v>
+        <v>100279</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12425,36 +12433,28 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12465,10 +12465,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471337</v>
+        <v>471343</v>
       </c>
       <c r="R99" t="n">
-        <v>6609424</v>
+        <v>6609410</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12538,7 +12538,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125151358</v>
+        <v>125148997</v>
       </c>
       <c r="B100" t="n">
         <v>100188</v>
@@ -12594,10 +12594,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471434</v>
+        <v>471337</v>
       </c>
       <c r="R100" t="n">
-        <v>6609505</v>
+        <v>6609424</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12641,6 +12641,16 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12657,10 +12667,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125151077</v>
+        <v>125151014</v>
       </c>
       <c r="B101" t="n">
-        <v>100279</v>
+        <v>101183</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12673,28 +12683,36 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -12705,10 +12723,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471343</v>
+        <v>471342</v>
       </c>
       <c r="R101" t="n">
-        <v>6609410</v>
+        <v>6609418</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12778,10 +12796,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125151014</v>
+        <v>125151358</v>
       </c>
       <c r="B102" t="n">
-        <v>101183</v>
+        <v>100188</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12794,26 +12812,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12823,7 +12841,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12834,10 +12852,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471342</v>
+        <v>471434</v>
       </c>
       <c r="R102" t="n">
-        <v>6609418</v>
+        <v>6609505</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12881,16 +12899,6 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12907,10 +12915,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151113</v>
+        <v>125151055</v>
       </c>
       <c r="B103" t="n">
-        <v>106461</v>
+        <v>101183</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12923,26 +12931,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12963,10 +12971,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471438</v>
+        <v>471343</v>
       </c>
       <c r="R103" t="n">
-        <v>6609330</v>
+        <v>6609410</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13036,10 +13044,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125150908</v>
+        <v>125151256</v>
       </c>
       <c r="B104" t="n">
-        <v>57847</v>
+        <v>102326</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13048,62 +13056,54 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103008</v>
+        <v>223246</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471387</v>
+        <v>471433</v>
       </c>
       <c r="R104" t="n">
-        <v>6609362</v>
+        <v>6609506</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13133,27 +13133,18 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13172,10 +13163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125151256</v>
+        <v>125151027</v>
       </c>
       <c r="B105" t="n">
-        <v>102326</v>
+        <v>100279</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13184,40 +13175,32 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -13228,10 +13211,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471433</v>
+        <v>471342</v>
       </c>
       <c r="R105" t="n">
-        <v>6609506</v>
+        <v>6609418</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13275,6 +13258,16 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -13291,10 +13284,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125151055</v>
+        <v>125150908</v>
       </c>
       <c r="B106" t="n">
-        <v>101183</v>
+        <v>57847</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13303,54 +13296,62 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221235</v>
+        <v>103008</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471343</v>
+        <v>471387</v>
       </c>
       <c r="R106" t="n">
-        <v>6609410</v>
+        <v>6609362</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13380,30 +13381,29 @@
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12159,10 +12159,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151113</v>
+        <v>125148993</v>
       </c>
       <c r="B97" t="n">
-        <v>106461</v>
+        <v>101183</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12175,26 +12175,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12215,10 +12215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471438</v>
+        <v>471337</v>
       </c>
       <c r="R97" t="n">
-        <v>6609330</v>
+        <v>6609424</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12288,10 +12288,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125148993</v>
+        <v>125151113</v>
       </c>
       <c r="B98" t="n">
-        <v>101183</v>
+        <v>106461</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12304,26 +12304,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221235</v>
+        <v>219686</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471337</v>
+        <v>471438</v>
       </c>
       <c r="R98" t="n">
-        <v>6609424</v>
+        <v>6609330</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13418,6 +13418,118 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>125251985</v>
+      </c>
+      <c r="B107" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Tebroängen, Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>471300</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6609443</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -12159,10 +12159,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125148993</v>
+        <v>125151027</v>
       </c>
       <c r="B97" t="n">
-        <v>101183</v>
+        <v>100279</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12175,36 +12175,28 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12215,10 +12207,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471337</v>
+        <v>471342</v>
       </c>
       <c r="R97" t="n">
-        <v>6609424</v>
+        <v>6609418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12288,10 +12280,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125151113</v>
+        <v>125148997</v>
       </c>
       <c r="B98" t="n">
-        <v>106461</v>
+        <v>100188</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12304,16 +12296,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219686</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -12323,7 +12315,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12333,7 +12325,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -12344,10 +12336,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471438</v>
+        <v>471337</v>
       </c>
       <c r="R98" t="n">
-        <v>6609330</v>
+        <v>6609424</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12417,10 +12409,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125151077</v>
+        <v>125148993</v>
       </c>
       <c r="B99" t="n">
-        <v>100279</v>
+        <v>101183</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12433,28 +12425,36 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12465,10 +12465,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471343</v>
+        <v>471337</v>
       </c>
       <c r="R99" t="n">
-        <v>6609410</v>
+        <v>6609424</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12538,10 +12538,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125148997</v>
+        <v>125151077</v>
       </c>
       <c r="B100" t="n">
-        <v>100188</v>
+        <v>100279</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12554,33 +12554,25 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12594,10 +12586,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471337</v>
+        <v>471343</v>
       </c>
       <c r="R100" t="n">
-        <v>6609424</v>
+        <v>6609410</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12796,10 +12788,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125151358</v>
+        <v>125151113</v>
       </c>
       <c r="B102" t="n">
-        <v>100188</v>
+        <v>106461</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12812,16 +12804,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>219686</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -12831,7 +12823,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12841,7 +12833,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12852,10 +12844,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471434</v>
+        <v>471438</v>
       </c>
       <c r="R102" t="n">
-        <v>6609505</v>
+        <v>6609330</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12899,6 +12891,16 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12915,10 +12917,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151055</v>
+        <v>125151256</v>
       </c>
       <c r="B103" t="n">
-        <v>101183</v>
+        <v>102326</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12927,30 +12929,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221235</v>
+        <v>223246</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12960,7 +12962,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12971,10 +12973,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471343</v>
+        <v>471433</v>
       </c>
       <c r="R103" t="n">
-        <v>6609410</v>
+        <v>6609506</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13018,16 +13020,6 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13044,10 +13036,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125151256</v>
+        <v>125150908</v>
       </c>
       <c r="B104" t="n">
-        <v>102326</v>
+        <v>57847</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13056,54 +13048,62 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>223246</v>
+        <v>103008</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471433</v>
+        <v>471387</v>
       </c>
       <c r="R104" t="n">
-        <v>6609506</v>
+        <v>6609362</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13133,18 +13133,27 @@
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13163,10 +13172,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125151027</v>
+        <v>125151055</v>
       </c>
       <c r="B105" t="n">
-        <v>100279</v>
+        <v>101183</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13179,28 +13188,36 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -13211,10 +13228,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471342</v>
+        <v>471343</v>
       </c>
       <c r="R105" t="n">
-        <v>6609418</v>
+        <v>6609410</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13284,10 +13301,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125150908</v>
+        <v>125151358</v>
       </c>
       <c r="B106" t="n">
-        <v>57847</v>
+        <v>100188</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13296,62 +13313,54 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103008</v>
+        <v>222771</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471387</v>
+        <v>471434</v>
       </c>
       <c r="R106" t="n">
-        <v>6609362</v>
+        <v>6609505</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13381,27 +13390,18 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -12159,10 +12159,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151027</v>
+        <v>125150908</v>
       </c>
       <c r="B97" t="n">
-        <v>100279</v>
+        <v>57847</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12171,46 +12171,62 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>103008</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471342</v>
+        <v>471387</v>
       </c>
       <c r="R97" t="n">
-        <v>6609418</v>
+        <v>6609362</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12240,30 +12256,29 @@
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12280,10 +12295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125148997</v>
+        <v>125151256</v>
       </c>
       <c r="B98" t="n">
-        <v>100188</v>
+        <v>102326</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12292,30 +12307,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>223246</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12325,7 +12340,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -12336,10 +12351,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471337</v>
+        <v>471433</v>
       </c>
       <c r="R98" t="n">
-        <v>6609424</v>
+        <v>6609506</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12383,16 +12398,6 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12409,7 +12414,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125148993</v>
+        <v>125151014</v>
       </c>
       <c r="B99" t="n">
         <v>101183</v>
@@ -12444,7 +12449,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12465,10 +12470,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471337</v>
+        <v>471342</v>
       </c>
       <c r="R99" t="n">
-        <v>6609424</v>
+        <v>6609418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12538,10 +12543,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125151077</v>
+        <v>125151113</v>
       </c>
       <c r="B100" t="n">
-        <v>100279</v>
+        <v>106461</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12554,28 +12559,36 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -12586,10 +12599,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471343</v>
+        <v>471438</v>
       </c>
       <c r="R100" t="n">
-        <v>6609410</v>
+        <v>6609330</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12659,10 +12672,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125151014</v>
+        <v>125151358</v>
       </c>
       <c r="B101" t="n">
-        <v>101183</v>
+        <v>100188</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12675,26 +12688,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12704,7 +12717,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -12715,10 +12728,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471342</v>
+        <v>471434</v>
       </c>
       <c r="R101" t="n">
-        <v>6609418</v>
+        <v>6609505</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12762,16 +12775,6 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12788,10 +12791,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125151113</v>
+        <v>125151027</v>
       </c>
       <c r="B102" t="n">
-        <v>106461</v>
+        <v>100279</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12804,36 +12807,28 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219686</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12844,10 +12839,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471438</v>
+        <v>471342</v>
       </c>
       <c r="R102" t="n">
-        <v>6609330</v>
+        <v>6609418</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12917,10 +12912,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151256</v>
+        <v>125151055</v>
       </c>
       <c r="B103" t="n">
-        <v>102326</v>
+        <v>101183</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12929,30 +12924,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>223246</v>
+        <v>221235</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12962,7 +12957,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12973,10 +12968,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471433</v>
+        <v>471343</v>
       </c>
       <c r="R103" t="n">
-        <v>6609506</v>
+        <v>6609410</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13020,6 +13015,16 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13036,10 +13041,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125150908</v>
+        <v>125148993</v>
       </c>
       <c r="B104" t="n">
-        <v>57847</v>
+        <v>101183</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13048,62 +13053,54 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103008</v>
+        <v>221235</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471387</v>
+        <v>471337</v>
       </c>
       <c r="R104" t="n">
-        <v>6609362</v>
+        <v>6609424</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13133,29 +13130,30 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13172,10 +13170,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125151055</v>
+        <v>125151077</v>
       </c>
       <c r="B105" t="n">
-        <v>101183</v>
+        <v>100279</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13188,36 +13186,28 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -13301,7 +13291,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125151358</v>
+        <v>125148997</v>
       </c>
       <c r="B106" t="n">
         <v>100188</v>
@@ -13357,10 +13347,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471434</v>
+        <v>471337</v>
       </c>
       <c r="R106" t="n">
-        <v>6609505</v>
+        <v>6609424</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13404,6 +13394,16 @@
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -12017,10 +12017,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125131092</v>
+        <v>125151014</v>
       </c>
       <c r="B96" t="n">
-        <v>57666</v>
+        <v>101183</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12029,47 +12029,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -12077,13 +12073,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471296</v>
+        <v>471342</v>
       </c>
       <c r="R96" t="n">
-        <v>6609358</v>
+        <v>6609418</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12110,27 +12106,18 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12141,7 +12128,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Gammal kalkgranskog</t>
+          <t>gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12159,10 +12146,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125150908</v>
+        <v>125151027</v>
       </c>
       <c r="B97" t="n">
-        <v>57847</v>
+        <v>100279</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12171,62 +12158,46 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103008</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471387</v>
+        <v>471342</v>
       </c>
       <c r="R97" t="n">
-        <v>6609362</v>
+        <v>6609418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12256,29 +12227,30 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12295,10 +12267,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125151256</v>
+        <v>125151113</v>
       </c>
       <c r="B98" t="n">
-        <v>102326</v>
+        <v>106461</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12307,30 +12279,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223246</v>
+        <v>219686</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12340,7 +12312,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -12351,10 +12323,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471433</v>
+        <v>471438</v>
       </c>
       <c r="R98" t="n">
-        <v>6609506</v>
+        <v>6609330</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12398,6 +12370,16 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12414,7 +12396,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125151014</v>
+        <v>125148993</v>
       </c>
       <c r="B99" t="n">
         <v>101183</v>
@@ -12449,7 +12431,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12470,10 +12452,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471342</v>
+        <v>471337</v>
       </c>
       <c r="R99" t="n">
-        <v>6609418</v>
+        <v>6609424</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12543,10 +12525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125151113</v>
+        <v>125151055</v>
       </c>
       <c r="B100" t="n">
-        <v>106461</v>
+        <v>101183</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12559,26 +12541,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12599,10 +12581,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471438</v>
+        <v>471343</v>
       </c>
       <c r="R100" t="n">
-        <v>6609330</v>
+        <v>6609410</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12791,10 +12773,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125151027</v>
+        <v>125148997</v>
       </c>
       <c r="B102" t="n">
-        <v>100279</v>
+        <v>100188</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12807,25 +12789,33 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12839,10 +12829,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471342</v>
+        <v>471337</v>
       </c>
       <c r="R102" t="n">
-        <v>6609418</v>
+        <v>6609424</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12912,10 +12902,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151055</v>
+        <v>125151256</v>
       </c>
       <c r="B103" t="n">
-        <v>101183</v>
+        <v>102326</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12924,30 +12914,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221235</v>
+        <v>223246</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12957,7 +12947,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12968,10 +12958,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471343</v>
+        <v>471433</v>
       </c>
       <c r="R103" t="n">
-        <v>6609410</v>
+        <v>6609506</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13015,16 +13005,6 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13041,10 +13021,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125148993</v>
+        <v>125151077</v>
       </c>
       <c r="B104" t="n">
-        <v>101183</v>
+        <v>100279</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13057,36 +13037,28 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -13097,10 +13069,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471337</v>
+        <v>471343</v>
       </c>
       <c r="R104" t="n">
-        <v>6609424</v>
+        <v>6609410</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13170,10 +13142,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125151077</v>
+        <v>125251985</v>
       </c>
       <c r="B105" t="n">
-        <v>100279</v>
+        <v>100188</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13186,42 +13158,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471343</v>
+        <v>471300</v>
       </c>
       <c r="R105" t="n">
-        <v>6609410</v>
+        <v>6609443</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13248,12 +13212,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13262,84 +13236,77 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125148997</v>
+        <v>125131092</v>
       </c>
       <c r="B106" t="n">
-        <v>100188</v>
+        <v>57666</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -13347,13 +13314,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471337</v>
+        <v>471296</v>
       </c>
       <c r="R106" t="n">
-        <v>6609424</v>
+        <v>6609358</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13380,18 +13347,27 @@
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -13402,7 +13378,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>gammal kalkgranskog</t>
+          <t>Gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13420,50 +13396,74 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125251985</v>
+        <v>125150908</v>
       </c>
       <c r="B107" t="n">
-        <v>100188</v>
+        <v>57847</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222771</v>
+        <v>103008</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tebroängen, Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471300</v>
+        <v>471387</v>
       </c>
       <c r="R107" t="n">
-        <v>6609443</v>
+        <v>6609362</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13490,22 +13490,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13520,12 +13520,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -12017,10 +12017,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125151014</v>
+        <v>125151113</v>
       </c>
       <c r="B96" t="n">
-        <v>101183</v>
+        <v>106461</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12033,26 +12033,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221235</v>
+        <v>219686</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12073,10 +12073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471342</v>
+        <v>471438</v>
       </c>
       <c r="R96" t="n">
-        <v>6609418</v>
+        <v>6609330</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12146,10 +12146,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151027</v>
+        <v>125151256</v>
       </c>
       <c r="B97" t="n">
-        <v>100279</v>
+        <v>102326</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12158,32 +12158,40 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>223246</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12194,10 +12202,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471342</v>
+        <v>471433</v>
       </c>
       <c r="R97" t="n">
-        <v>6609418</v>
+        <v>6609506</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12241,16 +12249,6 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12267,10 +12265,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125151113</v>
+        <v>125151014</v>
       </c>
       <c r="B98" t="n">
-        <v>106461</v>
+        <v>101183</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12283,26 +12281,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12323,10 +12321,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471438</v>
+        <v>471342</v>
       </c>
       <c r="R98" t="n">
-        <v>6609330</v>
+        <v>6609418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12396,10 +12394,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125148993</v>
+        <v>125151358</v>
       </c>
       <c r="B99" t="n">
-        <v>101183</v>
+        <v>100188</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12412,26 +12410,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12441,7 +12439,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12452,10 +12450,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471337</v>
+        <v>471434</v>
       </c>
       <c r="R99" t="n">
-        <v>6609424</v>
+        <v>6609505</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12499,16 +12497,6 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12525,10 +12513,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125151055</v>
+        <v>125148997</v>
       </c>
       <c r="B100" t="n">
-        <v>101183</v>
+        <v>100188</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12541,26 +12529,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12570,7 +12558,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -12581,10 +12569,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471343</v>
+        <v>471337</v>
       </c>
       <c r="R100" t="n">
-        <v>6609410</v>
+        <v>6609424</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12654,10 +12642,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125151358</v>
+        <v>125151027</v>
       </c>
       <c r="B101" t="n">
-        <v>100188</v>
+        <v>100279</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12670,33 +12658,25 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12710,10 +12690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471434</v>
+        <v>471342</v>
       </c>
       <c r="R101" t="n">
-        <v>6609505</v>
+        <v>6609418</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12757,6 +12737,16 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12773,10 +12763,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125148997</v>
+        <v>125148993</v>
       </c>
       <c r="B102" t="n">
-        <v>100188</v>
+        <v>101183</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12789,26 +12779,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12818,7 +12808,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12902,10 +12892,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151256</v>
+        <v>125151077</v>
       </c>
       <c r="B103" t="n">
-        <v>102326</v>
+        <v>100279</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12914,40 +12904,32 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12958,10 +12940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471433</v>
+        <v>471343</v>
       </c>
       <c r="R103" t="n">
-        <v>6609506</v>
+        <v>6609410</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13005,6 +12987,16 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13021,10 +13013,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125151077</v>
+        <v>125151055</v>
       </c>
       <c r="B104" t="n">
-        <v>100279</v>
+        <v>101183</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13037,28 +13029,36 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12017,10 +12017,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125151113</v>
+        <v>125151358</v>
       </c>
       <c r="B96" t="n">
-        <v>106461</v>
+        <v>100188</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12033,16 +12033,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219686</v>
+        <v>222771</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -12073,10 +12073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471438</v>
+        <v>471434</v>
       </c>
       <c r="R96" t="n">
-        <v>6609330</v>
+        <v>6609505</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12120,16 +12120,6 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12146,10 +12136,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151256</v>
+        <v>125148993</v>
       </c>
       <c r="B97" t="n">
-        <v>102326</v>
+        <v>101183</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12158,30 +12148,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223246</v>
+        <v>221235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12191,7 +12181,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12202,10 +12192,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471433</v>
+        <v>471337</v>
       </c>
       <c r="R97" t="n">
-        <v>6609506</v>
+        <v>6609424</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12249,6 +12239,16 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12265,10 +12265,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125151014</v>
+        <v>125151027</v>
       </c>
       <c r="B98" t="n">
-        <v>101183</v>
+        <v>100279</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12281,36 +12281,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -12394,10 +12386,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125151358</v>
+        <v>125151113</v>
       </c>
       <c r="B99" t="n">
-        <v>100188</v>
+        <v>106461</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12410,16 +12402,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222771</v>
+        <v>219686</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -12429,7 +12421,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12439,7 +12431,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12450,10 +12442,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471434</v>
+        <v>471438</v>
       </c>
       <c r="R99" t="n">
-        <v>6609505</v>
+        <v>6609330</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12497,6 +12489,16 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12513,10 +12515,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125148997</v>
+        <v>125151014</v>
       </c>
       <c r="B100" t="n">
-        <v>100188</v>
+        <v>101183</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12529,26 +12531,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12558,7 +12560,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -12569,10 +12571,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471337</v>
+        <v>471342</v>
       </c>
       <c r="R100" t="n">
-        <v>6609424</v>
+        <v>6609418</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12642,10 +12644,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125151027</v>
+        <v>125151055</v>
       </c>
       <c r="B101" t="n">
-        <v>100279</v>
+        <v>101183</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12658,28 +12660,36 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -12690,10 +12700,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471342</v>
+        <v>471343</v>
       </c>
       <c r="R101" t="n">
-        <v>6609418</v>
+        <v>6609410</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12763,10 +12773,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125148993</v>
+        <v>125151256</v>
       </c>
       <c r="B102" t="n">
-        <v>101183</v>
+        <v>102326</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12775,30 +12785,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221235</v>
+        <v>223246</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12808,7 +12818,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12819,10 +12829,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471337</v>
+        <v>471433</v>
       </c>
       <c r="R102" t="n">
-        <v>6609424</v>
+        <v>6609506</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12866,16 +12876,6 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13013,10 +13013,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125151055</v>
+        <v>125148997</v>
       </c>
       <c r="B104" t="n">
-        <v>101183</v>
+        <v>100188</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13029,26 +13029,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471343</v>
+        <v>471337</v>
       </c>
       <c r="R104" t="n">
-        <v>6609410</v>
+        <v>6609424</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13530,6 +13530,1199 @@
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>125457759</v>
+      </c>
+      <c r="B108" t="n">
+        <v>106461</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>471362</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6609461</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125443611</v>
+      </c>
+      <c r="B109" t="n">
+        <v>57992</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>471252</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6609607</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Den var mycket rörlig i ett lite större område från denna koordinat och mot öster och sydost och rörde sig högt upp i trädkronorna. Den var därför svårsedd, men vid den här koordinaten såg jag den sitta högst upp i en gran och sjunga. Mellan sångstroferna lockade den flitigt.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>naturskogsartad kalkbarrskog och barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>125457776</v>
+      </c>
+      <c r="B110" t="n">
+        <v>95347</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>471362</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6609461</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>125457874</v>
+      </c>
+      <c r="B111" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>471362</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6609461</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>125450450</v>
+      </c>
+      <c r="B112" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>210</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>471370</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>125457972</v>
+      </c>
+      <c r="B113" t="n">
+        <v>102326</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>471435</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6609510</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Två telningar och fem klena, unga träd.</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>125457870</v>
+      </c>
+      <c r="B114" t="n">
+        <v>101183</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>471362</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6609461</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>125450472</v>
+      </c>
+      <c r="B115" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>471370</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>125450120</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6609559</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>sång</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11891,7 +11891,7 @@
         <v>124860280</v>
       </c>
       <c r="B95" t="n">
-        <v>103528</v>
+        <v>103700</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12017,10 +12017,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125151358</v>
+        <v>125148993</v>
       </c>
       <c r="B96" t="n">
-        <v>100188</v>
+        <v>101355</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12033,26 +12033,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -12073,10 +12073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471434</v>
+        <v>471337</v>
       </c>
       <c r="R96" t="n">
-        <v>6609505</v>
+        <v>6609424</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12120,6 +12120,16 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12136,10 +12146,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125148993</v>
+        <v>125151358</v>
       </c>
       <c r="B97" t="n">
-        <v>101183</v>
+        <v>100358</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12152,26 +12162,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12181,7 +12191,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12192,10 +12202,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471337</v>
+        <v>471434</v>
       </c>
       <c r="R97" t="n">
-        <v>6609424</v>
+        <v>6609505</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12239,16 +12249,6 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12265,10 +12265,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125151027</v>
+        <v>125148997</v>
       </c>
       <c r="B98" t="n">
-        <v>100279</v>
+        <v>100358</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12281,25 +12281,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12313,10 +12321,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471342</v>
+        <v>471337</v>
       </c>
       <c r="R98" t="n">
-        <v>6609418</v>
+        <v>6609424</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12389,7 +12397,7 @@
         <v>125151113</v>
       </c>
       <c r="B99" t="n">
-        <v>106461</v>
+        <v>106640</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12515,10 +12523,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125151014</v>
+        <v>125151256</v>
       </c>
       <c r="B100" t="n">
-        <v>101183</v>
+        <v>102498</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12527,30 +12535,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221235</v>
+        <v>223246</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12560,7 +12568,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -12571,10 +12579,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471342</v>
+        <v>471433</v>
       </c>
       <c r="R100" t="n">
-        <v>6609418</v>
+        <v>6609506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12618,16 +12626,6 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12647,7 +12645,7 @@
         <v>125151055</v>
       </c>
       <c r="B101" t="n">
-        <v>101183</v>
+        <v>101355</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12773,10 +12771,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125151256</v>
+        <v>125151077</v>
       </c>
       <c r="B102" t="n">
-        <v>102326</v>
+        <v>100451</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12785,40 +12783,32 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -12829,10 +12819,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471433</v>
+        <v>471343</v>
       </c>
       <c r="R102" t="n">
-        <v>6609506</v>
+        <v>6609410</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12876,6 +12866,16 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12892,10 +12892,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151077</v>
+        <v>125151027</v>
       </c>
       <c r="B103" t="n">
-        <v>100279</v>
+        <v>100451</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12940,10 +12940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471343</v>
+        <v>471342</v>
       </c>
       <c r="R103" t="n">
-        <v>6609410</v>
+        <v>6609418</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13013,10 +13013,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125148997</v>
+        <v>125151014</v>
       </c>
       <c r="B104" t="n">
-        <v>100188</v>
+        <v>101355</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13029,26 +13029,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471337</v>
+        <v>471342</v>
       </c>
       <c r="R104" t="n">
-        <v>6609424</v>
+        <v>6609418</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13145,7 +13145,7 @@
         <v>125251985</v>
       </c>
       <c r="B105" t="n">
-        <v>100188</v>
+        <v>100358</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13254,10 +13254,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125131092</v>
+        <v>125150908</v>
       </c>
       <c r="B106" t="n">
-        <v>57666</v>
+        <v>57961</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>103008</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -13307,20 +13307,24 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471296</v>
+        <v>471387</v>
       </c>
       <c r="R106" t="n">
-        <v>6609358</v>
+        <v>6609362</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13349,7 +13353,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13359,7 +13363,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13370,16 +13374,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -13396,10 +13390,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125150908</v>
+        <v>125131092</v>
       </c>
       <c r="B107" t="n">
-        <v>57847</v>
+        <v>57793</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13412,21 +13406,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103008</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -13449,24 +13443,20 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471387</v>
+        <v>471296</v>
       </c>
       <c r="R107" t="n">
-        <v>6609362</v>
+        <v>6609358</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13495,7 +13485,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13505,7 +13495,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13516,6 +13506,16 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13532,10 +13532,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125457759</v>
+        <v>125443611</v>
       </c>
       <c r="B108" t="n">
-        <v>106461</v>
+        <v>58107</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13548,39 +13548,43 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219686</v>
+        <v>100058</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -13588,10 +13592,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471362</v>
+        <v>471252</v>
       </c>
       <c r="R108" t="n">
-        <v>6609461</v>
+        <v>6609607</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13621,24 +13625,43 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Den var mycket rörlig i ett lite större område från denna koordinat och mot öster och sydost och rörde sig högt upp i trädkronorna. Den var därför svårsedd, men vid den här koordinaten såg jag den sitta högst upp i en gran och sjunga. Mellan sångstroferna lockade den flitigt.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>naturskogsartad kalkbarrskog och barrsumpskog</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13656,10 +13679,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125443611</v>
+        <v>125457776</v>
       </c>
       <c r="B109" t="n">
-        <v>57992</v>
+        <v>95515</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13672,43 +13695,27 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100058</v>
+        <v>2813</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -13716,10 +13723,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471252</v>
+        <v>471362</v>
       </c>
       <c r="R109" t="n">
-        <v>6609607</v>
+        <v>6609461</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13749,43 +13756,24 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Den var mycket rörlig i ett lite större område från denna koordinat och mot öster och sydost och rörde sig högt upp i trädkronorna. Den var därför svårsedd, men vid den här koordinaten såg jag den sitta högst upp i en gran och sjunga. Mellan sångstroferna lockade den flitigt.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>naturskogsartad kalkbarrskog och barrsumpskog</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13803,10 +13791,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125457776</v>
+        <v>125457874</v>
       </c>
       <c r="B110" t="n">
-        <v>95347</v>
+        <v>95503</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13819,21 +13807,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13915,10 +13903,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125457874</v>
+        <v>125457870</v>
       </c>
       <c r="B111" t="n">
-        <v>95335</v>
+        <v>101355</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13931,26 +13919,38 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -14027,10 +14027,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125450450</v>
+        <v>125457972</v>
       </c>
       <c r="B112" t="n">
-        <v>95551</v>
+        <v>102498</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14039,40 +14039,40 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>210</v>
+        <v>223246</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471370</v>
+        <v>471435</v>
       </c>
       <c r="R112" t="n">
-        <v>6609456</v>
+        <v>6609510</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14116,19 +14116,14 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>08:40</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Två telningar och fem klena, unga träd.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14141,32 +14136,14 @@
       <c r="AG112" t="b">
         <v>0</v>
       </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
+          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14184,10 +14161,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125457972</v>
+        <v>125450120</v>
       </c>
       <c r="B113" t="n">
-        <v>102326</v>
+        <v>57793</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14196,43 +14173,39 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223246</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14240,13 +14213,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471435</v>
+        <v>471311</v>
       </c>
       <c r="R113" t="n">
-        <v>6609510</v>
+        <v>6609559</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14273,14 +14246,24 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Två telningar och fem klena, unga träd.</t>
+          <t>sång</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14289,18 +14272,12 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14318,10 +14295,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125457870</v>
+        <v>125450450</v>
       </c>
       <c r="B114" t="n">
-        <v>101183</v>
+        <v>95719</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14334,36 +14311,36 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221235</v>
+        <v>210</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -14374,10 +14351,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R114" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14407,9 +14384,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14425,6 +14412,29 @@
       <c r="AI114" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14445,7 +14455,7 @@
         <v>125450472</v>
       </c>
       <c r="B115" t="n">
-        <v>95455</v>
+        <v>95623</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14591,10 +14601,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125450120</v>
+        <v>125457759</v>
       </c>
       <c r="B116" t="n">
-        <v>57666</v>
+        <v>106640</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14603,39 +14613,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>219686</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -14643,13 +14657,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471311</v>
+        <v>471362</v>
       </c>
       <c r="R116" t="n">
-        <v>6609559</v>
+        <v>6609461</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14676,38 +14690,24 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>sång</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14722,6 +14722,1084 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>125547926</v>
+      </c>
+      <c r="B117" t="n">
+        <v>95624</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2819</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Trind spretmossa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Herzogiella striatella</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>471326</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6609568</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Humus</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Humus</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>125547900</v>
+      </c>
+      <c r="B118" t="n">
+        <v>74836</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>471326</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6609568</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>125557691</v>
+      </c>
+      <c r="B119" t="n">
+        <v>58107</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>471264</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6609623</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>125556711</v>
+      </c>
+      <c r="B120" t="n">
+        <v>80063</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6609624</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>125556114</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79963</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>471420</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6609517</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>På alm</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>125556037</v>
+      </c>
+      <c r="B122" t="n">
+        <v>95719</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>210</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>471417</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6609431</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>12 kapslar.</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>125556666</v>
+      </c>
+      <c r="B123" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>471398</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6609461</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>125557853</v>
+      </c>
+      <c r="B124" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>471420</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6609517</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>125555995</v>
+      </c>
+      <c r="B125" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>471424</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6609510</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13532,10 +13532,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125443611</v>
+        <v>125457776</v>
       </c>
       <c r="B108" t="n">
-        <v>58107</v>
+        <v>95515</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13548,43 +13548,27 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100058</v>
+        <v>2813</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -13592,10 +13576,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471252</v>
+        <v>471362</v>
       </c>
       <c r="R108" t="n">
-        <v>6609607</v>
+        <v>6609461</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13625,43 +13609,24 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Den var mycket rörlig i ett lite större område från denna koordinat och mot öster och sydost och rörde sig högt upp i trädkronorna. Den var därför svårsedd, men vid den här koordinaten såg jag den sitta högst upp i en gran och sjunga. Mellan sångstroferna lockade den flitigt.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>naturskogsartad kalkbarrskog och barrsumpskog</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13679,10 +13644,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125457776</v>
+        <v>125443611</v>
       </c>
       <c r="B109" t="n">
-        <v>95515</v>
+        <v>58107</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13695,27 +13660,43 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2813</v>
+        <v>100058</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -13723,10 +13704,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471362</v>
+        <v>471252</v>
       </c>
       <c r="R109" t="n">
-        <v>6609461</v>
+        <v>6609607</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13756,24 +13737,43 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Den var mycket rörlig i ett lite större område från denna koordinat och mot öster och sydost och rörde sig högt upp i trädkronorna. Den var därför svårsedd, men vid den här koordinaten såg jag den sitta högst upp i en gran och sjunga. Mellan sångstroferna lockade den flitigt.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>naturskogsartad kalkbarrskog och barrsumpskog</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -15350,10 +15350,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125556037</v>
+        <v>125580232</v>
       </c>
       <c r="B122" t="n">
-        <v>95719</v>
+        <v>102498</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15362,42 +15362,58 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>210</v>
+        <v>223246</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471417</v>
+        <v>471458</v>
       </c>
       <c r="R122" t="n">
-        <v>6609431</v>
+        <v>6609490</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15434,7 +15450,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>12 kapslar.</t>
+          <t>stort träd</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15447,30 +15463,35 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Murken granlåga.</t>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>surdråg med gråal, skogsalm, gran m.m.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125556666</v>
+        <v>125556037</v>
       </c>
       <c r="B123" t="n">
-        <v>100358</v>
+        <v>95719</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15483,21 +15504,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222771</v>
+        <v>210</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -15511,10 +15532,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471398</v>
+        <v>471417</v>
       </c>
       <c r="R123" t="n">
-        <v>6609461</v>
+        <v>6609431</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15551,7 +15572,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>12 kapslar.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15563,6 +15584,11 @@
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Murken granlåga.</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -15579,7 +15605,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125557853</v>
+        <v>125556666</v>
       </c>
       <c r="B124" t="n">
         <v>100358</v>
@@ -15623,10 +15649,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471420</v>
+        <v>471398</v>
       </c>
       <c r="R124" t="n">
-        <v>6609517</v>
+        <v>6609461</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15663,7 +15689,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15691,10 +15717,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125555995</v>
+        <v>125580326</v>
       </c>
       <c r="B125" t="n">
-        <v>95515</v>
+        <v>79366</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15703,42 +15729,49 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2813</v>
+        <v>130</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Savlundlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Bellicidia incompta</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Borrer) Kistenich et al.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471424</v>
+        <v>471439</v>
       </c>
       <c r="R125" t="n">
-        <v>6609510</v>
+        <v>6609505</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15773,11 +15806,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -15788,18 +15816,548 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
-      <c r="AT125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>surdråg med gråal, skogsalm, gran m.m.</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Bark on living woody plant # Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW125" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125557853</v>
+      </c>
+      <c r="B126" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>471420</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6609517</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
           <t>Toni Berglund</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
+      <c r="AX126" t="inlineStr">
         <is>
           <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
-      <c r="AY125" t="inlineStr"/>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125580133</v>
+      </c>
+      <c r="B127" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>471456</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6609465</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>grov kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>125555995</v>
+      </c>
+      <c r="B128" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>471424</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6609510</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Toni Berglund, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>125580376</v>
+      </c>
+      <c r="B129" t="n">
+        <v>102498</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>471439</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6609505</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>stort träd</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>surdråg med gråal, skogsalm, gran m.m.</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12017,7 +12017,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125148993</v>
+        <v>125151055</v>
       </c>
       <c r="B96" t="n">
         <v>101355</v>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12073,10 +12073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471337</v>
+        <v>471343</v>
       </c>
       <c r="R96" t="n">
-        <v>6609424</v>
+        <v>6609410</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12146,10 +12146,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151358</v>
+        <v>125151014</v>
       </c>
       <c r="B97" t="n">
-        <v>100358</v>
+        <v>101355</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12162,26 +12162,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471434</v>
+        <v>471342</v>
       </c>
       <c r="R97" t="n">
-        <v>6609505</v>
+        <v>6609418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12249,6 +12249,16 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12265,7 +12275,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125148997</v>
+        <v>125151358</v>
       </c>
       <c r="B98" t="n">
         <v>100358</v>
@@ -12321,10 +12331,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471337</v>
+        <v>471434</v>
       </c>
       <c r="R98" t="n">
-        <v>6609424</v>
+        <v>6609505</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12368,16 +12378,6 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -12394,10 +12394,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125151113</v>
+        <v>125151256</v>
       </c>
       <c r="B99" t="n">
-        <v>106640</v>
+        <v>102498</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12406,30 +12406,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219686</v>
+        <v>223246</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471438</v>
+        <v>471433</v>
       </c>
       <c r="R99" t="n">
-        <v>6609330</v>
+        <v>6609506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12497,16 +12497,6 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12523,10 +12513,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125151256</v>
+        <v>125151077</v>
       </c>
       <c r="B100" t="n">
-        <v>102498</v>
+        <v>100451</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12535,40 +12525,32 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -12579,10 +12561,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471433</v>
+        <v>471343</v>
       </c>
       <c r="R100" t="n">
-        <v>6609506</v>
+        <v>6609410</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12626,6 +12608,16 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12642,10 +12634,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125151055</v>
+        <v>125151113</v>
       </c>
       <c r="B101" t="n">
-        <v>101355</v>
+        <v>106640</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12658,26 +12650,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221235</v>
+        <v>219686</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12698,10 +12690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471343</v>
+        <v>471438</v>
       </c>
       <c r="R101" t="n">
-        <v>6609410</v>
+        <v>6609330</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12771,7 +12763,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125151077</v>
+        <v>125151027</v>
       </c>
       <c r="B102" t="n">
         <v>100451</v>
@@ -12819,10 +12811,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471343</v>
+        <v>471342</v>
       </c>
       <c r="R102" t="n">
-        <v>6609410</v>
+        <v>6609418</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12892,10 +12884,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125151027</v>
+        <v>125148993</v>
       </c>
       <c r="B103" t="n">
-        <v>100451</v>
+        <v>101355</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12908,28 +12900,36 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12940,10 +12940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471342</v>
+        <v>471337</v>
       </c>
       <c r="R103" t="n">
-        <v>6609418</v>
+        <v>6609424</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13013,10 +13013,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125151014</v>
+        <v>125148997</v>
       </c>
       <c r="B104" t="n">
-        <v>101355</v>
+        <v>100358</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13029,26 +13029,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471342</v>
+        <v>471337</v>
       </c>
       <c r="R104" t="n">
-        <v>6609418</v>
+        <v>6609424</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13254,10 +13254,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125150908</v>
+        <v>125131092</v>
       </c>
       <c r="B106" t="n">
-        <v>57961</v>
+        <v>57793</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103008</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -13307,24 +13307,20 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471387</v>
+        <v>471296</v>
       </c>
       <c r="R106" t="n">
-        <v>6609362</v>
+        <v>6609358</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13353,7 +13349,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13363,7 +13359,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13374,6 +13370,16 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Gammal kalkgranskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -13390,10 +13396,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125131092</v>
+        <v>125150908</v>
       </c>
       <c r="B107" t="n">
-        <v>57793</v>
+        <v>57961</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13406,21 +13412,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>103008</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -13443,20 +13449,24 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471296</v>
+        <v>471387</v>
       </c>
       <c r="R107" t="n">
-        <v>6609358</v>
+        <v>6609362</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13485,7 +13495,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13495,7 +13505,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13506,16 +13516,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Gammal kalkgranskog</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13532,10 +13532,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125457776</v>
+        <v>125450120</v>
       </c>
       <c r="B108" t="n">
-        <v>95515</v>
+        <v>57793</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13544,31 +13544,39 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2813</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -13576,13 +13584,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471362</v>
+        <v>471311</v>
       </c>
       <c r="R108" t="n">
-        <v>6609461</v>
+        <v>6609559</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13609,24 +13617,38 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>sång</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13644,10 +13666,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125443611</v>
+        <v>125450472</v>
       </c>
       <c r="B109" t="n">
-        <v>58107</v>
+        <v>95623</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13660,43 +13682,31 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100058</v>
+        <v>2818</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -13704,10 +13714,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471252</v>
+        <v>471370</v>
       </c>
       <c r="R109" t="n">
-        <v>6609607</v>
+        <v>6609456</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13739,7 +13749,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13752,28 +13762,42 @@
           <t>08:40</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Den var mycket rörlig i ett lite större område från denna koordinat och mot öster och sydost och rörde sig högt upp i trädkronorna. Den var därför svårsedd, men vid den här koordinaten såg jag den sitta högst upp i en gran och sjunga. Mellan sångstroferna lockade den flitigt.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>naturskogsartad kalkbarrskog och barrsumpskog</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13791,10 +13815,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125457874</v>
+        <v>125457972</v>
       </c>
       <c r="B110" t="n">
-        <v>95503</v>
+        <v>102498</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13803,30 +13827,42 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2809</v>
+        <v>223246</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -13835,10 +13871,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471362</v>
+        <v>471435</v>
       </c>
       <c r="R110" t="n">
-        <v>6609461</v>
+        <v>6609510</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13873,6 +13909,11 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Två telningar och fem klena, unga träd.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -13883,9 +13924,14 @@
       <c r="AG110" t="b">
         <v>0</v>
       </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13903,10 +13949,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125457870</v>
+        <v>125457759</v>
       </c>
       <c r="B111" t="n">
-        <v>101355</v>
+        <v>106640</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13919,26 +13965,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221235</v>
+        <v>219686</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14027,10 +14073,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125457972</v>
+        <v>125450450</v>
       </c>
       <c r="B112" t="n">
-        <v>102498</v>
+        <v>95719</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14039,40 +14085,40 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223246</v>
+        <v>210</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -14083,10 +14129,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471435</v>
+        <v>471370</v>
       </c>
       <c r="R112" t="n">
-        <v>6609510</v>
+        <v>6609456</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14116,14 +14162,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Två telningar och fem klena, unga träd.</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14136,14 +14187,32 @@
       <c r="AG112" t="b">
         <v>0</v>
       </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14161,10 +14230,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125450120</v>
+        <v>125457870</v>
       </c>
       <c r="B113" t="n">
-        <v>57793</v>
+        <v>101355</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14173,25 +14242,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -14199,13 +14268,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14213,13 +14286,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471311</v>
+        <v>471362</v>
       </c>
       <c r="R113" t="n">
-        <v>6609559</v>
+        <v>6609461</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14246,38 +14319,24 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>sång</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14295,10 +14354,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125450450</v>
+        <v>125457776</v>
       </c>
       <c r="B114" t="n">
-        <v>95719</v>
+        <v>95515</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14311,38 +14370,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>210</v>
+        <v>2813</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -14351,10 +14398,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R114" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14384,19 +14431,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14412,29 +14449,6 @@
       <c r="AI114" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN114" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14452,10 +14466,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125450472</v>
+        <v>125457874</v>
       </c>
       <c r="B115" t="n">
-        <v>95623</v>
+        <v>95503</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14468,30 +14482,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2818</v>
+        <v>2809</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -14500,10 +14510,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R115" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14533,19 +14543,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14561,29 +14561,6 @@
       <c r="AI115" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN115" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14601,10 +14578,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125457759</v>
+        <v>125547900</v>
       </c>
       <c r="B116" t="n">
-        <v>106640</v>
+        <v>74836</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14617,39 +14594,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219686</v>
+        <v>6428</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -14657,10 +14625,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471362</v>
+        <v>471326</v>
       </c>
       <c r="R116" t="n">
-        <v>6609461</v>
+        <v>6609568</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14687,12 +14655,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14705,9 +14678,34 @@
       <c r="AG116" t="b">
         <v>0</v>
       </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa # grovt träd</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14859,10 +14857,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125547900</v>
+        <v>125557853</v>
       </c>
       <c r="B118" t="n">
-        <v>74836</v>
+        <v>100358</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14875,41 +14873,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6428</v>
+        <v>222771</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471326</v>
+        <v>471420</v>
       </c>
       <c r="R118" t="n">
-        <v>6609568</v>
+        <v>6609517</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14946,7 +14941,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14959,55 +14954,25 @@
       <c r="AG118" t="b">
         <v>0</v>
       </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa # grovt träd</t>
-        </is>
-      </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125557691</v>
+        <v>125556037</v>
       </c>
       <c r="B119" t="n">
-        <v>58107</v>
+        <v>95719</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15020,35 +14985,27 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100058</v>
+        <v>210</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15056,13 +15013,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471264</v>
+        <v>471417</v>
       </c>
       <c r="R119" t="n">
-        <v>6609623</v>
+        <v>6609431</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15089,19 +15046,14 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>12 kapslar.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15110,8 +15062,14 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Murken granlåga.</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -15121,17 +15079,17 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125556711</v>
+        <v>125580133</v>
       </c>
       <c r="B120" t="n">
-        <v>80063</v>
+        <v>100451</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15144,37 +15102,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471311</v>
+        <v>471456</v>
       </c>
       <c r="R120" t="n">
-        <v>6609624</v>
+        <v>6609465</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15219,30 +15182,30 @@
       <c r="AG120" t="b">
         <v>0</v>
       </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Asp.</t>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>grov kalkgranskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125556114</v>
+        <v>125555995</v>
       </c>
       <c r="B121" t="n">
-        <v>79963</v>
+        <v>95515</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15255,26 +15218,27 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6457</v>
+        <v>2813</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -15282,10 +15246,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471420</v>
+        <v>471424</v>
       </c>
       <c r="R121" t="n">
-        <v>6609517</v>
+        <v>6609510</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15320,6 +15284,11 @@
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -15330,11 +15299,6 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>På alm</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
@@ -15343,17 +15307,17 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125580232</v>
+        <v>125556666</v>
       </c>
       <c r="B122" t="n">
-        <v>102498</v>
+        <v>100358</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15362,58 +15326,42 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471458</v>
+        <v>471398</v>
       </c>
       <c r="R122" t="n">
-        <v>6609490</v>
+        <v>6609461</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15450,7 +15398,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>stort träd</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15463,35 +15411,25 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>surdråg med gråal, skogsalm, gran m.m.</t>
-        </is>
-      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125556037</v>
+        <v>125556114</v>
       </c>
       <c r="B123" t="n">
-        <v>95719</v>
+        <v>79963</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15504,27 +15442,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -15532,10 +15469,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471417</v>
+        <v>471420</v>
       </c>
       <c r="R123" t="n">
-        <v>6609431</v>
+        <v>6609517</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15570,11 +15507,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>12 kapslar.</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -15587,7 +15519,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Murken granlåga.</t>
+          <t>På alm</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15598,17 +15530,17 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125556666</v>
+        <v>125580376</v>
       </c>
       <c r="B124" t="n">
-        <v>100358</v>
+        <v>102498</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15617,42 +15549,58 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>222771</v>
+        <v>223246</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471398</v>
+        <v>471439</v>
       </c>
       <c r="R124" t="n">
-        <v>6609461</v>
+        <v>6609505</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15682,14 +15630,24 @@
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>stort träd</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15702,15 +15660,25 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>surdråg med gråal, skogsalm, gran m.m.</t>
+        </is>
+      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -15873,10 +15841,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125557853</v>
+        <v>125580232</v>
       </c>
       <c r="B126" t="n">
-        <v>100358</v>
+        <v>102498</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15885,42 +15853,58 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>222771</v>
+        <v>223246</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471420</v>
+        <v>471458</v>
       </c>
       <c r="R126" t="n">
-        <v>6609517</v>
+        <v>6609490</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15957,7 +15941,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>stort träd</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15970,25 +15954,35 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>surdråg med gråal, skogsalm, gran m.m.</t>
+        </is>
+      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125580133</v>
+        <v>125556711</v>
       </c>
       <c r="B127" t="n">
-        <v>100451</v>
+        <v>80063</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -16001,42 +15995,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471456</v>
+        <v>471311</v>
       </c>
       <c r="R127" t="n">
-        <v>6609465</v>
+        <v>6609624</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16081,30 +16070,30 @@
       <c r="AG127" t="b">
         <v>0</v>
       </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>grov kalkgranskog</t>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Asp.</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125555995</v>
+        <v>125638785</v>
       </c>
       <c r="B128" t="n">
-        <v>95515</v>
+        <v>102771</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -16117,38 +16106,50 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471424</v>
+        <v>471336</v>
       </c>
       <c r="R128" t="n">
-        <v>6609510</v>
+        <v>6609447</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16175,17 +16176,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16198,25 +16194,30 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125580376</v>
+        <v>125638825</v>
       </c>
       <c r="B129" t="n">
-        <v>102498</v>
+        <v>102771</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -16225,58 +16226,46 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>223246</v>
+        <v>222002</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471439</v>
+        <v>471334</v>
       </c>
       <c r="R129" t="n">
-        <v>6609505</v>
+        <v>6609447</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16303,27 +16292,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>stort träd</t>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16336,14 +16315,9 @@
       <c r="AG129" t="b">
         <v>0</v>
       </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>surdråg med gråal, skogsalm, gran m.m.</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16354,10 +16328,5500 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>125639036</v>
+      </c>
+      <c r="B130" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>471281</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6609438</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>kalkblandskog: gran och gråal</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>125638438</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98292</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>471350</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6609454</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>125647849</v>
+      </c>
+      <c r="B132" t="n">
+        <v>95127</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>471232</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6609657</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>125638865</v>
+      </c>
+      <c r="B133" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6609451</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>125639406</v>
+      </c>
+      <c r="B134" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>471294</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6609352</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>125639134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>471271</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6609429</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>125638320</v>
+      </c>
+      <c r="B136" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>471329</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6609462</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten med surdråg</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>125638823</v>
+      </c>
+      <c r="B137" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>471334</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6609447</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>125638511</v>
+      </c>
+      <c r="B138" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>471371</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6609452</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>125647908</v>
+      </c>
+      <c r="B139" t="n">
+        <v>97008</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>2617</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Flikbålmossa</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Riccardia multifida</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>471286</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6609621</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>125638527</v>
+      </c>
+      <c r="B140" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>471371</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6609452</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>125647784</v>
+      </c>
+      <c r="B141" t="n">
+        <v>96842</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2326</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Vanlig rörsvepemossa</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Liochlaena lanceolata</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Nees</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>471261</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6609660</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>125638375</v>
+      </c>
+      <c r="B142" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>471329</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6609462</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten med surdråg</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>125638908</v>
+      </c>
+      <c r="B143" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>471306</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>125639167</v>
+      </c>
+      <c r="B144" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>471265</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>125638455</v>
+      </c>
+      <c r="B145" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>471350</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6609454</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>125638618</v>
+      </c>
+      <c r="B146" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>471408</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6609463</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>125638876</v>
+      </c>
+      <c r="B147" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6609451</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>125639216</v>
+      </c>
+      <c r="B148" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>471261</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6609384</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>125638720</v>
+      </c>
+      <c r="B149" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>471352</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6609455</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>125638819</v>
+      </c>
+      <c r="B150" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>471334</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6609447</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>125638580</v>
+      </c>
+      <c r="B151" t="n">
+        <v>95623</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>471393</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6609458</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>125638831</v>
+      </c>
+      <c r="B152" t="n">
+        <v>98292</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>471334</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6609447</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>125638463</v>
+      </c>
+      <c r="B153" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>471350</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6609454</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>125638903</v>
+      </c>
+      <c r="B154" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>471306</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>125638917</v>
+      </c>
+      <c r="B155" t="n">
+        <v>103700</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>471306</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>125638915</v>
+      </c>
+      <c r="B156" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>471306</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>125638955</v>
+      </c>
+      <c r="B157" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>471281</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6609438</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>125638457</v>
+      </c>
+      <c r="B158" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>471350</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6609454</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>125647918</v>
+      </c>
+      <c r="B159" t="n">
+        <v>96747</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>231</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Blå säckmossa</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Calypogeia azurea</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Stotler &amp; Crotz</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>471286</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6609621</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>125638551</v>
+      </c>
+      <c r="B160" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>471386</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6609448</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>125639232</v>
+      </c>
+      <c r="B161" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>471252</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6609379</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>125638771</v>
+      </c>
+      <c r="B162" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>471336</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6609447</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>125638348</v>
+      </c>
+      <c r="B163" t="n">
+        <v>98292</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>471329</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6609462</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten med surdråg</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>125639147</v>
+      </c>
+      <c r="B164" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>471271</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6609429</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>125639081</v>
+      </c>
+      <c r="B165" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>471281</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6609438</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>kalkblandskog: gran och gråal</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>125638940</v>
+      </c>
+      <c r="B166" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>471288</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6609428</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>125638893</v>
+      </c>
+      <c r="B167" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>471306</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6609456</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>125638871</v>
+      </c>
+      <c r="B168" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6609451</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>125639177</v>
+      </c>
+      <c r="B169" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>471265</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>125638361</v>
+      </c>
+      <c r="B170" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>471329</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6609462</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten med surdråg</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>125638625</v>
+      </c>
+      <c r="B171" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>471408</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6609463</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>125638867</v>
+      </c>
+      <c r="B172" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>471319</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6609451</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>125647825</v>
+      </c>
+      <c r="B173" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>53</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Tebroängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6609467</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>125639241</v>
+      </c>
+      <c r="B174" t="n">
+        <v>98292</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>471252</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6609379</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>125638600</v>
+      </c>
+      <c r="B175" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>471393</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6609458</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY175"/>
+  <dimension ref="A1:AY174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13532,10 +13532,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125450120</v>
+        <v>125457972</v>
       </c>
       <c r="B108" t="n">
-        <v>57793</v>
+        <v>102498</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13544,39 +13544,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>223246</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -13584,13 +13588,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471311</v>
+        <v>471435</v>
       </c>
       <c r="R108" t="n">
-        <v>6609559</v>
+        <v>6609510</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13617,24 +13621,14 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>sång</t>
+          <t>Två telningar och fem klena, unga träd.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13643,12 +13637,18 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125457972</v>
+        <v>125457759</v>
       </c>
       <c r="B110" t="n">
-        <v>102498</v>
+        <v>106640</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13827,25 +13827,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223246</v>
+        <v>219686</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471435</v>
+        <v>471362</v>
       </c>
       <c r="R110" t="n">
-        <v>6609510</v>
+        <v>6609461</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13909,11 +13909,6 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Två telningar och fem klena, unga träd.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -13924,14 +13919,9 @@
       <c r="AG110" t="b">
         <v>0</v>
       </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13949,10 +13939,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125457759</v>
+        <v>125450450</v>
       </c>
       <c r="B111" t="n">
-        <v>106640</v>
+        <v>95719</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13965,36 +13955,36 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -14005,10 +13995,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R111" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14038,9 +14028,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14056,6 +14056,29 @@
       <c r="AI111" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14073,10 +14096,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125450450</v>
+        <v>125457870</v>
       </c>
       <c r="B112" t="n">
-        <v>95719</v>
+        <v>101355</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14089,36 +14112,36 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>210</v>
+        <v>221235</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -14129,10 +14152,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R112" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14162,19 +14185,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14190,29 +14203,6 @@
       <c r="AI112" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14230,10 +14220,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125457870</v>
+        <v>125457776</v>
       </c>
       <c r="B113" t="n">
-        <v>101355</v>
+        <v>95515</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14246,38 +14236,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221235</v>
+        <v>2813</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -14354,10 +14332,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125457776</v>
+        <v>125457874</v>
       </c>
       <c r="B114" t="n">
-        <v>95515</v>
+        <v>95503</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14370,21 +14348,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14466,10 +14444,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125457874</v>
+        <v>125547900</v>
       </c>
       <c r="B115" t="n">
-        <v>95503</v>
+        <v>74836</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14482,27 +14460,30 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2809</v>
+        <v>6428</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -14510,10 +14491,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471362</v>
+        <v>471326</v>
       </c>
       <c r="R115" t="n">
-        <v>6609461</v>
+        <v>6609568</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14540,12 +14521,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14558,9 +14544,34 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa # grovt träd</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14578,10 +14589,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125547900</v>
+        <v>125547926</v>
       </c>
       <c r="B116" t="n">
-        <v>74836</v>
+        <v>95624</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14594,30 +14605,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6428</v>
+        <v>2819</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -14663,11 +14683,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Riklig</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -14683,29 +14698,14 @@
           <t>Blandsumpskog</t>
         </is>
       </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
-        </is>
-      </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Humus</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Alnus glutinosa # grovt träd</t>
+          <t>Humus</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14723,10 +14723,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125547926</v>
+        <v>125557853</v>
       </c>
       <c r="B117" t="n">
-        <v>95624</v>
+        <v>100358</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14739,50 +14739,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2819</v>
+        <v>222771</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471326</v>
+        <v>471420</v>
       </c>
       <c r="R117" t="n">
-        <v>6609568</v>
+        <v>6609517</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14817,6 +14805,11 @@
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -14827,40 +14820,25 @@
       <c r="AG117" t="b">
         <v>0</v>
       </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Humus</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Humus</t>
-        </is>
-      </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125557853</v>
+        <v>125556037</v>
       </c>
       <c r="B118" t="n">
-        <v>100358</v>
+        <v>95719</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14873,21 +14851,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222771</v>
+        <v>210</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14901,10 +14879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471420</v>
+        <v>471417</v>
       </c>
       <c r="R118" t="n">
-        <v>6609517</v>
+        <v>6609431</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14941,7 +14919,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>12 kapslar.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14954,6 +14932,11 @@
       <c r="AG118" t="b">
         <v>0</v>
       </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Murken granlåga.</t>
+        </is>
+      </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
@@ -14962,17 +14945,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125556037</v>
+        <v>125580133</v>
       </c>
       <c r="B119" t="n">
-        <v>95719</v>
+        <v>100451</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14985,38 +14968,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471417</v>
+        <v>471456</v>
       </c>
       <c r="R119" t="n">
-        <v>6609431</v>
+        <v>6609465</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15051,11 +15038,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>12 kapslar.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -15066,30 +15048,30 @@
       <c r="AG119" t="b">
         <v>0</v>
       </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Murken granlåga.</t>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>grov kalkgranskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125580133</v>
+        <v>125555995</v>
       </c>
       <c r="B120" t="n">
-        <v>100451</v>
+        <v>95515</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15102,42 +15084,38 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471456</v>
+        <v>471424</v>
       </c>
       <c r="R120" t="n">
-        <v>6609465</v>
+        <v>6609510</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15172,6 +15150,11 @@
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -15182,30 +15165,25 @@
       <c r="AG120" t="b">
         <v>0</v>
       </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>grov kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125555995</v>
+        <v>125556666</v>
       </c>
       <c r="B121" t="n">
-        <v>95515</v>
+        <v>100358</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15218,21 +15196,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2813</v>
+        <v>222771</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15246,10 +15224,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471424</v>
+        <v>471398</v>
       </c>
       <c r="R121" t="n">
-        <v>6609510</v>
+        <v>6609461</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15286,7 +15264,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15314,10 +15292,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125556666</v>
+        <v>125556114</v>
       </c>
       <c r="B122" t="n">
-        <v>100358</v>
+        <v>79963</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15330,27 +15308,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222771</v>
+        <v>6457</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -15358,10 +15335,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471398</v>
+        <v>471420</v>
       </c>
       <c r="R122" t="n">
-        <v>6609461</v>
+        <v>6609517</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15396,11 +15373,6 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Enstaka.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -15411,6 +15383,11 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>På alm</t>
+        </is>
+      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
@@ -15419,17 +15396,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125556114</v>
+        <v>125580376</v>
       </c>
       <c r="B123" t="n">
-        <v>79963</v>
+        <v>102498</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15438,41 +15415,58 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6457</v>
+        <v>223246</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471420</v>
+        <v>471439</v>
       </c>
       <c r="R123" t="n">
-        <v>6609517</v>
+        <v>6609505</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15502,9 +15496,24 @@
           <t>2025-05-30</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>stort träd</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15517,27 +15526,32 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>På alm</t>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>surdråg med gråal, skogsalm, gran m.m.</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125580376</v>
+        <v>125580232</v>
       </c>
       <c r="B124" t="n">
         <v>102498</v>
@@ -15597,10 +15611,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471439</v>
+        <v>471458</v>
       </c>
       <c r="R124" t="n">
-        <v>6609505</v>
+        <v>6609490</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15630,19 +15644,9 @@
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -15678,17 +15682,17 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125580326</v>
+        <v>125556711</v>
       </c>
       <c r="B125" t="n">
-        <v>79366</v>
+        <v>80063</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15697,49 +15701,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>130</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Savlundlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bellicidia incompta</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Borrer) Kistenich et al.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471439</v>
+        <v>471311</v>
       </c>
       <c r="R125" t="n">
-        <v>6609505</v>
+        <v>6609624</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15784,67 +15780,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>surdråg med gråal, skogsalm, gran m.m.</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN125" t="n">
-        <v>1</v>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>1 substratenheter # Bark on living woody plant # Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
+          <t>Asp.</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
         <is>
           <t>Toni Berglund</t>
         </is>
       </c>
-      <c r="AT125" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125580232</v>
+        <v>125638785</v>
       </c>
       <c r="B126" t="n">
-        <v>102498</v>
+        <v>102771</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15853,25 +15812,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>223246</v>
+        <v>222002</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -15886,25 +15845,21 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471458</v>
+        <v>471336</v>
       </c>
       <c r="R126" t="n">
-        <v>6609490</v>
+        <v>6609447</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15931,17 +15886,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>stort träd</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15954,14 +15904,9 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>surdråg med gråal, skogsalm, gran m.m.</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15979,10 +15924,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125556711</v>
+        <v>125638825</v>
       </c>
       <c r="B127" t="n">
-        <v>80063</v>
+        <v>102771</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15995,37 +15940,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6463</v>
+        <v>222002</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471311</v>
+        <v>471334</v>
       </c>
       <c r="R127" t="n">
-        <v>6609624</v>
+        <v>6609447</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16052,12 +16002,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16070,30 +16025,30 @@
       <c r="AG127" t="b">
         <v>0</v>
       </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Asp.</t>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125638785</v>
+        <v>125639036</v>
       </c>
       <c r="B128" t="n">
-        <v>102771</v>
+        <v>95515</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -16106,38 +16061,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -16146,10 +16089,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471336</v>
+        <v>471281</v>
       </c>
       <c r="R128" t="n">
-        <v>6609447</v>
+        <v>6609438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16196,7 +16139,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -16214,10 +16157,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125638825</v>
+        <v>125638438</v>
       </c>
       <c r="B129" t="n">
-        <v>102771</v>
+        <v>98292</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -16230,25 +16173,33 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222002</v>
+        <v>219847</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -16262,10 +16213,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471334</v>
+        <v>471350</v>
       </c>
       <c r="R129" t="n">
-        <v>6609447</v>
+        <v>6609454</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16300,11 +16251,6 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -16317,7 +16263,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16335,10 +16281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125639036</v>
+        <v>125647849</v>
       </c>
       <c r="B130" t="n">
-        <v>95515</v>
+        <v>95127</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -16351,21 +16297,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2813</v>
+        <v>2387</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -16375,14 +16321,14 @@
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>471281</v>
+        <v>471232</v>
       </c>
       <c r="R130" t="n">
-        <v>6609438</v>
+        <v>6609657</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16409,12 +16355,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16427,30 +16373,25 @@
       <c r="AG130" t="b">
         <v>0</v>
       </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>kalkblandskog: gran och gråal</t>
-        </is>
-      </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125638438</v>
+        <v>125638865</v>
       </c>
       <c r="B131" t="n">
-        <v>98292</v>
+        <v>100358</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16463,26 +16404,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219847</v>
+        <v>222771</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -16492,7 +16433,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -16503,10 +16444,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>471350</v>
+        <v>471319</v>
       </c>
       <c r="R131" t="n">
-        <v>6609454</v>
+        <v>6609451</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16553,7 +16494,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -16571,10 +16512,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125647849</v>
+        <v>125639406</v>
       </c>
       <c r="B132" t="n">
-        <v>95127</v>
+        <v>100451</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16587,38 +16528,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2387</v>
+        <v>222498</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>471232</v>
+        <v>471294</v>
       </c>
       <c r="R132" t="n">
-        <v>6609657</v>
+        <v>6609352</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16645,12 +16590,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16663,25 +16608,30 @@
       <c r="AG132" t="b">
         <v>0</v>
       </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125638865</v>
+        <v>125639134</v>
       </c>
       <c r="B133" t="n">
-        <v>100358</v>
+        <v>100451</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16694,36 +16644,28 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -16734,10 +16676,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471319</v>
+        <v>471271</v>
       </c>
       <c r="R133" t="n">
-        <v>6609451</v>
+        <v>6609429</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16781,11 +16723,6 @@
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -16802,10 +16739,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125639406</v>
+        <v>125638320</v>
       </c>
       <c r="B134" t="n">
-        <v>100451</v>
+        <v>101355</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16818,28 +16755,36 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -16850,10 +16795,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>471294</v>
+        <v>471329</v>
       </c>
       <c r="R134" t="n">
-        <v>6609352</v>
+        <v>6609462</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16894,13 +16839,12 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -16918,7 +16862,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125639134</v>
+        <v>125638823</v>
       </c>
       <c r="B135" t="n">
         <v>100451</v>
@@ -16966,10 +16910,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471271</v>
+        <v>471334</v>
       </c>
       <c r="R135" t="n">
-        <v>6609429</v>
+        <v>6609447</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17013,6 +16957,11 @@
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -17029,10 +16978,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125638320</v>
+        <v>125638511</v>
       </c>
       <c r="B136" t="n">
-        <v>101355</v>
+        <v>95503</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -17045,38 +16994,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -17085,10 +17022,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471329</v>
+        <v>471371</v>
       </c>
       <c r="R136" t="n">
-        <v>6609462</v>
+        <v>6609452</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17129,12 +17066,23 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -17152,10 +17100,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125638823</v>
+        <v>125647908</v>
       </c>
       <c r="B137" t="n">
-        <v>100451</v>
+        <v>97008</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -17164,46 +17112,42 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222498</v>
+        <v>2617</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471334</v>
+        <v>471286</v>
       </c>
       <c r="R137" t="n">
-        <v>6609447</v>
+        <v>6609621</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17230,12 +17174,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17248,30 +17192,25 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125638511</v>
+        <v>125638527</v>
       </c>
       <c r="B138" t="n">
-        <v>95503</v>
+        <v>100358</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -17284,26 +17223,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2809</v>
+        <v>222771</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -17363,16 +17314,6 @@
       <c r="AI138" t="inlineStr">
         <is>
           <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17390,10 +17331,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125647908</v>
+        <v>125647784</v>
       </c>
       <c r="B139" t="n">
-        <v>97008</v>
+        <v>96842</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -17402,25 +17343,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2617</v>
+        <v>2326</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -17434,10 +17375,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471286</v>
+        <v>471261</v>
       </c>
       <c r="R139" t="n">
-        <v>6609621</v>
+        <v>6609660</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17470,6 +17411,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17497,10 +17443,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125638527</v>
+        <v>125638375</v>
       </c>
       <c r="B140" t="n">
-        <v>100358</v>
+        <v>95503</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -17513,38 +17459,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -17553,10 +17487,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>471371</v>
+        <v>471329</v>
       </c>
       <c r="R140" t="n">
-        <v>6609452</v>
+        <v>6609462</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17597,13 +17531,12 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17621,10 +17554,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125647784</v>
+        <v>125638908</v>
       </c>
       <c r="B141" t="n">
-        <v>96842</v>
+        <v>102771</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17637,38 +17570,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2326</v>
+        <v>222002</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471261</v>
+        <v>471306</v>
       </c>
       <c r="R141" t="n">
-        <v>6609660</v>
+        <v>6609456</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17695,17 +17632,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Riklig.</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17718,25 +17650,30 @@
       <c r="AG141" t="b">
         <v>0</v>
       </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125638375</v>
+        <v>125639167</v>
       </c>
       <c r="B142" t="n">
-        <v>95503</v>
+        <v>100451</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17749,26 +17686,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -17777,10 +17718,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471329</v>
+        <v>471265</v>
       </c>
       <c r="R142" t="n">
-        <v>6609462</v>
+        <v>6609407</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17821,13 +17762,9 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
@@ -17844,10 +17781,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125638908</v>
+        <v>125638455</v>
       </c>
       <c r="B143" t="n">
-        <v>102771</v>
+        <v>95515</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17860,30 +17797,26 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -17892,10 +17825,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471306</v>
+        <v>471350</v>
       </c>
       <c r="R143" t="n">
-        <v>6609456</v>
+        <v>6609454</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17942,7 +17875,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -17960,10 +17893,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125639167</v>
+        <v>125638618</v>
       </c>
       <c r="B144" t="n">
-        <v>100451</v>
+        <v>101355</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17976,28 +17909,36 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -18008,10 +17949,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471265</v>
+        <v>471408</v>
       </c>
       <c r="R144" t="n">
-        <v>6609407</v>
+        <v>6609463</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18041,9 +17982,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18055,6 +18006,11 @@
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -18071,10 +18027,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125638455</v>
+        <v>125638876</v>
       </c>
       <c r="B145" t="n">
-        <v>95515</v>
+        <v>102771</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -18087,26 +18043,30 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -18115,10 +18075,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471350</v>
+        <v>471319</v>
       </c>
       <c r="R145" t="n">
-        <v>6609454</v>
+        <v>6609451</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18165,7 +18125,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18183,10 +18143,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125638618</v>
+        <v>125639216</v>
       </c>
       <c r="B146" t="n">
-        <v>101355</v>
+        <v>100451</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -18199,36 +18159,28 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -18239,10 +18191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471408</v>
+        <v>471261</v>
       </c>
       <c r="R146" t="n">
-        <v>6609463</v>
+        <v>6609384</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18272,19 +18224,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18296,11 +18238,6 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18317,10 +18254,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125638876</v>
+        <v>125638720</v>
       </c>
       <c r="B147" t="n">
-        <v>102771</v>
+        <v>100358</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18333,16 +18270,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -18350,8 +18287,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18365,10 +18310,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471319</v>
+        <v>471352</v>
       </c>
       <c r="R147" t="n">
-        <v>6609451</v>
+        <v>6609455</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18398,9 +18343,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18415,7 +18370,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18433,10 +18388,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125639216</v>
+        <v>125638819</v>
       </c>
       <c r="B148" t="n">
-        <v>100451</v>
+        <v>101355</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18449,28 +18404,36 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -18481,10 +18444,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471261</v>
+        <v>471334</v>
       </c>
       <c r="R148" t="n">
-        <v>6609384</v>
+        <v>6609447</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18528,6 +18491,11 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18544,10 +18512,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125638720</v>
+        <v>125638580</v>
       </c>
       <c r="B149" t="n">
-        <v>100358</v>
+        <v>95623</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18560,36 +18528,28 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -18600,10 +18560,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471352</v>
+        <v>471393</v>
       </c>
       <c r="R149" t="n">
-        <v>6609455</v>
+        <v>6609458</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18633,19 +18593,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18660,7 +18610,27 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -18678,10 +18648,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125638819</v>
+        <v>125638831</v>
       </c>
       <c r="B150" t="n">
-        <v>101355</v>
+        <v>98292</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18694,26 +18664,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18723,7 +18693,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -18802,10 +18772,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125638580</v>
+        <v>125638463</v>
       </c>
       <c r="B151" t="n">
-        <v>95623</v>
+        <v>101355</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18818,30 +18788,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2818</v>
+        <v>221235</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -18850,10 +18824,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471393</v>
+        <v>471350</v>
       </c>
       <c r="R151" t="n">
-        <v>6609458</v>
+        <v>6609454</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18900,27 +18874,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Stump # murken stubbe # Picea abies</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -18938,10 +18892,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125638831</v>
+        <v>125638903</v>
       </c>
       <c r="B152" t="n">
-        <v>98292</v>
+        <v>100358</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18954,26 +18908,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>219847</v>
+        <v>222771</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18983,7 +18937,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -18994,10 +18948,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>471334</v>
+        <v>471306</v>
       </c>
       <c r="R152" t="n">
-        <v>6609447</v>
+        <v>6609456</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19044,7 +18998,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -19062,10 +19016,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125638463</v>
+        <v>125638917</v>
       </c>
       <c r="B153" t="n">
-        <v>101355</v>
+        <v>103700</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -19078,21 +19032,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -19105,7 +19059,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -19114,10 +19072,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471350</v>
+        <v>471306</v>
       </c>
       <c r="R153" t="n">
-        <v>6609454</v>
+        <v>6609456</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -19164,7 +19122,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -19182,10 +19140,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125638903</v>
+        <v>125638915</v>
       </c>
       <c r="B154" t="n">
-        <v>100358</v>
+        <v>100451</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -19198,36 +19156,28 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -19306,10 +19256,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125638917</v>
+        <v>125638955</v>
       </c>
       <c r="B155" t="n">
-        <v>103700</v>
+        <v>101355</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19322,26 +19272,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -19351,7 +19301,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -19362,10 +19312,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>471306</v>
+        <v>471281</v>
       </c>
       <c r="R155" t="n">
-        <v>6609456</v>
+        <v>6609438</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -19430,10 +19380,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125638915</v>
+        <v>125638457</v>
       </c>
       <c r="B156" t="n">
-        <v>100451</v>
+        <v>95503</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19446,30 +19396,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -19478,10 +19424,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471306</v>
+        <v>471350</v>
       </c>
       <c r="R156" t="n">
-        <v>6609456</v>
+        <v>6609454</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19528,7 +19474,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -19546,10 +19492,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125638955</v>
+        <v>125647918</v>
       </c>
       <c r="B157" t="n">
-        <v>101355</v>
+        <v>96747</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19558,54 +19504,42 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221235</v>
+        <v>231</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blå säckmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Calypogeia azurea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Stotler &amp; Crotz</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471281</v>
+        <v>471286</v>
       </c>
       <c r="R157" t="n">
-        <v>6609438</v>
+        <v>6609621</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19632,12 +19566,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19650,27 +19584,22 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125638457</v>
+        <v>125638551</v>
       </c>
       <c r="B158" t="n">
         <v>95503</v>
@@ -19714,10 +19643,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>471350</v>
+        <v>471386</v>
       </c>
       <c r="R158" t="n">
-        <v>6609454</v>
+        <v>6609448</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19764,7 +19693,17 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -19782,10 +19721,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125647918</v>
+        <v>125639232</v>
       </c>
       <c r="B159" t="n">
-        <v>96747</v>
+        <v>100451</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19794,42 +19733,46 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>231</v>
+        <v>222498</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blå säckmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Calypogeia azurea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Stotler &amp; Crotz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471286</v>
+        <v>471252</v>
       </c>
       <c r="R159" t="n">
-        <v>6609621</v>
+        <v>6609379</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19856,12 +19799,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19877,22 +19820,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125638551</v>
+        <v>125638771</v>
       </c>
       <c r="B160" t="n">
-        <v>95503</v>
+        <v>101355</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19905,26 +19848,38 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
@@ -19933,10 +19888,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471386</v>
+        <v>471336</v>
       </c>
       <c r="R160" t="n">
-        <v>6609448</v>
+        <v>6609447</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19984,16 +19939,6 @@
       <c r="AI160" t="inlineStr">
         <is>
           <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -20011,10 +19956,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125639232</v>
+        <v>125638348</v>
       </c>
       <c r="B161" t="n">
-        <v>100451</v>
+        <v>98292</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -20027,25 +19972,33 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -20059,10 +20012,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471252</v>
+        <v>471329</v>
       </c>
       <c r="R161" t="n">
-        <v>6609379</v>
+        <v>6609462</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -20103,9 +20056,13 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten med surdråg</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
@@ -20122,10 +20079,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125638771</v>
+        <v>125638940</v>
       </c>
       <c r="B162" t="n">
-        <v>101355</v>
+        <v>100451</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -20138,36 +20095,28 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -20178,10 +20127,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471336</v>
+        <v>471288</v>
       </c>
       <c r="R162" t="n">
-        <v>6609447</v>
+        <v>6609428</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -20228,7 +20177,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -20246,10 +20195,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125638348</v>
+        <v>125638893</v>
       </c>
       <c r="B163" t="n">
-        <v>98292</v>
+        <v>101355</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20262,26 +20211,26 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -20291,7 +20240,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -20302,10 +20251,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471329</v>
+        <v>471306</v>
       </c>
       <c r="R163" t="n">
-        <v>6609462</v>
+        <v>6609456</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -20346,12 +20295,13 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -20369,10 +20319,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125639147</v>
+        <v>125639081</v>
       </c>
       <c r="B164" t="n">
-        <v>101355</v>
+        <v>100451</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20385,36 +20335,28 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -20425,10 +20367,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471271</v>
+        <v>471281</v>
       </c>
       <c r="R164" t="n">
-        <v>6609429</v>
+        <v>6609438</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20472,6 +20414,11 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>kalkblandskog: gran och gråal</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -20488,10 +20435,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125639081</v>
+        <v>125639147</v>
       </c>
       <c r="B165" t="n">
-        <v>100451</v>
+        <v>101355</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20504,28 +20451,36 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -20536,10 +20491,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471281</v>
+        <v>471271</v>
       </c>
       <c r="R165" t="n">
-        <v>6609438</v>
+        <v>6609429</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20583,11 +20538,6 @@
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>kalkblandskog: gran och gråal</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -20604,10 +20554,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125638940</v>
+        <v>125638871</v>
       </c>
       <c r="B166" t="n">
-        <v>100451</v>
+        <v>101355</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20620,25 +20570,33 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -20652,10 +20610,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471288</v>
+        <v>471319</v>
       </c>
       <c r="R166" t="n">
-        <v>6609428</v>
+        <v>6609451</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20720,10 +20678,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125638893</v>
+        <v>125638361</v>
       </c>
       <c r="B167" t="n">
-        <v>101355</v>
+        <v>102771</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -20736,26 +20694,26 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -20765,7 +20723,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -20776,10 +20734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471306</v>
+        <v>471329</v>
       </c>
       <c r="R167" t="n">
-        <v>6609456</v>
+        <v>6609462</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20820,13 +20778,12 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -20844,7 +20801,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125638871</v>
+        <v>125639177</v>
       </c>
       <c r="B168" t="n">
         <v>101355</v>
@@ -20879,7 +20836,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -20900,10 +20857,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471319</v>
+        <v>471265</v>
       </c>
       <c r="R168" t="n">
-        <v>6609451</v>
+        <v>6609407</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20947,11 +20904,6 @@
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -20968,10 +20920,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125639177</v>
+        <v>125638625</v>
       </c>
       <c r="B169" t="n">
-        <v>101355</v>
+        <v>100358</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -20984,26 +20936,26 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -21024,10 +20976,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471265</v>
+        <v>471408</v>
       </c>
       <c r="R169" t="n">
-        <v>6609407</v>
+        <v>6609463</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -21057,9 +21009,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -21071,6 +21033,11 @@
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -21087,10 +21054,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125638361</v>
+        <v>125638867</v>
       </c>
       <c r="B170" t="n">
-        <v>102771</v>
+        <v>100451</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -21103,33 +21070,25 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -21143,10 +21102,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471329</v>
+        <v>471319</v>
       </c>
       <c r="R170" t="n">
-        <v>6609462</v>
+        <v>6609451</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -21187,12 +21146,13 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -21210,10 +21170,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125638625</v>
+        <v>125647825</v>
       </c>
       <c r="B171" t="n">
-        <v>100358</v>
+        <v>96522</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -21222,54 +21182,42 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222771</v>
+        <v>53</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471408</v>
+        <v>471311</v>
       </c>
       <c r="R171" t="n">
-        <v>6609463</v>
+        <v>6609467</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -21296,22 +21244,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21324,30 +21262,30 @@
       <c r="AG171" t="b">
         <v>0</v>
       </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125638867</v>
+        <v>125639241</v>
       </c>
       <c r="B172" t="n">
-        <v>100451</v>
+        <v>98292</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -21360,25 +21298,33 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -21392,10 +21338,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471319</v>
+        <v>471252</v>
       </c>
       <c r="R172" t="n">
-        <v>6609451</v>
+        <v>6609379</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -21439,11 +21385,6 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
@@ -21460,10 +21401,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125647825</v>
+        <v>125638600</v>
       </c>
       <c r="B173" t="n">
-        <v>96522</v>
+        <v>100358</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -21472,42 +21413,54 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>53</v>
+        <v>222771</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471311</v>
+        <v>471393</v>
       </c>
       <c r="R173" t="n">
-        <v>6609467</v>
+        <v>6609458</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -21534,12 +21487,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21552,75 +21515,71 @@
       <c r="AG173" t="b">
         <v>0</v>
       </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125639241</v>
+        <v>125450120</v>
       </c>
       <c r="B174" t="n">
-        <v>98292</v>
+        <v>57793</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
@@ -21628,13 +21587,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471252</v>
+        <v>471311</v>
       </c>
       <c r="R174" t="n">
-        <v>6609379</v>
+        <v>6609559</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -21661,20 +21620,39 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>sång</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
@@ -21688,140 +21666,6 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>125638600</v>
-      </c>
-      <c r="B175" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
-        </is>
-      </c>
-      <c r="Q175" t="n">
-        <v>471393</v>
-      </c>
-      <c r="R175" t="n">
-        <v>6609458</v>
-      </c>
-      <c r="S175" t="n">
-        <v>10</v>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>Hällefors</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>Grythyttan</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AD175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF175" t="inlineStr"/>
-      <c r="AG175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AT175" t="inlineStr"/>
-      <c r="AW175" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AX175" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY174"/>
+  <dimension ref="A1:AY239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8894,7 +8894,7 @@
         <v>121698315</v>
       </c>
       <c r="B70" t="n">
-        <v>97095</v>
+        <v>97141</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8907,23 +8907,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>224361</v>
+        <v>221944</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -9300,7 +9296,7 @@
         <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>97095</v>
+        <v>97141</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9313,23 +9309,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224361</v>
+        <v>221944</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -9417,7 +9409,7 @@
         <v>121698313</v>
       </c>
       <c r="B74" t="n">
-        <v>97095</v>
+        <v>97141</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9430,23 +9422,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224361</v>
+        <v>221944</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -13532,10 +13520,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125457972</v>
+        <v>125450472</v>
       </c>
       <c r="B108" t="n">
-        <v>102498</v>
+        <v>95623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13544,40 +13532,32 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>223246</v>
+        <v>2818</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -13588,10 +13568,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471435</v>
+        <v>471370</v>
       </c>
       <c r="R108" t="n">
-        <v>6609510</v>
+        <v>6609456</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13621,14 +13601,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Två telningar och fem klena, unga träd.</t>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13641,14 +13626,32 @@
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13666,10 +13669,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125450472</v>
+        <v>125457972</v>
       </c>
       <c r="B109" t="n">
-        <v>95623</v>
+        <v>102498</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13678,32 +13681,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2818</v>
+        <v>223246</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -13714,10 +13725,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471370</v>
+        <v>471435</v>
       </c>
       <c r="R109" t="n">
-        <v>6609456</v>
+        <v>6609510</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13747,19 +13758,14 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>08:40</t>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Två telningar och fem klena, unga träd.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13772,32 +13778,14 @@
       <c r="AG109" t="b">
         <v>0</v>
       </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN109" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
+          <t>Surdråg med gråal, gran, rönn, skogsalm, skogslind och skogslönn</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -17781,10 +17769,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125638455</v>
+        <v>125638618</v>
       </c>
       <c r="B143" t="n">
-        <v>95515</v>
+        <v>101355</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17797,26 +17785,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2813</v>
+        <v>221235</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -17825,10 +17825,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471350</v>
+        <v>471408</v>
       </c>
       <c r="R143" t="n">
-        <v>6609454</v>
+        <v>6609463</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17858,9 +17858,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17875,7 +17885,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -17893,10 +17903,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125638618</v>
+        <v>125638876</v>
       </c>
       <c r="B144" t="n">
-        <v>101355</v>
+        <v>102771</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17909,36 +17919,28 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -17949,10 +17951,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471408</v>
+        <v>471319</v>
       </c>
       <c r="R144" t="n">
-        <v>6609463</v>
+        <v>6609451</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17982,19 +17984,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18027,10 +18019,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125638876</v>
+        <v>125639216</v>
       </c>
       <c r="B145" t="n">
-        <v>102771</v>
+        <v>100451</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -18043,21 +18035,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -18075,10 +18067,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471319</v>
+        <v>471261</v>
       </c>
       <c r="R145" t="n">
-        <v>6609451</v>
+        <v>6609384</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18122,11 +18114,6 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18143,10 +18130,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125639216</v>
+        <v>125638455</v>
       </c>
       <c r="B146" t="n">
-        <v>100451</v>
+        <v>95515</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -18159,30 +18146,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -18191,10 +18174,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471261</v>
+        <v>471350</v>
       </c>
       <c r="R146" t="n">
-        <v>6609384</v>
+        <v>6609454</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18238,6 +18221,11 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -19256,10 +19244,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125638955</v>
+        <v>125647918</v>
       </c>
       <c r="B155" t="n">
-        <v>101355</v>
+        <v>96747</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19268,54 +19256,42 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221235</v>
+        <v>231</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blå säckmossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Calypogeia azurea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Stotler &amp; Crotz</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>471281</v>
+        <v>471286</v>
       </c>
       <c r="R155" t="n">
-        <v>6609438</v>
+        <v>6609621</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -19342,12 +19318,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19360,30 +19336,25 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125638457</v>
+        <v>125638955</v>
       </c>
       <c r="B156" t="n">
-        <v>95503</v>
+        <v>101355</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19396,26 +19367,38 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -19424,10 +19407,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471350</v>
+        <v>471281</v>
       </c>
       <c r="R156" t="n">
-        <v>6609454</v>
+        <v>6609438</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19474,7 +19457,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -19492,10 +19475,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125647918</v>
+        <v>125638457</v>
       </c>
       <c r="B157" t="n">
-        <v>96747</v>
+        <v>95503</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19504,25 +19487,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>231</v>
+        <v>2809</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blå säckmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Calypogeia azurea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Stotler &amp; Crotz</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -19532,14 +19515,14 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471286</v>
+        <v>471350</v>
       </c>
       <c r="R157" t="n">
-        <v>6609621</v>
+        <v>6609454</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19566,12 +19549,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19584,15 +19567,20 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -21667,6 +21655,7517 @@
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>125693203</v>
+      </c>
+      <c r="B175" t="n">
+        <v>103700</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6609562</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>125691752</v>
+      </c>
+      <c r="B176" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6609440</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>125691658</v>
+      </c>
+      <c r="B177" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>471309</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6609409</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>125691600</v>
+      </c>
+      <c r="B178" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>471299</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>125691638</v>
+      </c>
+      <c r="B179" t="n">
+        <v>95623</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>471299</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>125692324</v>
+      </c>
+      <c r="B180" t="n">
+        <v>106640</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>471446</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6609377</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>125691596</v>
+      </c>
+      <c r="B181" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>471299</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>125693046</v>
+      </c>
+      <c r="B182" t="n">
+        <v>97147</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>471207</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6609720</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>125693086</v>
+      </c>
+      <c r="B183" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>471336</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6609592</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>125692396</v>
+      </c>
+      <c r="B184" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>471375</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6609431</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>125692169</v>
+      </c>
+      <c r="B185" t="n">
+        <v>98292</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>471438</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6609315</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>Källkärr</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>125692508</v>
+      </c>
+      <c r="B186" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>471352</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6609490</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>125688723</v>
+      </c>
+      <c r="B187" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>471312</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6609616</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>125692947</v>
+      </c>
+      <c r="B188" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>471213</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6609721</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>125692378</v>
+      </c>
+      <c r="B189" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>471440</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6609375</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>125691817</v>
+      </c>
+      <c r="B190" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>471334</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6609428</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>125691824</v>
+      </c>
+      <c r="B191" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>471334</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6609428</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>125692269</v>
+      </c>
+      <c r="B192" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>471437</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6609338</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>125693090</v>
+      </c>
+      <c r="B193" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>471336</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6609592</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>125694224</v>
+      </c>
+      <c r="B194" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>471320</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6609374</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>125692924</v>
+      </c>
+      <c r="B195" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>471200</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6609727</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>125692474</v>
+      </c>
+      <c r="B196" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>471368</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6609493</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>125691551</v>
+      </c>
+      <c r="B197" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>471277</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6609410</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>125691940</v>
+      </c>
+      <c r="B198" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>471421</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6609338</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>125691487</v>
+      </c>
+      <c r="B199" t="n">
+        <v>98292</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>471256</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6609375</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>125691768</v>
+      </c>
+      <c r="B200" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6609440</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>125691650</v>
+      </c>
+      <c r="B201" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>471309</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6609409</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>125691678</v>
+      </c>
+      <c r="B202" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>471307</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6609405</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>125691883</v>
+      </c>
+      <c r="B203" t="n">
+        <v>103700</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>471342</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6609418</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>125692480</v>
+      </c>
+      <c r="B204" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>471368</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6609493</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>125691701</v>
+      </c>
+      <c r="B205" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>471323</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6609406</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>125694447</v>
+      </c>
+      <c r="B206" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6609388</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>125691724</v>
+      </c>
+      <c r="B207" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>471295</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6609415</v>
+      </c>
+      <c r="S207" t="n">
+        <v>10</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>125692746</v>
+      </c>
+      <c r="B208" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>471175</v>
+      </c>
+      <c r="R208" t="n">
+        <v>6609737</v>
+      </c>
+      <c r="S208" t="n">
+        <v>10</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>125694768</v>
+      </c>
+      <c r="B209" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>471450</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6609501</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>125691756</v>
+      </c>
+      <c r="B210" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>471316</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6609440</v>
+      </c>
+      <c r="S210" t="n">
+        <v>10</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>125691555</v>
+      </c>
+      <c r="B211" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>471277</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6609410</v>
+      </c>
+      <c r="S211" t="n">
+        <v>10</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>125691568</v>
+      </c>
+      <c r="B212" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>471299</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S212" t="n">
+        <v>10</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>125691655</v>
+      </c>
+      <c r="B213" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>471309</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6609409</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>125691532</v>
+      </c>
+      <c r="B214" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>471263</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6609389</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>125694704</v>
+      </c>
+      <c r="B215" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>471383</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6609437</v>
+      </c>
+      <c r="S215" t="n">
+        <v>10</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>blockrik kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>125693113</v>
+      </c>
+      <c r="B216" t="n">
+        <v>106640</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>471338</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6609551</v>
+      </c>
+      <c r="S216" t="n">
+        <v>10</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>125692503</v>
+      </c>
+      <c r="B217" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>471352</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6609490</v>
+      </c>
+      <c r="S217" t="n">
+        <v>10</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>många</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>125691504</v>
+      </c>
+      <c r="B218" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>471256</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6609375</v>
+      </c>
+      <c r="S218" t="n">
+        <v>10</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>125693285</v>
+      </c>
+      <c r="B219" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>471321</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6609614</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>125691545</v>
+      </c>
+      <c r="B220" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>471275</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6609399</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>125692234</v>
+      </c>
+      <c r="B221" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>471438</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6609323</v>
+      </c>
+      <c r="S221" t="n">
+        <v>10</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>125693289</v>
+      </c>
+      <c r="B222" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6609611</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>125694805</v>
+      </c>
+      <c r="B223" t="n">
+        <v>102498</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>471442</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6609507</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>klent träd</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>125692655</v>
+      </c>
+      <c r="B224" t="n">
+        <v>95624</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>2819</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Trind spretmossa</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Herzogiella striatella</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>471404</v>
+      </c>
+      <c r="R224" t="n">
+        <v>6609514</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>125694456</v>
+      </c>
+      <c r="B225" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6609388</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>125688737</v>
+      </c>
+      <c r="B226" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>471312</v>
+      </c>
+      <c r="R226" t="n">
+        <v>6609616</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>125692901</v>
+      </c>
+      <c r="B227" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>471195</v>
+      </c>
+      <c r="R227" t="n">
+        <v>6609738</v>
+      </c>
+      <c r="S227" t="n">
+        <v>10</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>125693283</v>
+      </c>
+      <c r="B228" t="n">
+        <v>95623</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>471321</v>
+      </c>
+      <c r="R228" t="n">
+        <v>6609614</v>
+      </c>
+      <c r="S228" t="n">
+        <v>10</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>125691671</v>
+      </c>
+      <c r="B229" t="n">
+        <v>101355</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>471307</v>
+      </c>
+      <c r="R229" t="n">
+        <v>6609405</v>
+      </c>
+      <c r="S229" t="n">
+        <v>10</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>125691775</v>
+      </c>
+      <c r="B230" t="n">
+        <v>106640</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>471330</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6609444</v>
+      </c>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>under gran</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>125692758</v>
+      </c>
+      <c r="B231" t="n">
+        <v>95515</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>471191</v>
+      </c>
+      <c r="R231" t="n">
+        <v>6609737</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>125693315</v>
+      </c>
+      <c r="B232" t="n">
+        <v>95624</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>2819</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Trind spretmossa</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Herzogiella striatella</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R232" t="n">
+        <v>6609611</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>125691689</v>
+      </c>
+      <c r="B233" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>471315</v>
+      </c>
+      <c r="R233" t="n">
+        <v>6609406</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>125691675</v>
+      </c>
+      <c r="B234" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>471307</v>
+      </c>
+      <c r="R234" t="n">
+        <v>6609405</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>125691522</v>
+      </c>
+      <c r="B235" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>471257</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6609382</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF235" t="inlineStr"/>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>125693221</v>
+      </c>
+      <c r="B236" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>471325</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6609612</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>125692303</v>
+      </c>
+      <c r="B237" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>471447</v>
+      </c>
+      <c r="R237" t="n">
+        <v>6609354</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>125691772</v>
+      </c>
+      <c r="B238" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>471330</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6609444</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>125691592</v>
+      </c>
+      <c r="B239" t="n">
+        <v>100358</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>471299</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6609407</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -12233,10 +12233,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125151077</v>
+        <v>125148997</v>
       </c>
       <c r="B98" t="n">
-        <v>100506</v>
+        <v>100413</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12244,25 +12244,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12276,10 +12284,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471343</v>
+        <v>471337</v>
       </c>
       <c r="R98" t="n">
-        <v>6609410</v>
+        <v>6609424</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12349,10 +12357,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125148997</v>
+        <v>125151077</v>
       </c>
       <c r="B99" t="n">
-        <v>100413</v>
+        <v>100506</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12360,33 +12368,25 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12400,10 +12400,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471337</v>
+        <v>471343</v>
       </c>
       <c r="R99" t="n">
-        <v>6609424</v>
+        <v>6609410</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -18000,10 +18000,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125639167</v>
+        <v>125638893</v>
       </c>
       <c r="B147" t="n">
-        <v>100506</v>
+        <v>101410</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18011,28 +18011,36 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -18043,10 +18051,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471265</v>
+        <v>471306</v>
       </c>
       <c r="R147" t="n">
-        <v>6609407</v>
+        <v>6609456</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18090,6 +18098,11 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18106,10 +18119,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125638893</v>
+        <v>125639167</v>
       </c>
       <c r="B148" t="n">
-        <v>101410</v>
+        <v>100506</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18117,36 +18130,28 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -18157,10 +18162,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471306</v>
+        <v>471265</v>
       </c>
       <c r="R148" t="n">
-        <v>6609456</v>
+        <v>6609407</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18204,11 +18209,6 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18225,61 +18225,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125638527</v>
+        <v>125647918</v>
       </c>
       <c r="B149" t="n">
-        <v>100413</v>
+        <v>96802</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222771</v>
+        <v>231</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blå säckmossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Calypogeia azurea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Stotler &amp; Crotz</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471371</v>
+        <v>471286</v>
       </c>
       <c r="R149" t="n">
-        <v>6609452</v>
+        <v>6609621</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18306,12 +18294,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18324,30 +18312,25 @@
       <c r="AG149" t="b">
         <v>0</v>
       </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125638785</v>
+        <v>125638527</v>
       </c>
       <c r="B150" t="n">
-        <v>102826</v>
+        <v>100413</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18355,16 +18338,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -18384,7 +18367,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -18395,10 +18378,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471336</v>
+        <v>471371</v>
       </c>
       <c r="R150" t="n">
-        <v>6609447</v>
+        <v>6609452</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18463,49 +18446,61 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125647918</v>
+        <v>125638785</v>
       </c>
       <c r="B151" t="n">
-        <v>96802</v>
+        <v>102826</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>231</v>
+        <v>222002</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blå säckmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Calypogeia azurea</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Stotler &amp; Crotz</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471286</v>
+        <v>471336</v>
       </c>
       <c r="R151" t="n">
-        <v>6609621</v>
+        <v>6609447</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18532,12 +18527,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18550,25 +18545,30 @@
       <c r="AG151" t="b">
         <v>0</v>
       </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125638600</v>
+        <v>125638867</v>
       </c>
       <c r="B152" t="n">
-        <v>100413</v>
+        <v>100506</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18576,33 +18576,25 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18616,10 +18608,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>471393</v>
+        <v>471319</v>
       </c>
       <c r="R152" t="n">
-        <v>6609458</v>
+        <v>6609451</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18649,19 +18641,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18694,10 +18676,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125638867</v>
+        <v>125638600</v>
       </c>
       <c r="B153" t="n">
-        <v>100506</v>
+        <v>100413</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18705,25 +18687,33 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18737,10 +18727,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471319</v>
+        <v>471393</v>
       </c>
       <c r="R153" t="n">
-        <v>6609451</v>
+        <v>6609458</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18770,9 +18760,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19026,10 +19026,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125638438</v>
+        <v>125638320</v>
       </c>
       <c r="B156" t="n">
-        <v>98347</v>
+        <v>101410</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19037,26 +19037,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -19077,10 +19077,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471350</v>
+        <v>471329</v>
       </c>
       <c r="R156" t="n">
-        <v>6609454</v>
+        <v>6609462</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19121,13 +19121,12 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -19145,10 +19144,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125638320</v>
+        <v>125638438</v>
       </c>
       <c r="B157" t="n">
-        <v>101410</v>
+        <v>98347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19156,26 +19155,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -19185,7 +19184,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -19196,10 +19195,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471329</v>
+        <v>471350</v>
       </c>
       <c r="R157" t="n">
-        <v>6609462</v>
+        <v>6609454</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19240,12 +19239,13 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -19751,10 +19751,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125639134</v>
+        <v>125638831</v>
       </c>
       <c r="B162" t="n">
-        <v>100506</v>
+        <v>98347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19762,25 +19762,33 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19794,10 +19802,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471271</v>
+        <v>471334</v>
       </c>
       <c r="R162" t="n">
-        <v>6609429</v>
+        <v>6609447</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19841,6 +19849,11 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -19857,10 +19870,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125638831</v>
+        <v>125639134</v>
       </c>
       <c r="B163" t="n">
-        <v>98347</v>
+        <v>100506</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19868,33 +19881,25 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19908,10 +19913,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471334</v>
+        <v>471271</v>
       </c>
       <c r="R163" t="n">
-        <v>6609447</v>
+        <v>6609429</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19955,11 +19960,6 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -21242,10 +21242,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125691817</v>
+        <v>125691568</v>
       </c>
       <c r="B175" t="n">
-        <v>101410</v>
+        <v>100506</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21253,26 +21253,26 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21293,10 +21293,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471334</v>
+        <v>471299</v>
       </c>
       <c r="R175" t="n">
-        <v>6609428</v>
+        <v>6609407</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21356,10 +21356,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125692508</v>
+        <v>125691817</v>
       </c>
       <c r="B176" t="n">
-        <v>100413</v>
+        <v>101410</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21367,26 +21367,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -21407,10 +21407,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471352</v>
+        <v>471334</v>
       </c>
       <c r="R176" t="n">
-        <v>6609490</v>
+        <v>6609428</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -21470,10 +21470,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125691568</v>
+        <v>125692508</v>
       </c>
       <c r="B177" t="n">
-        <v>100506</v>
+        <v>100413</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21481,21 +21481,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -21521,10 +21521,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471299</v>
+        <v>471352</v>
       </c>
       <c r="R177" t="n">
-        <v>6609407</v>
+        <v>6609490</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -23687,10 +23687,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125691655</v>
+        <v>125693289</v>
       </c>
       <c r="B197" t="n">
-        <v>102826</v>
+        <v>100506</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23698,24 +23698,28 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -23730,10 +23734,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471309</v>
+        <v>471315</v>
       </c>
       <c r="R197" t="n">
-        <v>6609409</v>
+        <v>6609611</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23793,7 +23797,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125693289</v>
+        <v>125692378</v>
       </c>
       <c r="B198" t="n">
         <v>100506</v>
@@ -23821,11 +23825,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
@@ -23840,10 +23840,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471315</v>
+        <v>471440</v>
       </c>
       <c r="R198" t="n">
-        <v>6609611</v>
+        <v>6609375</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23903,7 +23903,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125692378</v>
+        <v>125691756</v>
       </c>
       <c r="B199" t="n">
         <v>100506</v>
@@ -23946,10 +23946,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471440</v>
+        <v>471316</v>
       </c>
       <c r="R199" t="n">
-        <v>6609375</v>
+        <v>6609440</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24009,10 +24009,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125691756</v>
+        <v>125691655</v>
       </c>
       <c r="B200" t="n">
-        <v>100506</v>
+        <v>102826</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24020,21 +24020,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -24052,10 +24052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471316</v>
+        <v>471309</v>
       </c>
       <c r="R200" t="n">
-        <v>6609440</v>
+        <v>6609409</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24115,10 +24115,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125692924</v>
+        <v>125694447</v>
       </c>
       <c r="B201" t="n">
-        <v>95569</v>
+        <v>100506</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24126,26 +24126,30 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -24154,10 +24158,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471200</v>
+        <v>471315</v>
       </c>
       <c r="R201" t="n">
-        <v>6609727</v>
+        <v>6609388</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24184,12 +24188,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24201,6 +24205,11 @@
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -24217,10 +24226,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125691675</v>
+        <v>125691940</v>
       </c>
       <c r="B202" t="n">
-        <v>102826</v>
+        <v>100506</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24228,21 +24237,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -24260,10 +24269,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>471307</v>
+        <v>471421</v>
       </c>
       <c r="R202" t="n">
-        <v>6609405</v>
+        <v>6609338</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24323,10 +24332,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125694447</v>
+        <v>125691675</v>
       </c>
       <c r="B203" t="n">
-        <v>100506</v>
+        <v>102826</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24334,21 +24343,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -24366,10 +24375,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>471315</v>
+        <v>471307</v>
       </c>
       <c r="R203" t="n">
-        <v>6609388</v>
+        <v>6609405</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24396,12 +24405,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -24413,11 +24422,6 @@
       <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
@@ -24434,10 +24438,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125691940</v>
+        <v>125692924</v>
       </c>
       <c r="B204" t="n">
-        <v>100506</v>
+        <v>95569</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24445,30 +24449,26 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
@@ -24477,10 +24477,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471421</v>
+        <v>471200</v>
       </c>
       <c r="R204" t="n">
-        <v>6609338</v>
+        <v>6609727</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -25845,37 +25845,37 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>125694805</v>
+        <v>125693113</v>
       </c>
       <c r="B217" t="n">
-        <v>102553</v>
+        <v>106695</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>223246</v>
+        <v>219686</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -25885,7 +25885,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -25896,10 +25896,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471442</v>
+        <v>471338</v>
       </c>
       <c r="R217" t="n">
-        <v>6609507</v>
+        <v>6609551</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25926,17 +25926,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>klent träd</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25964,10 +25959,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>125693113</v>
+        <v>125691883</v>
       </c>
       <c r="B218" t="n">
-        <v>106695</v>
+        <v>103755</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25975,16 +25970,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>219686</v>
+        <v>222412</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -25994,7 +25989,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -26004,7 +25999,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -26015,10 +26010,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471338</v>
+        <v>471342</v>
       </c>
       <c r="R218" t="n">
-        <v>6609551</v>
+        <v>6609418</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -26078,32 +26073,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>125691883</v>
+        <v>125694805</v>
       </c>
       <c r="B219" t="n">
-        <v>103755</v>
+        <v>102553</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>222412</v>
+        <v>223246</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -26129,10 +26124,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471342</v>
+        <v>471442</v>
       </c>
       <c r="R219" t="n">
-        <v>6609418</v>
+        <v>6609507</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -26159,12 +26154,17 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>klent träd</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26306,10 +26306,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>125692169</v>
+        <v>125692758</v>
       </c>
       <c r="B221" t="n">
-        <v>98347</v>
+        <v>95569</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26317,38 +26317,26 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>219847</v>
+        <v>2813</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
@@ -26357,10 +26345,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471438</v>
+        <v>471191</v>
       </c>
       <c r="R221" t="n">
-        <v>6609315</v>
+        <v>6609737</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26401,13 +26389,9 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>Källkärr</t>
-        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
@@ -26424,10 +26408,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>125691678</v>
+        <v>125692169</v>
       </c>
       <c r="B222" t="n">
-        <v>100506</v>
+        <v>98347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26435,25 +26419,33 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K222" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -26467,10 +26459,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>471307</v>
+        <v>471438</v>
       </c>
       <c r="R222" t="n">
-        <v>6609405</v>
+        <v>6609315</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26511,9 +26503,13 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>Källkärr</t>
+        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
@@ -26530,7 +26526,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>125691689</v>
+        <v>125691678</v>
       </c>
       <c r="B223" t="n">
         <v>100506</v>
@@ -26573,10 +26569,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471315</v>
+        <v>471307</v>
       </c>
       <c r="R223" t="n">
-        <v>6609406</v>
+        <v>6609405</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26636,7 +26632,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>125694768</v>
+        <v>125691689</v>
       </c>
       <c r="B224" t="n">
         <v>100506</v>
@@ -26679,10 +26675,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>471450</v>
+        <v>471315</v>
       </c>
       <c r="R224" t="n">
-        <v>6609501</v>
+        <v>6609406</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26709,12 +26705,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26726,16 +26722,6 @@
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>surdråg</t>
-        </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
@@ -26752,10 +26738,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>125692758</v>
+        <v>125694768</v>
       </c>
       <c r="B225" t="n">
-        <v>95569</v>
+        <v>100506</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26763,26 +26749,30 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
@@ -26791,10 +26781,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>471191</v>
+        <v>471450</v>
       </c>
       <c r="R225" t="n">
-        <v>6609737</v>
+        <v>6609501</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26821,12 +26811,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26838,6 +26828,16 @@
       <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
@@ -27752,10 +27752,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>125691824</v>
+        <v>125691658</v>
       </c>
       <c r="B234" t="n">
-        <v>100506</v>
+        <v>101410</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27763,28 +27763,36 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -27795,10 +27803,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>471334</v>
+        <v>471309</v>
       </c>
       <c r="R234" t="n">
-        <v>6609428</v>
+        <v>6609409</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27858,7 +27866,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>125693090</v>
+        <v>125691824</v>
       </c>
       <c r="B235" t="n">
         <v>100506</v>
@@ -27901,10 +27909,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>471336</v>
+        <v>471334</v>
       </c>
       <c r="R235" t="n">
-        <v>6609592</v>
+        <v>6609428</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27964,7 +27972,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>125691551</v>
+        <v>125693090</v>
       </c>
       <c r="B236" t="n">
         <v>100506</v>
@@ -27992,11 +28000,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
@@ -28011,10 +28015,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>471277</v>
+        <v>471336</v>
       </c>
       <c r="R236" t="n">
-        <v>6609410</v>
+        <v>6609592</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -28074,10 +28078,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>125691658</v>
+        <v>125691551</v>
       </c>
       <c r="B237" t="n">
-        <v>101410</v>
+        <v>100506</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28085,36 +28089,32 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -28125,10 +28125,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>471309</v>
+        <v>471277</v>
       </c>
       <c r="R237" t="n">
-        <v>6609409</v>
+        <v>6609410</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -8894,7 +8894,7 @@
         <v>121698315</v>
       </c>
       <c r="B70" t="n">
-        <v>97196</v>
+        <v>97203</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>97196</v>
+        <v>97203</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>121698313</v>
       </c>
       <c r="B74" t="n">
-        <v>97196</v>
+        <v>97203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11985,10 +11985,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125151113</v>
+        <v>125151014</v>
       </c>
       <c r="B96" t="n">
-        <v>106695</v>
+        <v>101417</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11996,26 +11996,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12036,10 +12036,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471438</v>
+        <v>471342</v>
       </c>
       <c r="R96" t="n">
-        <v>6609330</v>
+        <v>6609418</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12109,10 +12109,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125151014</v>
+        <v>125151113</v>
       </c>
       <c r="B97" t="n">
-        <v>101410</v>
+        <v>106702</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12120,26 +12120,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221235</v>
+        <v>219686</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12160,10 +12160,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471342</v>
+        <v>471438</v>
       </c>
       <c r="R97" t="n">
-        <v>6609418</v>
+        <v>6609330</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12233,10 +12233,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125148997</v>
+        <v>125151077</v>
       </c>
       <c r="B98" t="n">
-        <v>100413</v>
+        <v>100513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12244,33 +12244,25 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12284,10 +12276,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471337</v>
+        <v>471343</v>
       </c>
       <c r="R98" t="n">
-        <v>6609424</v>
+        <v>6609410</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12357,10 +12349,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125151077</v>
+        <v>125148997</v>
       </c>
       <c r="B99" t="n">
-        <v>100506</v>
+        <v>100420</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12368,25 +12360,33 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -12400,10 +12400,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471343</v>
+        <v>471337</v>
       </c>
       <c r="R99" t="n">
-        <v>6609410</v>
+        <v>6609424</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
         <v>125151027</v>
       </c>
       <c r="B100" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>125151055</v>
       </c>
       <c r="B101" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>125151358</v>
       </c>
       <c r="B102" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>125151256</v>
       </c>
       <c r="B103" t="n">
-        <v>102553</v>
+        <v>102560</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>125148993</v>
       </c>
       <c r="B104" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>125251985</v>
       </c>
       <c r="B105" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>125457870</v>
       </c>
       <c r="B108" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>125457776</v>
       </c>
       <c r="B109" t="n">
-        <v>95569</v>
+        <v>95576</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>125450472</v>
       </c>
       <c r="B110" t="n">
-        <v>95677</v>
+        <v>95684</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>125457759</v>
       </c>
       <c r="B111" t="n">
-        <v>106695</v>
+        <v>106702</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>125457972</v>
       </c>
       <c r="B112" t="n">
-        <v>102553</v>
+        <v>102560</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14058,10 +14058,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125457874</v>
+        <v>125450450</v>
       </c>
       <c r="B113" t="n">
-        <v>95557</v>
+        <v>95780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14069,26 +14069,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -14097,10 +14109,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R113" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14130,9 +14142,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14148,6 +14170,29 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14165,10 +14210,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125450450</v>
+        <v>125457874</v>
       </c>
       <c r="B114" t="n">
-        <v>95773</v>
+        <v>95564</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14176,38 +14221,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>210</v>
+        <v>2809</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -14216,10 +14249,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R114" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14249,19 +14282,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14277,29 +14300,6 @@
       <c r="AI114" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN114" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14320,7 +14320,7 @@
         <v>125547926</v>
       </c>
       <c r="B115" t="n">
-        <v>95678</v>
+        <v>95685</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>125556037</v>
       </c>
       <c r="B117" t="n">
-        <v>95773</v>
+        <v>95780</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>125557853</v>
       </c>
       <c r="B118" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>125555995</v>
       </c>
       <c r="B119" t="n">
-        <v>95569</v>
+        <v>95576</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>125556666</v>
       </c>
       <c r="B120" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>125580232</v>
       </c>
       <c r="B121" t="n">
-        <v>102553</v>
+        <v>102560</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15152,10 +15152,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125556711</v>
+        <v>125580133</v>
       </c>
       <c r="B122" t="n">
-        <v>80105</v>
+        <v>100513</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15163,37 +15163,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471311</v>
+        <v>471456</v>
       </c>
       <c r="R122" t="n">
-        <v>6609624</v>
+        <v>6609465</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15238,30 +15243,30 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Asp.</t>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>grov kalkgranskog</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125580133</v>
+        <v>125556711</v>
       </c>
       <c r="B123" t="n">
-        <v>100506</v>
+        <v>80105</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15269,42 +15274,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471456</v>
+        <v>471311</v>
       </c>
       <c r="R123" t="n">
-        <v>6609465</v>
+        <v>6609624</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15349,20 +15349,20 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>grov kalkgranskog</t>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Asp.</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -15478,7 +15478,7 @@
         <v>125580376</v>
       </c>
       <c r="B125" t="n">
-        <v>102553</v>
+        <v>102560</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>125638955</v>
       </c>
       <c r="B126" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>125639232</v>
       </c>
       <c r="B127" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>125639241</v>
       </c>
       <c r="B128" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>125638580</v>
       </c>
       <c r="B129" t="n">
-        <v>95677</v>
+        <v>95684</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>125639216</v>
       </c>
       <c r="B130" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16194,10 +16194,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125638819</v>
+        <v>125638940</v>
       </c>
       <c r="B131" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16205,36 +16205,28 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -16245,10 +16237,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>471334</v>
+        <v>471288</v>
       </c>
       <c r="R131" t="n">
-        <v>6609447</v>
+        <v>6609428</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16295,7 +16287,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -16313,10 +16305,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125638940</v>
+        <v>125639081</v>
       </c>
       <c r="B132" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16356,10 +16348,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>471288</v>
+        <v>471281</v>
       </c>
       <c r="R132" t="n">
-        <v>6609428</v>
+        <v>6609438</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16406,7 +16398,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -16424,10 +16416,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125639081</v>
+        <v>125638819</v>
       </c>
       <c r="B133" t="n">
-        <v>100506</v>
+        <v>101417</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16435,28 +16427,36 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -16467,10 +16467,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471281</v>
+        <v>471334</v>
       </c>
       <c r="R133" t="n">
-        <v>6609438</v>
+        <v>6609447</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -16535,10 +16535,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125647849</v>
+        <v>125639177</v>
       </c>
       <c r="B134" t="n">
-        <v>95181</v>
+        <v>101417</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16546,38 +16546,50 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2387</v>
+        <v>221235</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>471232</v>
+        <v>471265</v>
       </c>
       <c r="R134" t="n">
-        <v>6609657</v>
+        <v>6609407</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16604,12 +16616,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16625,22 +16637,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125638551</v>
+        <v>125638915</v>
       </c>
       <c r="B135" t="n">
-        <v>95557</v>
+        <v>100513</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16648,26 +16660,30 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -16676,10 +16692,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471386</v>
+        <v>471306</v>
       </c>
       <c r="R135" t="n">
-        <v>6609448</v>
+        <v>6609456</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16726,17 +16742,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16754,10 +16760,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125639177</v>
+        <v>125638551</v>
       </c>
       <c r="B136" t="n">
-        <v>101410</v>
+        <v>95564</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16765,38 +16771,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -16805,10 +16799,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471265</v>
+        <v>471386</v>
       </c>
       <c r="R136" t="n">
-        <v>6609407</v>
+        <v>6609448</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16852,6 +16846,21 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -16868,10 +16877,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125638915</v>
+        <v>125647849</v>
       </c>
       <c r="B137" t="n">
-        <v>100506</v>
+        <v>95188</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16879,42 +16888,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222498</v>
+        <v>2387</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471306</v>
+        <v>471232</v>
       </c>
       <c r="R137" t="n">
-        <v>6609456</v>
+        <v>6609657</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16941,12 +16946,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16959,20 +16964,15 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
         <v>125638871</v>
       </c>
       <c r="B138" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>125638457</v>
       </c>
       <c r="B139" t="n">
-        <v>95557</v>
+        <v>95564</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>125638618</v>
       </c>
       <c r="B140" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17334,49 +17334,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125647908</v>
+        <v>125639406</v>
       </c>
       <c r="B141" t="n">
-        <v>97063</v>
+        <v>100513</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2617</v>
+        <v>222498</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471286</v>
+        <v>471294</v>
       </c>
       <c r="R141" t="n">
-        <v>6609621</v>
+        <v>6609352</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17403,12 +17407,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17421,25 +17425,30 @@
       <c r="AG141" t="b">
         <v>0</v>
       </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125638455</v>
+        <v>125638876</v>
       </c>
       <c r="B142" t="n">
-        <v>95569</v>
+        <v>102833</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17447,26 +17456,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -17475,10 +17488,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471350</v>
+        <v>471319</v>
       </c>
       <c r="R142" t="n">
-        <v>6609454</v>
+        <v>6609451</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17525,7 +17538,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -17543,53 +17556,49 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125638876</v>
+        <v>125647908</v>
       </c>
       <c r="B143" t="n">
-        <v>102826</v>
+        <v>97070</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222002</v>
+        <v>2617</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471319</v>
+        <v>471286</v>
       </c>
       <c r="R143" t="n">
-        <v>6609451</v>
+        <v>6609621</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17616,12 +17625,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17634,30 +17643,25 @@
       <c r="AG143" t="b">
         <v>0</v>
       </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125639406</v>
+        <v>125638455</v>
       </c>
       <c r="B144" t="n">
-        <v>100506</v>
+        <v>95576</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17665,30 +17669,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471294</v>
+        <v>471350</v>
       </c>
       <c r="R144" t="n">
-        <v>6609352</v>
+        <v>6609454</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17765,10 +17765,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125638865</v>
+        <v>125638893</v>
       </c>
       <c r="B145" t="n">
-        <v>100413</v>
+        <v>101417</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17776,21 +17776,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -17816,10 +17816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471319</v>
+        <v>471306</v>
       </c>
       <c r="R145" t="n">
-        <v>6609451</v>
+        <v>6609456</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17884,10 +17884,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125638825</v>
+        <v>125639167</v>
       </c>
       <c r="B146" t="n">
-        <v>102826</v>
+        <v>100513</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17895,21 +17895,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17927,10 +17927,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471334</v>
+        <v>471265</v>
       </c>
       <c r="R146" t="n">
-        <v>6609447</v>
+        <v>6609407</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17965,11 +17965,6 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -17979,11 +17974,6 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18000,10 +17990,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125638893</v>
+        <v>125638825</v>
       </c>
       <c r="B147" t="n">
-        <v>101410</v>
+        <v>102833</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18011,36 +18001,28 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -18051,10 +18033,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471306</v>
+        <v>471334</v>
       </c>
       <c r="R147" t="n">
-        <v>6609456</v>
+        <v>6609447</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18089,6 +18071,11 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -18101,7 +18088,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18119,10 +18106,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125639167</v>
+        <v>125638865</v>
       </c>
       <c r="B148" t="n">
-        <v>100506</v>
+        <v>100420</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18130,28 +18117,36 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -18162,10 +18157,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471265</v>
+        <v>471319</v>
       </c>
       <c r="R148" t="n">
-        <v>6609407</v>
+        <v>6609451</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18209,6 +18204,11 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18228,7 +18228,7 @@
         <v>125647918</v>
       </c>
       <c r="B149" t="n">
-        <v>96802</v>
+        <v>96809</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>125638527</v>
       </c>
       <c r="B150" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>125638785</v>
       </c>
       <c r="B151" t="n">
-        <v>102826</v>
+        <v>102833</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18565,10 +18565,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125638867</v>
+        <v>125638600</v>
       </c>
       <c r="B152" t="n">
-        <v>100506</v>
+        <v>100420</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18576,25 +18576,33 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18608,10 +18616,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>471319</v>
+        <v>471393</v>
       </c>
       <c r="R152" t="n">
-        <v>6609451</v>
+        <v>6609458</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18641,9 +18649,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18676,10 +18694,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125638600</v>
+        <v>125638867</v>
       </c>
       <c r="B153" t="n">
-        <v>100413</v>
+        <v>100513</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18687,33 +18705,25 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18727,10 +18737,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471393</v>
+        <v>471319</v>
       </c>
       <c r="R153" t="n">
-        <v>6609458</v>
+        <v>6609451</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18760,19 +18770,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18808,7 +18808,7 @@
         <v>125639147</v>
       </c>
       <c r="B154" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>125647784</v>
       </c>
       <c r="B155" t="n">
-        <v>96897</v>
+        <v>96904</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>125638320</v>
       </c>
       <c r="B156" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>125638438</v>
       </c>
       <c r="B157" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19263,10 +19263,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125638903</v>
+        <v>125638823</v>
       </c>
       <c r="B158" t="n">
-        <v>100413</v>
+        <v>100513</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19274,36 +19274,28 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -19314,10 +19306,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>471306</v>
+        <v>471334</v>
       </c>
       <c r="R158" t="n">
-        <v>6609456</v>
+        <v>6609447</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19364,7 +19356,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -19382,10 +19374,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125638625</v>
+        <v>125638903</v>
       </c>
       <c r="B159" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19422,7 +19414,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -19433,10 +19425,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471408</v>
+        <v>471306</v>
       </c>
       <c r="R159" t="n">
-        <v>6609463</v>
+        <v>6609456</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19466,19 +19458,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19511,10 +19493,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125638720</v>
+        <v>125638625</v>
       </c>
       <c r="B160" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19541,7 +19523,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19562,10 +19544,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471352</v>
+        <v>471408</v>
       </c>
       <c r="R160" t="n">
-        <v>6609455</v>
+        <v>6609463</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19622,7 +19604,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -19640,10 +19622,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125638823</v>
+        <v>125638720</v>
       </c>
       <c r="B161" t="n">
-        <v>100506</v>
+        <v>100420</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19651,25 +19633,33 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19683,10 +19673,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471334</v>
+        <v>471352</v>
       </c>
       <c r="R161" t="n">
-        <v>6609447</v>
+        <v>6609455</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19716,9 +19706,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19754,7 +19754,7 @@
         <v>125638831</v>
       </c>
       <c r="B162" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>125639134</v>
       </c>
       <c r="B163" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19976,10 +19976,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125639036</v>
+        <v>125638375</v>
       </c>
       <c r="B164" t="n">
-        <v>95569</v>
+        <v>95564</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19987,21 +19987,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20015,10 +20015,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471281</v>
+        <v>471329</v>
       </c>
       <c r="R164" t="n">
-        <v>6609438</v>
+        <v>6609462</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20059,13 +20059,12 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -20083,10 +20082,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125638375</v>
+        <v>125639036</v>
       </c>
       <c r="B165" t="n">
-        <v>95557</v>
+        <v>95576</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20094,21 +20093,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20122,10 +20121,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471329</v>
+        <v>471281</v>
       </c>
       <c r="R165" t="n">
-        <v>6609462</v>
+        <v>6609438</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20166,12 +20165,13 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20192,7 +20192,7 @@
         <v>125638908</v>
       </c>
       <c r="B166" t="n">
-        <v>102826</v>
+        <v>102833</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20300,10 +20300,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125638771</v>
+        <v>125638348</v>
       </c>
       <c r="B167" t="n">
-        <v>101410</v>
+        <v>98354</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20311,26 +20311,26 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -20340,7 +20340,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -20351,10 +20351,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471336</v>
+        <v>471329</v>
       </c>
       <c r="R167" t="n">
-        <v>6609447</v>
+        <v>6609462</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20395,13 +20395,12 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -20419,49 +20418,61 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125647825</v>
+        <v>125638771</v>
       </c>
       <c r="B168" t="n">
-        <v>96577</v>
+        <v>101417</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471311</v>
+        <v>471336</v>
       </c>
       <c r="R168" t="n">
-        <v>6609467</v>
+        <v>6609447</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20488,12 +20499,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20506,81 +20517,69 @@
       <c r="AG168" t="b">
         <v>0</v>
       </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125638348</v>
+        <v>125647825</v>
       </c>
       <c r="B169" t="n">
-        <v>98347</v>
+        <v>96584</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>219847</v>
+        <v>53</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471329</v>
+        <v>471311</v>
       </c>
       <c r="R169" t="n">
-        <v>6609462</v>
+        <v>6609467</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20607,12 +20606,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20621,33 +20620,34 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125638463</v>
+        <v>125638511</v>
       </c>
       <c r="B170" t="n">
-        <v>101410</v>
+        <v>95564</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20655,33 +20655,25 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
@@ -20691,10 +20683,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471350</v>
+        <v>471371</v>
       </c>
       <c r="R170" t="n">
-        <v>6609454</v>
+        <v>6609452</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20741,7 +20733,17 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -20759,10 +20761,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125638511</v>
+        <v>125638361</v>
       </c>
       <c r="B171" t="n">
-        <v>95557</v>
+        <v>102833</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20770,26 +20772,38 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2809</v>
+        <v>222002</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -20798,10 +20812,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471371</v>
+        <v>471329</v>
       </c>
       <c r="R171" t="n">
-        <v>6609452</v>
+        <v>6609462</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20842,23 +20856,12 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -20876,10 +20879,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125638361</v>
+        <v>125638917</v>
       </c>
       <c r="B172" t="n">
-        <v>102826</v>
+        <v>103762</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20887,16 +20890,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -20927,10 +20930,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471329</v>
+        <v>471306</v>
       </c>
       <c r="R172" t="n">
-        <v>6609462</v>
+        <v>6609456</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20971,12 +20974,13 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -20994,10 +20998,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125638917</v>
+        <v>125638463</v>
       </c>
       <c r="B173" t="n">
-        <v>103755</v>
+        <v>101417</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21005,21 +21009,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -21032,11 +21036,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -21045,10 +21045,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471306</v>
+        <v>471350</v>
       </c>
       <c r="R173" t="n">
-        <v>6609456</v>
+        <v>6609454</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -21242,10 +21242,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125691568</v>
+        <v>125691817</v>
       </c>
       <c r="B175" t="n">
-        <v>100506</v>
+        <v>101417</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21253,26 +21253,26 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21293,10 +21293,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471299</v>
+        <v>471334</v>
       </c>
       <c r="R175" t="n">
-        <v>6609407</v>
+        <v>6609428</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21356,10 +21356,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125691817</v>
+        <v>125691568</v>
       </c>
       <c r="B176" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21367,26 +21367,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -21407,10 +21407,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471334</v>
+        <v>471299</v>
       </c>
       <c r="R176" t="n">
-        <v>6609428</v>
+        <v>6609407</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -21473,7 +21473,7 @@
         <v>125692508</v>
       </c>
       <c r="B177" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>125693285</v>
       </c>
       <c r="B178" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>125688723</v>
       </c>
       <c r="B179" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21796,10 +21796,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125691522</v>
+        <v>125691638</v>
       </c>
       <c r="B180" t="n">
-        <v>100506</v>
+        <v>95684</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21807,32 +21807,28 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -21843,10 +21839,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471257</v>
+        <v>471299</v>
       </c>
       <c r="R180" t="n">
-        <v>6609382</v>
+        <v>6609407</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21890,6 +21886,26 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
@@ -21906,10 +21922,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125691596</v>
+        <v>125692947</v>
       </c>
       <c r="B181" t="n">
-        <v>102826</v>
+        <v>95576</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21917,30 +21933,26 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -21949,10 +21961,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471299</v>
+        <v>471213</v>
       </c>
       <c r="R181" t="n">
-        <v>6609407</v>
+        <v>6609721</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -22012,10 +22024,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125694456</v>
+        <v>125693315</v>
       </c>
       <c r="B182" t="n">
-        <v>102826</v>
+        <v>95685</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22023,28 +22035,28 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>222002</v>
+        <v>2819</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
@@ -22058,7 +22070,7 @@
         <v>471315</v>
       </c>
       <c r="R182" t="n">
-        <v>6609388</v>
+        <v>6609611</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22085,12 +22097,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22103,9 +22115,17 @@
       <c r="AG182" t="b">
         <v>0</v>
       </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -22123,10 +22143,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125691772</v>
+        <v>125691522</v>
       </c>
       <c r="B183" t="n">
-        <v>102826</v>
+        <v>100513</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22134,21 +22154,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -22170,10 +22190,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471330</v>
+        <v>471257</v>
       </c>
       <c r="R183" t="n">
-        <v>6609444</v>
+        <v>6609382</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -22233,10 +22253,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125691638</v>
+        <v>125691596</v>
       </c>
       <c r="B184" t="n">
-        <v>95677</v>
+        <v>102833</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22244,28 +22264,28 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2818</v>
+        <v>222002</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -22323,26 +22343,6 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gråal</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
@@ -22359,10 +22359,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125692947</v>
+        <v>125694456</v>
       </c>
       <c r="B185" t="n">
-        <v>95569</v>
+        <v>102833</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22370,26 +22370,30 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -22398,10 +22402,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471213</v>
+        <v>471315</v>
       </c>
       <c r="R185" t="n">
-        <v>6609721</v>
+        <v>6609388</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22428,12 +22432,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22445,6 +22449,11 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
@@ -22461,10 +22470,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125693315</v>
+        <v>125691772</v>
       </c>
       <c r="B186" t="n">
-        <v>95678</v>
+        <v>102833</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22472,28 +22481,32 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2819</v>
+        <v>222002</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -22504,10 +22517,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471315</v>
+        <v>471330</v>
       </c>
       <c r="R186" t="n">
-        <v>6609611</v>
+        <v>6609444</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -22551,19 +22564,6 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN186" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Stump # murken stubbe</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
@@ -22580,10 +22580,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125691504</v>
+        <v>125691671</v>
       </c>
       <c r="B187" t="n">
-        <v>100506</v>
+        <v>101417</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22591,28 +22591,36 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
@@ -22623,10 +22631,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471256</v>
+        <v>471307</v>
       </c>
       <c r="R187" t="n">
-        <v>6609375</v>
+        <v>6609405</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22689,7 +22697,7 @@
         <v>125691752</v>
       </c>
       <c r="B188" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22803,7 +22811,7 @@
         <v>125691775</v>
       </c>
       <c r="B189" t="n">
-        <v>106695</v>
+        <v>106702</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22919,10 +22927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125691545</v>
+        <v>125691504</v>
       </c>
       <c r="B190" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22962,10 +22970,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471275</v>
+        <v>471256</v>
       </c>
       <c r="R190" t="n">
-        <v>6609399</v>
+        <v>6609375</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -23025,10 +23033,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125691671</v>
+        <v>125691545</v>
       </c>
       <c r="B191" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23036,36 +23044,28 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -23076,10 +23076,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471307</v>
+        <v>471275</v>
       </c>
       <c r="R191" t="n">
-        <v>6609405</v>
+        <v>6609399</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -23142,7 +23142,7 @@
         <v>125692480</v>
       </c>
       <c r="B192" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>125692234</v>
       </c>
       <c r="B193" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>125692324</v>
       </c>
       <c r="B194" t="n">
-        <v>106695</v>
+        <v>106702</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>125691650</v>
       </c>
       <c r="B195" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>125692303</v>
       </c>
       <c r="B196" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23687,10 +23687,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125693289</v>
+        <v>125691655</v>
       </c>
       <c r="B197" t="n">
-        <v>100506</v>
+        <v>102833</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23698,28 +23698,24 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -23734,10 +23730,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471315</v>
+        <v>471309</v>
       </c>
       <c r="R197" t="n">
-        <v>6609611</v>
+        <v>6609409</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23797,10 +23793,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125692378</v>
+        <v>125693289</v>
       </c>
       <c r="B198" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23825,7 +23821,11 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
@@ -23840,10 +23840,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471440</v>
+        <v>471315</v>
       </c>
       <c r="R198" t="n">
-        <v>6609375</v>
+        <v>6609611</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23903,10 +23903,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125691756</v>
+        <v>125692378</v>
       </c>
       <c r="B199" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23946,10 +23946,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471316</v>
+        <v>471440</v>
       </c>
       <c r="R199" t="n">
-        <v>6609440</v>
+        <v>6609375</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24009,10 +24009,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125691655</v>
+        <v>125691756</v>
       </c>
       <c r="B200" t="n">
-        <v>102826</v>
+        <v>100513</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24020,21 +24020,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -24052,10 +24052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471309</v>
+        <v>471316</v>
       </c>
       <c r="R200" t="n">
-        <v>6609409</v>
+        <v>6609440</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24118,7 +24118,7 @@
         <v>125694447</v>
       </c>
       <c r="B201" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>125691940</v>
       </c>
       <c r="B202" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24332,10 +24332,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125691675</v>
+        <v>125692924</v>
       </c>
       <c r="B203" t="n">
-        <v>102826</v>
+        <v>95576</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24343,30 +24343,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
@@ -24375,10 +24371,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>471307</v>
+        <v>471200</v>
       </c>
       <c r="R203" t="n">
-        <v>6609405</v>
+        <v>6609727</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24438,10 +24434,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125692924</v>
+        <v>125691675</v>
       </c>
       <c r="B204" t="n">
-        <v>95569</v>
+        <v>102833</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24449,26 +24445,30 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
@@ -24477,10 +24477,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471200</v>
+        <v>471307</v>
       </c>
       <c r="R204" t="n">
-        <v>6609727</v>
+        <v>6609405</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -24540,10 +24540,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125693221</v>
+        <v>125691724</v>
       </c>
       <c r="B205" t="n">
-        <v>100506</v>
+        <v>101417</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24551,28 +24551,36 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
@@ -24583,10 +24591,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471325</v>
+        <v>471295</v>
       </c>
       <c r="R205" t="n">
-        <v>6609612</v>
+        <v>6609415</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24646,10 +24654,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>125691724</v>
+        <v>125691555</v>
       </c>
       <c r="B206" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24676,7 +24684,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -24697,10 +24705,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>471295</v>
+        <v>471277</v>
       </c>
       <c r="R206" t="n">
-        <v>6609415</v>
+        <v>6609410</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24760,10 +24768,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>125691555</v>
+        <v>125693221</v>
       </c>
       <c r="B207" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24771,36 +24779,28 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -24811,10 +24811,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>471277</v>
+        <v>471325</v>
       </c>
       <c r="R207" t="n">
-        <v>6609410</v>
+        <v>6609612</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24877,7 +24877,7 @@
         <v>125692746</v>
       </c>
       <c r="B208" t="n">
-        <v>95569</v>
+        <v>95576</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>125692901</v>
       </c>
       <c r="B209" t="n">
-        <v>95569</v>
+        <v>95576</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>125694704</v>
       </c>
       <c r="B210" t="n">
-        <v>95557</v>
+        <v>95564</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>125691701</v>
       </c>
       <c r="B211" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>125692396</v>
       </c>
       <c r="B212" t="n">
-        <v>95557</v>
+        <v>95564</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25417,10 +25417,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>125691532</v>
+        <v>125693046</v>
       </c>
       <c r="B213" t="n">
-        <v>100506</v>
+        <v>97209</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25428,34 +25428,26 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
@@ -25464,10 +25456,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471263</v>
+        <v>471207</v>
       </c>
       <c r="R213" t="n">
-        <v>6609389</v>
+        <v>6609720</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25527,10 +25519,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125693203</v>
+        <v>125688737</v>
       </c>
       <c r="B214" t="n">
-        <v>103755</v>
+        <v>101417</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25538,38 +25530,26 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
@@ -25578,10 +25558,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471315</v>
+        <v>471312</v>
       </c>
       <c r="R214" t="n">
-        <v>6609562</v>
+        <v>6609616</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25641,10 +25621,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>125688737</v>
+        <v>125691532</v>
       </c>
       <c r="B215" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25652,26 +25632,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
@@ -25680,10 +25668,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471312</v>
+        <v>471263</v>
       </c>
       <c r="R215" t="n">
-        <v>6609616</v>
+        <v>6609389</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25743,10 +25731,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>125693046</v>
+        <v>125693203</v>
       </c>
       <c r="B216" t="n">
-        <v>97202</v>
+        <v>103762</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25754,16 +25742,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221945</v>
+        <v>222412</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -25771,9 +25759,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -25782,10 +25782,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471207</v>
+        <v>471315</v>
       </c>
       <c r="R216" t="n">
-        <v>6609720</v>
+        <v>6609562</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25845,37 +25845,37 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>125693113</v>
+        <v>125694805</v>
       </c>
       <c r="B217" t="n">
-        <v>106695</v>
+        <v>102560</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>219686</v>
+        <v>223246</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -25885,7 +25885,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -25896,10 +25896,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471338</v>
+        <v>471442</v>
       </c>
       <c r="R217" t="n">
-        <v>6609551</v>
+        <v>6609507</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25926,12 +25926,17 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>klent träd</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25959,10 +25964,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>125691883</v>
+        <v>125693113</v>
       </c>
       <c r="B218" t="n">
-        <v>103755</v>
+        <v>106702</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25970,16 +25975,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>222412</v>
+        <v>219686</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -25989,7 +25994,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -25999,7 +26004,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -26010,10 +26015,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471342</v>
+        <v>471338</v>
       </c>
       <c r="R218" t="n">
-        <v>6609418</v>
+        <v>6609551</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -26073,32 +26078,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>125694805</v>
+        <v>125691883</v>
       </c>
       <c r="B219" t="n">
-        <v>102553</v>
+        <v>103762</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>223246</v>
+        <v>222412</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -26124,10 +26129,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471442</v>
+        <v>471342</v>
       </c>
       <c r="R219" t="n">
-        <v>6609507</v>
+        <v>6609418</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -26154,17 +26159,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>klent träd</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26195,7 +26195,7 @@
         <v>125692474</v>
       </c>
       <c r="B220" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>125692758</v>
       </c>
       <c r="B221" t="n">
-        <v>95569</v>
+        <v>95576</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>125692169</v>
       </c>
       <c r="B222" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>125691678</v>
       </c>
       <c r="B223" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>125691689</v>
       </c>
       <c r="B224" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>125694768</v>
       </c>
       <c r="B225" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26854,10 +26854,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>125692655</v>
+        <v>125691768</v>
       </c>
       <c r="B226" t="n">
-        <v>95678</v>
+        <v>102833</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26865,28 +26865,28 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2819</v>
+        <v>222002</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -26897,10 +26897,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>471404</v>
+        <v>471316</v>
       </c>
       <c r="R226" t="n">
-        <v>6609514</v>
+        <v>6609440</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26944,19 +26944,6 @@
       <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN226" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Stump # murken stubbe</t>
-        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -26976,7 +26963,7 @@
         <v>125692269</v>
       </c>
       <c r="B227" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27079,10 +27066,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>125691768</v>
+        <v>125692655</v>
       </c>
       <c r="B228" t="n">
-        <v>102826</v>
+        <v>95685</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27090,28 +27077,28 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>222002</v>
+        <v>2819</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -27122,10 +27109,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>471316</v>
+        <v>471404</v>
       </c>
       <c r="R228" t="n">
-        <v>6609440</v>
+        <v>6609514</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -27169,6 +27156,19 @@
       <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -27185,10 +27185,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>125694224</v>
+        <v>125693086</v>
       </c>
       <c r="B229" t="n">
-        <v>100506</v>
+        <v>101417</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27196,28 +27196,36 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -27228,10 +27236,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>471320</v>
+        <v>471336</v>
       </c>
       <c r="R229" t="n">
-        <v>6609374</v>
+        <v>6609592</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27258,12 +27266,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -27272,13 +27280,9 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -27295,10 +27299,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>125693086</v>
+        <v>125694224</v>
       </c>
       <c r="B230" t="n">
-        <v>101410</v>
+        <v>100513</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27306,36 +27310,28 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
@@ -27346,10 +27342,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>471336</v>
+        <v>471320</v>
       </c>
       <c r="R230" t="n">
-        <v>6609592</v>
+        <v>6609374</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27376,12 +27372,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -27390,9 +27386,13 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
@@ -27412,7 +27412,7 @@
         <v>125691600</v>
       </c>
       <c r="B231" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>125692503</v>
       </c>
       <c r="B232" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>125691592</v>
       </c>
       <c r="B233" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>125691658</v>
       </c>
       <c r="B234" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>125691824</v>
       </c>
       <c r="B235" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>125693090</v>
       </c>
       <c r="B236" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>125691551</v>
       </c>
       <c r="B237" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28188,10 +28188,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>125691487</v>
+        <v>125693283</v>
       </c>
       <c r="B238" t="n">
-        <v>98347</v>
+        <v>95684</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28199,36 +28199,28 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>219847</v>
+        <v>2818</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -28239,10 +28231,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>471256</v>
+        <v>471321</v>
       </c>
       <c r="R238" t="n">
-        <v>6609375</v>
+        <v>6609614</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -28286,6 +28278,26 @@
       <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
+        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
@@ -28302,10 +28314,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>125693283</v>
+        <v>125691487</v>
       </c>
       <c r="B239" t="n">
-        <v>95677</v>
+        <v>98354</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28313,28 +28325,36 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2818</v>
+        <v>219847</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L239" t="inlineStr"/>
@@ -28345,10 +28365,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471321</v>
+        <v>471256</v>
       </c>
       <c r="R239" t="n">
-        <v>6609614</v>
+        <v>6609375</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28392,26 +28412,6 @@
       <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>Stump # murken stubbe # Picea abies</t>
-        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -15957,10 +15957,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125638580</v>
+        <v>125639216</v>
       </c>
       <c r="B129" t="n">
-        <v>95684</v>
+        <v>100513</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15968,28 +15968,28 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471393</v>
+        <v>471261</v>
       </c>
       <c r="R129" t="n">
-        <v>6609458</v>
+        <v>6609384</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16047,31 +16047,6 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Stump # murken stubbe # Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -16088,10 +16063,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125639216</v>
+        <v>125638580</v>
       </c>
       <c r="B130" t="n">
-        <v>100513</v>
+        <v>95684</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16099,28 +16074,28 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -16131,10 +16106,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>471261</v>
+        <v>471393</v>
       </c>
       <c r="R130" t="n">
-        <v>6609384</v>
+        <v>6609458</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16178,6 +16153,31 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -17334,53 +17334,49 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125639406</v>
+        <v>125647908</v>
       </c>
       <c r="B141" t="n">
-        <v>100513</v>
+        <v>97070</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222498</v>
+        <v>2617</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471294</v>
+        <v>471286</v>
       </c>
       <c r="R141" t="n">
-        <v>6609352</v>
+        <v>6609621</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17407,12 +17403,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17425,30 +17421,25 @@
       <c r="AG141" t="b">
         <v>0</v>
       </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125638876</v>
+        <v>125638455</v>
       </c>
       <c r="B142" t="n">
-        <v>102833</v>
+        <v>95576</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17456,30 +17447,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -17488,10 +17475,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471319</v>
+        <v>471350</v>
       </c>
       <c r="R142" t="n">
-        <v>6609451</v>
+        <v>6609454</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17538,7 +17525,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -17556,49 +17543,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125647908</v>
+        <v>125639406</v>
       </c>
       <c r="B143" t="n">
-        <v>97070</v>
+        <v>100513</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2617</v>
+        <v>222498</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471286</v>
+        <v>471294</v>
       </c>
       <c r="R143" t="n">
-        <v>6609621</v>
+        <v>6609352</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17625,12 +17616,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17643,25 +17634,30 @@
       <c r="AG143" t="b">
         <v>0</v>
       </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125638455</v>
+        <v>125638876</v>
       </c>
       <c r="B144" t="n">
-        <v>95576</v>
+        <v>102833</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17669,26 +17665,30 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471350</v>
+        <v>471319</v>
       </c>
       <c r="R144" t="n">
-        <v>6609454</v>
+        <v>6609451</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17884,10 +17884,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125639167</v>
+        <v>125638865</v>
       </c>
       <c r="B146" t="n">
-        <v>100513</v>
+        <v>100420</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17895,28 +17895,36 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -17927,10 +17935,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471265</v>
+        <v>471319</v>
       </c>
       <c r="R146" t="n">
-        <v>6609407</v>
+        <v>6609451</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17974,6 +17982,11 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -17990,10 +18003,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125638825</v>
+        <v>125639167</v>
       </c>
       <c r="B147" t="n">
-        <v>102833</v>
+        <v>100513</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18001,21 +18014,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -18033,10 +18046,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471334</v>
+        <v>471265</v>
       </c>
       <c r="R147" t="n">
-        <v>6609447</v>
+        <v>6609407</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18071,11 +18084,6 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -18085,11 +18093,6 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18106,10 +18109,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125638865</v>
+        <v>125638825</v>
       </c>
       <c r="B148" t="n">
-        <v>100420</v>
+        <v>102833</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18117,16 +18120,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222771</v>
+        <v>222002</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -18134,19 +18137,11 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -18157,10 +18152,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471319</v>
+        <v>471334</v>
       </c>
       <c r="R148" t="n">
-        <v>6609451</v>
+        <v>6609447</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18195,6 +18190,11 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19026,10 +19026,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125638320</v>
+        <v>125638438</v>
       </c>
       <c r="B156" t="n">
-        <v>101417</v>
+        <v>98354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19037,26 +19037,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -19077,10 +19077,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471329</v>
+        <v>471350</v>
       </c>
       <c r="R156" t="n">
-        <v>6609462</v>
+        <v>6609454</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19121,12 +19121,13 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -19144,10 +19145,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125638438</v>
+        <v>125638320</v>
       </c>
       <c r="B157" t="n">
-        <v>98354</v>
+        <v>101417</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19155,26 +19156,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -19184,7 +19185,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -19195,10 +19196,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471350</v>
+        <v>471329</v>
       </c>
       <c r="R157" t="n">
-        <v>6609454</v>
+        <v>6609462</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19239,13 +19240,12 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -19263,10 +19263,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125638823</v>
+        <v>125638903</v>
       </c>
       <c r="B158" t="n">
-        <v>100513</v>
+        <v>100420</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19274,28 +19274,36 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -19306,10 +19314,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>471334</v>
+        <v>471306</v>
       </c>
       <c r="R158" t="n">
-        <v>6609447</v>
+        <v>6609456</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19356,7 +19364,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -19374,7 +19382,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125638903</v>
+        <v>125638625</v>
       </c>
       <c r="B159" t="n">
         <v>100420</v>
@@ -19414,7 +19422,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -19425,10 +19433,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471306</v>
+        <v>471408</v>
       </c>
       <c r="R159" t="n">
-        <v>6609456</v>
+        <v>6609463</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19458,9 +19466,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19493,7 +19511,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125638625</v>
+        <v>125638720</v>
       </c>
       <c r="B160" t="n">
         <v>100420</v>
@@ -19523,7 +19541,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19544,10 +19562,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471408</v>
+        <v>471352</v>
       </c>
       <c r="R160" t="n">
-        <v>6609463</v>
+        <v>6609455</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19604,7 +19622,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -19622,10 +19640,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125638720</v>
+        <v>125638823</v>
       </c>
       <c r="B161" t="n">
-        <v>100420</v>
+        <v>100513</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19633,33 +19651,25 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19673,10 +19683,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471352</v>
+        <v>471334</v>
       </c>
       <c r="R161" t="n">
-        <v>6609455</v>
+        <v>6609447</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19706,19 +19716,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19751,10 +19751,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125638831</v>
+        <v>125639134</v>
       </c>
       <c r="B162" t="n">
-        <v>98354</v>
+        <v>100513</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19762,33 +19762,25 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19802,10 +19794,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471334</v>
+        <v>471271</v>
       </c>
       <c r="R162" t="n">
-        <v>6609447</v>
+        <v>6609429</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19849,11 +19841,6 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -19870,10 +19857,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125639134</v>
+        <v>125638831</v>
       </c>
       <c r="B163" t="n">
-        <v>100513</v>
+        <v>98354</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19881,25 +19868,33 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19913,10 +19908,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471271</v>
+        <v>471334</v>
       </c>
       <c r="R163" t="n">
-        <v>6609429</v>
+        <v>6609447</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19960,6 +19955,11 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19976,10 +19976,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125638375</v>
+        <v>125638908</v>
       </c>
       <c r="B164" t="n">
-        <v>95564</v>
+        <v>102833</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19987,26 +19987,30 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2809</v>
+        <v>222002</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -20015,10 +20019,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471329</v>
+        <v>471306</v>
       </c>
       <c r="R164" t="n">
-        <v>6609462</v>
+        <v>6609456</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20059,12 +20063,13 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -20082,10 +20087,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125639036</v>
+        <v>125638375</v>
       </c>
       <c r="B165" t="n">
-        <v>95576</v>
+        <v>95564</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20093,21 +20098,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20121,10 +20126,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471281</v>
+        <v>471329</v>
       </c>
       <c r="R165" t="n">
-        <v>6609438</v>
+        <v>6609462</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20165,13 +20170,12 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20189,10 +20193,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125638908</v>
+        <v>125639036</v>
       </c>
       <c r="B166" t="n">
-        <v>102833</v>
+        <v>95576</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20200,30 +20204,26 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471306</v>
+        <v>471281</v>
       </c>
       <c r="R166" t="n">
-        <v>6609456</v>
+        <v>6609438</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -20644,10 +20644,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125638511</v>
+        <v>125638463</v>
       </c>
       <c r="B170" t="n">
-        <v>95564</v>
+        <v>101417</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20655,25 +20655,33 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
@@ -20683,10 +20691,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471371</v>
+        <v>471350</v>
       </c>
       <c r="R170" t="n">
-        <v>6609452</v>
+        <v>6609454</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20733,17 +20741,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -20998,10 +20996,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125638463</v>
+        <v>125638511</v>
       </c>
       <c r="B173" t="n">
-        <v>101417</v>
+        <v>95564</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21009,33 +21007,25 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
@@ -21045,10 +21035,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471350</v>
+        <v>471371</v>
       </c>
       <c r="R173" t="n">
-        <v>6609454</v>
+        <v>6609452</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -21095,7 +21085,17 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -23687,10 +23687,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125691655</v>
+        <v>125693289</v>
       </c>
       <c r="B197" t="n">
-        <v>102833</v>
+        <v>100513</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23698,24 +23698,28 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -23730,10 +23734,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471309</v>
+        <v>471315</v>
       </c>
       <c r="R197" t="n">
-        <v>6609409</v>
+        <v>6609611</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23793,7 +23797,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125693289</v>
+        <v>125692378</v>
       </c>
       <c r="B198" t="n">
         <v>100513</v>
@@ -23821,11 +23825,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
@@ -23840,10 +23840,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471315</v>
+        <v>471440</v>
       </c>
       <c r="R198" t="n">
-        <v>6609611</v>
+        <v>6609375</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23903,7 +23903,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125692378</v>
+        <v>125691756</v>
       </c>
       <c r="B199" t="n">
         <v>100513</v>
@@ -23946,10 +23946,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471440</v>
+        <v>471316</v>
       </c>
       <c r="R199" t="n">
-        <v>6609375</v>
+        <v>6609440</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24009,10 +24009,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125691756</v>
+        <v>125691655</v>
       </c>
       <c r="B200" t="n">
-        <v>100513</v>
+        <v>102833</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24020,21 +24020,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -24052,10 +24052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471316</v>
+        <v>471309</v>
       </c>
       <c r="R200" t="n">
-        <v>6609440</v>
+        <v>6609409</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -26306,10 +26306,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>125692758</v>
+        <v>125692169</v>
       </c>
       <c r="B221" t="n">
-        <v>95576</v>
+        <v>98354</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26317,26 +26317,38 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2813</v>
+        <v>219847</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
@@ -26345,10 +26357,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471191</v>
+        <v>471438</v>
       </c>
       <c r="R221" t="n">
-        <v>6609737</v>
+        <v>6609315</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26389,9 +26401,13 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>Källkärr</t>
+        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
@@ -26408,10 +26424,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>125692169</v>
+        <v>125691678</v>
       </c>
       <c r="B222" t="n">
-        <v>98354</v>
+        <v>100513</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26419,33 +26435,25 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -26459,10 +26467,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>471438</v>
+        <v>471307</v>
       </c>
       <c r="R222" t="n">
-        <v>6609315</v>
+        <v>6609405</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26503,13 +26511,9 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>Källkärr</t>
-        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
@@ -26526,7 +26530,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>125691678</v>
+        <v>125691689</v>
       </c>
       <c r="B223" t="n">
         <v>100513</v>
@@ -26569,10 +26573,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471307</v>
+        <v>471315</v>
       </c>
       <c r="R223" t="n">
-        <v>6609405</v>
+        <v>6609406</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26632,7 +26636,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>125691689</v>
+        <v>125694768</v>
       </c>
       <c r="B224" t="n">
         <v>100513</v>
@@ -26675,10 +26679,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>471315</v>
+        <v>471450</v>
       </c>
       <c r="R224" t="n">
-        <v>6609406</v>
+        <v>6609501</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26705,12 +26709,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26722,6 +26726,16 @@
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
@@ -26738,10 +26752,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>125694768</v>
+        <v>125692758</v>
       </c>
       <c r="B225" t="n">
-        <v>100513</v>
+        <v>95576</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26749,30 +26763,26 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
@@ -26781,10 +26791,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>471450</v>
+        <v>471191</v>
       </c>
       <c r="R225" t="n">
-        <v>6609501</v>
+        <v>6609737</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26811,12 +26821,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26828,16 +26838,6 @@
       <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>surdråg</t>
-        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -14058,10 +14058,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125450450</v>
+        <v>125457874</v>
       </c>
       <c r="B113" t="n">
-        <v>95780</v>
+        <v>95564</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14069,38 +14069,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>210</v>
+        <v>2809</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -14109,10 +14097,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R113" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14142,19 +14130,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14170,29 +14148,6 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN113" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14210,10 +14165,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125457874</v>
+        <v>125450450</v>
       </c>
       <c r="B114" t="n">
-        <v>95564</v>
+        <v>95780</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14221,26 +14176,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -14249,10 +14216,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R114" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14282,9 +14249,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14300,6 +14277,29 @@
       <c r="AI114" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125638955</v>
+        <v>125639241</v>
       </c>
       <c r="B126" t="n">
-        <v>101417</v>
+        <v>98354</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15629,26 +15629,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471281</v>
+        <v>471252</v>
       </c>
       <c r="R126" t="n">
-        <v>6609438</v>
+        <v>6609379</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15716,11 +15716,6 @@
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
@@ -15737,10 +15732,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125639232</v>
+        <v>125638955</v>
       </c>
       <c r="B127" t="n">
-        <v>100513</v>
+        <v>101417</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15748,28 +15743,36 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -15780,10 +15783,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471252</v>
+        <v>471281</v>
       </c>
       <c r="R127" t="n">
-        <v>6609379</v>
+        <v>6609438</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15827,6 +15830,11 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -15843,10 +15851,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125639241</v>
+        <v>125639232</v>
       </c>
       <c r="B128" t="n">
-        <v>98354</v>
+        <v>100513</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15854,33 +15862,25 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -15957,10 +15957,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125639216</v>
+        <v>125638580</v>
       </c>
       <c r="B129" t="n">
-        <v>100513</v>
+        <v>95684</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15968,28 +15968,28 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471261</v>
+        <v>471393</v>
       </c>
       <c r="R129" t="n">
-        <v>6609384</v>
+        <v>6609458</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16047,6 +16047,31 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -16063,10 +16088,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125638580</v>
+        <v>125639216</v>
       </c>
       <c r="B130" t="n">
-        <v>95684</v>
+        <v>100513</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16074,28 +16099,28 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -16106,10 +16131,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>471393</v>
+        <v>471261</v>
       </c>
       <c r="R130" t="n">
-        <v>6609458</v>
+        <v>6609384</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16153,31 +16178,6 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Stump # murken stubbe # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -19263,10 +19263,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125638903</v>
+        <v>125638823</v>
       </c>
       <c r="B158" t="n">
-        <v>100420</v>
+        <v>100513</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19274,36 +19274,28 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -19314,10 +19306,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>471306</v>
+        <v>471334</v>
       </c>
       <c r="R158" t="n">
-        <v>6609456</v>
+        <v>6609447</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19364,7 +19356,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -19382,7 +19374,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125638625</v>
+        <v>125638903</v>
       </c>
       <c r="B159" t="n">
         <v>100420</v>
@@ -19422,7 +19414,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -19433,10 +19425,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471408</v>
+        <v>471306</v>
       </c>
       <c r="R159" t="n">
-        <v>6609463</v>
+        <v>6609456</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19466,19 +19458,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19511,7 +19493,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125638720</v>
+        <v>125638625</v>
       </c>
       <c r="B160" t="n">
         <v>100420</v>
@@ -19541,7 +19523,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19562,10 +19544,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471352</v>
+        <v>471408</v>
       </c>
       <c r="R160" t="n">
-        <v>6609455</v>
+        <v>6609463</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19622,7 +19604,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -19640,10 +19622,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125638823</v>
+        <v>125638720</v>
       </c>
       <c r="B161" t="n">
-        <v>100513</v>
+        <v>100420</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19651,25 +19633,33 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19683,10 +19673,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471334</v>
+        <v>471352</v>
       </c>
       <c r="R161" t="n">
-        <v>6609447</v>
+        <v>6609455</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19716,9 +19706,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -21796,10 +21796,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125691638</v>
+        <v>125691596</v>
       </c>
       <c r="B180" t="n">
-        <v>95684</v>
+        <v>102833</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21807,28 +21807,28 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2818</v>
+        <v>222002</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -21886,26 +21886,6 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>gråal</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
@@ -21922,10 +21902,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125692947</v>
+        <v>125694456</v>
       </c>
       <c r="B181" t="n">
-        <v>95576</v>
+        <v>102833</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21933,26 +21913,30 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -21961,10 +21945,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471213</v>
+        <v>471315</v>
       </c>
       <c r="R181" t="n">
-        <v>6609721</v>
+        <v>6609388</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21991,12 +21975,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22008,6 +21992,11 @@
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
@@ -22024,10 +22013,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125693315</v>
+        <v>125691772</v>
       </c>
       <c r="B182" t="n">
-        <v>95685</v>
+        <v>102833</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22035,28 +22024,32 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2819</v>
+        <v>222002</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
@@ -22067,10 +22060,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471315</v>
+        <v>471330</v>
       </c>
       <c r="R182" t="n">
-        <v>6609611</v>
+        <v>6609444</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22114,19 +22107,6 @@
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN182" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Stump # murken stubbe</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
@@ -22253,10 +22233,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125691596</v>
+        <v>125691638</v>
       </c>
       <c r="B184" t="n">
-        <v>102833</v>
+        <v>95684</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22264,28 +22244,28 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>222002</v>
+        <v>2818</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -22343,6 +22323,26 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
@@ -22359,10 +22359,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125694456</v>
+        <v>125692947</v>
       </c>
       <c r="B185" t="n">
-        <v>102833</v>
+        <v>95576</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22370,30 +22370,26 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -22402,10 +22398,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471315</v>
+        <v>471213</v>
       </c>
       <c r="R185" t="n">
-        <v>6609388</v>
+        <v>6609721</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22432,12 +22428,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22449,11 +22445,6 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
@@ -22470,10 +22461,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125691772</v>
+        <v>125693315</v>
       </c>
       <c r="B186" t="n">
-        <v>102833</v>
+        <v>95685</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22481,32 +22472,28 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>222002</v>
+        <v>2819</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -22517,10 +22504,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471330</v>
+        <v>471315</v>
       </c>
       <c r="R186" t="n">
-        <v>6609444</v>
+        <v>6609611</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -22564,6 +22551,19 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
@@ -24874,10 +24874,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>125692746</v>
+        <v>125691701</v>
       </c>
       <c r="B208" t="n">
-        <v>95576</v>
+        <v>100513</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24885,26 +24885,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
@@ -24913,10 +24921,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>471175</v>
+        <v>471323</v>
       </c>
       <c r="R208" t="n">
-        <v>6609737</v>
+        <v>6609406</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24976,7 +24984,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>125692901</v>
+        <v>125692746</v>
       </c>
       <c r="B209" t="n">
         <v>95576</v>
@@ -25015,10 +25023,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471195</v>
+        <v>471175</v>
       </c>
       <c r="R209" t="n">
-        <v>6609738</v>
+        <v>6609737</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25078,10 +25086,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125694704</v>
+        <v>125692901</v>
       </c>
       <c r="B210" t="n">
-        <v>95564</v>
+        <v>95576</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25089,21 +25097,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -25117,10 +25125,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471383</v>
+        <v>471195</v>
       </c>
       <c r="R210" t="n">
-        <v>6609437</v>
+        <v>6609738</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25147,12 +25155,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25164,21 +25172,6 @@
       <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>blockrik kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO210" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
@@ -25195,10 +25188,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125691701</v>
+        <v>125694704</v>
       </c>
       <c r="B211" t="n">
-        <v>100513</v>
+        <v>95564</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25206,34 +25199,26 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
@@ -25242,10 +25227,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471323</v>
+        <v>471383</v>
       </c>
       <c r="R211" t="n">
-        <v>6609406</v>
+        <v>6609437</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25272,12 +25257,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25289,6 +25274,21 @@
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>blockrik kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
@@ -25964,10 +25964,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>125693113</v>
+        <v>125691883</v>
       </c>
       <c r="B218" t="n">
-        <v>106702</v>
+        <v>103762</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25975,16 +25975,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>219686</v>
+        <v>222412</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -26015,10 +26015,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471338</v>
+        <v>471342</v>
       </c>
       <c r="R218" t="n">
-        <v>6609551</v>
+        <v>6609418</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -26078,10 +26078,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>125691883</v>
+        <v>125693113</v>
       </c>
       <c r="B219" t="n">
-        <v>103762</v>
+        <v>106702</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26089,16 +26089,16 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>222412</v>
+        <v>219686</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -26129,10 +26129,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471342</v>
+        <v>471338</v>
       </c>
       <c r="R219" t="n">
-        <v>6609418</v>
+        <v>6609551</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -8894,7 +8894,7 @@
         <v>121698315</v>
       </c>
       <c r="B70" t="n">
-        <v>97203</v>
+        <v>97206</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>97203</v>
+        <v>97206</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>121698313</v>
       </c>
       <c r="B74" t="n">
-        <v>97203</v>
+        <v>97206</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>125251985</v>
       </c>
       <c r="B105" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>125150908</v>
       </c>
       <c r="B107" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>125457870</v>
       </c>
       <c r="B108" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>125457776</v>
       </c>
       <c r="B109" t="n">
-        <v>95576</v>
+        <v>95579</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13666,10 +13666,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125450472</v>
+        <v>125457759</v>
       </c>
       <c r="B110" t="n">
-        <v>95684</v>
+        <v>106705</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13677,28 +13677,36 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2818</v>
+        <v>219686</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -13709,10 +13717,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R110" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13742,19 +13750,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13770,29 +13768,6 @@
       <c r="AI110" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN110" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13810,10 +13785,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125457759</v>
+        <v>125450472</v>
       </c>
       <c r="B111" t="n">
-        <v>106702</v>
+        <v>95687</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13821,36 +13796,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219686</v>
+        <v>2818</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13861,10 +13828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R111" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13894,9 +13861,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13912,6 +13889,29 @@
       <c r="AI111" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -13932,7 +13932,7 @@
         <v>125457972</v>
       </c>
       <c r="B112" t="n">
-        <v>102560</v>
+        <v>102563</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14058,10 +14058,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125457874</v>
+        <v>125450450</v>
       </c>
       <c r="B113" t="n">
-        <v>95564</v>
+        <v>95783</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14069,26 +14069,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -14097,10 +14109,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R113" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14130,9 +14142,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14148,6 +14170,29 @@
       <c r="AI113" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14165,10 +14210,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125450450</v>
+        <v>125457874</v>
       </c>
       <c r="B114" t="n">
-        <v>95780</v>
+        <v>95567</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14176,38 +14221,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>210</v>
+        <v>2809</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -14216,10 +14249,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R114" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14249,19 +14282,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14277,29 +14300,6 @@
       <c r="AI114" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN114" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Horizontal, dead with ground contact # starkt murkna klena lågor # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14320,7 +14320,7 @@
         <v>125547926</v>
       </c>
       <c r="B115" t="n">
-        <v>95685</v>
+        <v>95688</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>125547900</v>
       </c>
       <c r="B116" t="n">
-        <v>74877</v>
+        <v>74878</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>125556037</v>
       </c>
       <c r="B117" t="n">
-        <v>95780</v>
+        <v>95783</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>125557853</v>
       </c>
       <c r="B118" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>125555995</v>
       </c>
       <c r="B119" t="n">
-        <v>95576</v>
+        <v>95579</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>125556666</v>
       </c>
       <c r="B120" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>125580232</v>
       </c>
       <c r="B121" t="n">
-        <v>102560</v>
+        <v>102563</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15152,10 +15152,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125580133</v>
+        <v>125556711</v>
       </c>
       <c r="B122" t="n">
-        <v>100513</v>
+        <v>80106</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15163,42 +15163,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471456</v>
+        <v>471311</v>
       </c>
       <c r="R122" t="n">
-        <v>6609465</v>
+        <v>6609624</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15243,30 +15238,30 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>grov kalkgranskog</t>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Asp.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125556711</v>
+        <v>125580133</v>
       </c>
       <c r="B123" t="n">
-        <v>80105</v>
+        <v>100516</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15274,37 +15269,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471311</v>
+        <v>471456</v>
       </c>
       <c r="R123" t="n">
-        <v>6609624</v>
+        <v>6609465</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15349,20 +15349,20 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Asp.</t>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>grov kalkgranskog</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -15372,7 +15372,7 @@
         <v>125556114</v>
       </c>
       <c r="B124" t="n">
-        <v>80005</v>
+        <v>80006</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>125580376</v>
       </c>
       <c r="B125" t="n">
-        <v>102560</v>
+        <v>102563</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>125639241</v>
       </c>
       <c r="B126" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>125638955</v>
       </c>
       <c r="B127" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>125639232</v>
       </c>
       <c r="B128" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15957,10 +15957,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125638580</v>
+        <v>125639216</v>
       </c>
       <c r="B129" t="n">
-        <v>95684</v>
+        <v>100516</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15968,28 +15968,28 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>471393</v>
+        <v>471261</v>
       </c>
       <c r="R129" t="n">
-        <v>6609458</v>
+        <v>6609384</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16047,31 +16047,6 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Stump # murken stubbe # Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -16088,10 +16063,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125639216</v>
+        <v>125638580</v>
       </c>
       <c r="B130" t="n">
-        <v>100513</v>
+        <v>95687</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16099,28 +16074,28 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -16131,10 +16106,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>471261</v>
+        <v>471393</v>
       </c>
       <c r="R130" t="n">
-        <v>6609384</v>
+        <v>6609458</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16178,6 +16153,31 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Stump # murken stubbe # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -16194,10 +16194,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125638940</v>
+        <v>125638819</v>
       </c>
       <c r="B131" t="n">
-        <v>100513</v>
+        <v>101420</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16205,28 +16205,36 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -16237,10 +16245,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>471288</v>
+        <v>471334</v>
       </c>
       <c r="R131" t="n">
-        <v>6609428</v>
+        <v>6609447</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16287,7 +16295,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -16305,10 +16313,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125639081</v>
+        <v>125638940</v>
       </c>
       <c r="B132" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16348,10 +16356,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>471281</v>
+        <v>471288</v>
       </c>
       <c r="R132" t="n">
-        <v>6609438</v>
+        <v>6609428</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16398,7 +16406,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -16416,10 +16424,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125638819</v>
+        <v>125639081</v>
       </c>
       <c r="B133" t="n">
-        <v>101417</v>
+        <v>100516</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16427,36 +16435,28 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -16467,10 +16467,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471334</v>
+        <v>471281</v>
       </c>
       <c r="R133" t="n">
-        <v>6609447</v>
+        <v>6609438</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -16535,10 +16535,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125639177</v>
+        <v>125638551</v>
       </c>
       <c r="B134" t="n">
-        <v>101417</v>
+        <v>95567</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16546,38 +16546,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -16586,10 +16574,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>471265</v>
+        <v>471386</v>
       </c>
       <c r="R134" t="n">
-        <v>6609407</v>
+        <v>6609448</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16633,6 +16621,21 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -16649,10 +16652,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125638915</v>
+        <v>125647849</v>
       </c>
       <c r="B135" t="n">
-        <v>100513</v>
+        <v>95191</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16660,42 +16663,38 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>222498</v>
+        <v>2387</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471306</v>
+        <v>471232</v>
       </c>
       <c r="R135" t="n">
-        <v>6609456</v>
+        <v>6609657</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16722,12 +16721,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16740,30 +16739,25 @@
       <c r="AG135" t="b">
         <v>0</v>
       </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125638551</v>
+        <v>125639177</v>
       </c>
       <c r="B136" t="n">
-        <v>95564</v>
+        <v>101420</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16771,26 +16765,38 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -16799,10 +16805,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471386</v>
+        <v>471265</v>
       </c>
       <c r="R136" t="n">
-        <v>6609448</v>
+        <v>6609407</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16846,21 +16852,6 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -16877,10 +16868,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125647849</v>
+        <v>125638915</v>
       </c>
       <c r="B137" t="n">
-        <v>95188</v>
+        <v>100516</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16888,38 +16879,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2387</v>
+        <v>222498</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471232</v>
+        <v>471306</v>
       </c>
       <c r="R137" t="n">
-        <v>6609657</v>
+        <v>6609456</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16946,12 +16941,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16964,15 +16959,20 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
         <v>125638871</v>
       </c>
       <c r="B138" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17098,10 +17098,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125638457</v>
+        <v>125638618</v>
       </c>
       <c r="B139" t="n">
-        <v>95564</v>
+        <v>101420</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17109,26 +17109,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -17137,10 +17149,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471350</v>
+        <v>471408</v>
       </c>
       <c r="R139" t="n">
-        <v>6609454</v>
+        <v>6609463</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17170,9 +17182,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17187,7 +17209,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17205,10 +17227,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125638618</v>
+        <v>125638457</v>
       </c>
       <c r="B140" t="n">
-        <v>101417</v>
+        <v>95567</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17216,38 +17238,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -17256,10 +17266,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>471408</v>
+        <v>471350</v>
       </c>
       <c r="R140" t="n">
-        <v>6609463</v>
+        <v>6609454</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17289,19 +17299,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17337,7 +17337,7 @@
         <v>125647908</v>
       </c>
       <c r="B141" t="n">
-        <v>97070</v>
+        <v>97073</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>125638455</v>
       </c>
       <c r="B142" t="n">
-        <v>95576</v>
+        <v>95579</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17543,10 +17543,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125639406</v>
+        <v>125638876</v>
       </c>
       <c r="B143" t="n">
-        <v>100513</v>
+        <v>102836</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17554,21 +17554,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471294</v>
+        <v>471319</v>
       </c>
       <c r="R143" t="n">
-        <v>6609352</v>
+        <v>6609451</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17654,10 +17654,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125638876</v>
+        <v>125639406</v>
       </c>
       <c r="B144" t="n">
-        <v>102833</v>
+        <v>100516</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17665,21 +17665,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471319</v>
+        <v>471294</v>
       </c>
       <c r="R144" t="n">
-        <v>6609451</v>
+        <v>6609352</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17768,7 +17768,7 @@
         <v>125638893</v>
       </c>
       <c r="B145" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>125638865</v>
       </c>
       <c r="B146" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>125639167</v>
       </c>
       <c r="B147" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>125638825</v>
       </c>
       <c r="B148" t="n">
-        <v>102833</v>
+        <v>102836</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18225,49 +18225,61 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125647918</v>
+        <v>125638785</v>
       </c>
       <c r="B149" t="n">
-        <v>96809</v>
+        <v>102836</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>231</v>
+        <v>222002</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Blå säckmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Calypogeia azurea</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Stotler &amp; Crotz</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471286</v>
+        <v>471336</v>
       </c>
       <c r="R149" t="n">
-        <v>6609621</v>
+        <v>6609447</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18294,12 +18306,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18312,76 +18324,69 @@
       <c r="AG149" t="b">
         <v>0</v>
       </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125638527</v>
+        <v>125647918</v>
       </c>
       <c r="B150" t="n">
-        <v>100420</v>
+        <v>96812</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>222771</v>
+        <v>231</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blå säckmossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Calypogeia azurea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Stotler &amp; Crotz</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471371</v>
+        <v>471286</v>
       </c>
       <c r="R150" t="n">
-        <v>6609452</v>
+        <v>6609621</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18408,12 +18413,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18426,30 +18431,25 @@
       <c r="AG150" t="b">
         <v>0</v>
       </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125638785</v>
+        <v>125638527</v>
       </c>
       <c r="B151" t="n">
-        <v>102833</v>
+        <v>100423</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18457,16 +18457,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -18497,10 +18497,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471336</v>
+        <v>471371</v>
       </c>
       <c r="R151" t="n">
-        <v>6609447</v>
+        <v>6609452</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18568,7 +18568,7 @@
         <v>125638600</v>
       </c>
       <c r="B152" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>125638867</v>
       </c>
       <c r="B153" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>125639147</v>
       </c>
       <c r="B154" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>125647784</v>
       </c>
       <c r="B155" t="n">
-        <v>96904</v>
+        <v>96907</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19026,10 +19026,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125638438</v>
+        <v>125638320</v>
       </c>
       <c r="B156" t="n">
-        <v>98354</v>
+        <v>101420</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19037,26 +19037,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -19077,10 +19077,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471350</v>
+        <v>471329</v>
       </c>
       <c r="R156" t="n">
-        <v>6609454</v>
+        <v>6609462</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19121,13 +19121,12 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -19145,10 +19144,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125638320</v>
+        <v>125638438</v>
       </c>
       <c r="B157" t="n">
-        <v>101417</v>
+        <v>98357</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19156,26 +19155,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -19185,7 +19184,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -19196,10 +19195,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471329</v>
+        <v>471350</v>
       </c>
       <c r="R157" t="n">
-        <v>6609462</v>
+        <v>6609454</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19240,12 +19239,13 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -19266,7 +19266,7 @@
         <v>125638823</v>
       </c>
       <c r="B158" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>125638903</v>
       </c>
       <c r="B159" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>125638625</v>
       </c>
       <c r="B160" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>125638720</v>
       </c>
       <c r="B161" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19751,10 +19751,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125639134</v>
+        <v>125638831</v>
       </c>
       <c r="B162" t="n">
-        <v>100513</v>
+        <v>98357</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19762,25 +19762,33 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19794,10 +19802,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471271</v>
+        <v>471334</v>
       </c>
       <c r="R162" t="n">
-        <v>6609429</v>
+        <v>6609447</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19841,6 +19849,11 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -19857,10 +19870,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125638831</v>
+        <v>125639134</v>
       </c>
       <c r="B163" t="n">
-        <v>98354</v>
+        <v>100516</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19868,33 +19881,25 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19908,10 +19913,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471334</v>
+        <v>471271</v>
       </c>
       <c r="R163" t="n">
-        <v>6609447</v>
+        <v>6609429</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19955,11 +19960,6 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19976,10 +19976,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125638908</v>
+        <v>125639036</v>
       </c>
       <c r="B164" t="n">
-        <v>102833</v>
+        <v>95579</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19987,30 +19987,26 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -20019,10 +20015,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471306</v>
+        <v>471281</v>
       </c>
       <c r="R164" t="n">
-        <v>6609456</v>
+        <v>6609438</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20069,7 +20065,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -20090,7 +20086,7 @@
         <v>125638375</v>
       </c>
       <c r="B165" t="n">
-        <v>95564</v>
+        <v>95567</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20193,10 +20189,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125639036</v>
+        <v>125638908</v>
       </c>
       <c r="B166" t="n">
-        <v>95576</v>
+        <v>102836</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20204,26 +20200,30 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471281</v>
+        <v>471306</v>
       </c>
       <c r="R166" t="n">
-        <v>6609438</v>
+        <v>6609456</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -20300,61 +20300,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125638348</v>
+        <v>125647825</v>
       </c>
       <c r="B167" t="n">
-        <v>98354</v>
+        <v>96587</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>219847</v>
+        <v>53</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471329</v>
+        <v>471311</v>
       </c>
       <c r="R167" t="n">
-        <v>6609462</v>
+        <v>6609467</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20381,12 +20369,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20395,33 +20383,34 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125638771</v>
+        <v>125638348</v>
       </c>
       <c r="B168" t="n">
-        <v>101417</v>
+        <v>98357</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20429,26 +20418,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -20458,7 +20447,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -20469,10 +20458,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471336</v>
+        <v>471329</v>
       </c>
       <c r="R168" t="n">
-        <v>6609447</v>
+        <v>6609462</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20513,13 +20502,12 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20537,49 +20525,61 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125647825</v>
+        <v>125638771</v>
       </c>
       <c r="B169" t="n">
-        <v>96584</v>
+        <v>101420</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471311</v>
+        <v>471336</v>
       </c>
       <c r="R169" t="n">
-        <v>6609467</v>
+        <v>6609447</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20606,12 +20606,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20624,20 +20624,20 @@
       <c r="AG169" t="b">
         <v>0</v>
       </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -20647,7 +20647,7 @@
         <v>125638463</v>
       </c>
       <c r="B170" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20759,10 +20759,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125638361</v>
+        <v>125638511</v>
       </c>
       <c r="B171" t="n">
-        <v>102833</v>
+        <v>95567</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20770,38 +20770,26 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222002</v>
+        <v>2809</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -20810,10 +20798,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471329</v>
+        <v>471371</v>
       </c>
       <c r="R171" t="n">
-        <v>6609462</v>
+        <v>6609452</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20854,12 +20842,23 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -20877,10 +20876,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125638917</v>
+        <v>125638361</v>
       </c>
       <c r="B172" t="n">
-        <v>103762</v>
+        <v>102836</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20888,16 +20887,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -20928,10 +20927,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471306</v>
+        <v>471329</v>
       </c>
       <c r="R172" t="n">
-        <v>6609456</v>
+        <v>6609462</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20972,13 +20971,12 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -20996,10 +20994,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125638511</v>
+        <v>125638917</v>
       </c>
       <c r="B173" t="n">
-        <v>95564</v>
+        <v>103765</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21007,26 +21005,38 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2809</v>
+        <v>222412</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -21035,10 +21045,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471371</v>
+        <v>471306</v>
       </c>
       <c r="R173" t="n">
-        <v>6609452</v>
+        <v>6609456</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -21085,17 +21095,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -21242,10 +21242,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125691817</v>
+        <v>125692508</v>
       </c>
       <c r="B175" t="n">
-        <v>101417</v>
+        <v>100423</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21253,26 +21253,26 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -21293,10 +21293,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471334</v>
+        <v>471352</v>
       </c>
       <c r="R175" t="n">
-        <v>6609428</v>
+        <v>6609490</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21356,10 +21356,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125691568</v>
+        <v>125691817</v>
       </c>
       <c r="B176" t="n">
-        <v>100513</v>
+        <v>101420</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21367,26 +21367,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -21407,10 +21407,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471299</v>
+        <v>471334</v>
       </c>
       <c r="R176" t="n">
-        <v>6609407</v>
+        <v>6609428</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -21470,10 +21470,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125692508</v>
+        <v>125691568</v>
       </c>
       <c r="B177" t="n">
-        <v>100420</v>
+        <v>100516</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21481,21 +21481,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -21521,10 +21521,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471352</v>
+        <v>471299</v>
       </c>
       <c r="R177" t="n">
-        <v>6609490</v>
+        <v>6609407</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -21587,7 +21587,7 @@
         <v>125693285</v>
       </c>
       <c r="B178" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>125688723</v>
       </c>
       <c r="B179" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21796,10 +21796,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125691596</v>
+        <v>125693315</v>
       </c>
       <c r="B180" t="n">
-        <v>102833</v>
+        <v>95688</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21807,28 +21807,28 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>222002</v>
+        <v>2819</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -21839,10 +21839,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471299</v>
+        <v>471315</v>
       </c>
       <c r="R180" t="n">
-        <v>6609407</v>
+        <v>6609611</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21886,6 +21886,19 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
@@ -21902,10 +21915,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125694456</v>
+        <v>125691638</v>
       </c>
       <c r="B181" t="n">
-        <v>102833</v>
+        <v>95687</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21913,28 +21926,28 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>222002</v>
+        <v>2818</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -21945,10 +21958,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471315</v>
+        <v>471299</v>
       </c>
       <c r="R181" t="n">
-        <v>6609388</v>
+        <v>6609407</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21975,12 +21988,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21993,9 +22006,24 @@
       <c r="AG181" t="b">
         <v>0</v>
       </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -22013,10 +22041,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125691772</v>
+        <v>125692947</v>
       </c>
       <c r="B182" t="n">
-        <v>102833</v>
+        <v>95579</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22024,34 +22052,26 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>222002</v>
+        <v>2813</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -22060,10 +22080,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471330</v>
+        <v>471213</v>
       </c>
       <c r="R182" t="n">
-        <v>6609444</v>
+        <v>6609721</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22126,7 +22146,7 @@
         <v>125691522</v>
       </c>
       <c r="B183" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22233,10 +22253,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125691638</v>
+        <v>125691596</v>
       </c>
       <c r="B184" t="n">
-        <v>95684</v>
+        <v>102836</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22244,28 +22264,28 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2818</v>
+        <v>222002</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -22323,26 +22343,6 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gråal</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # murken låga # Alnus incana</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
@@ -22359,10 +22359,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125692947</v>
+        <v>125694456</v>
       </c>
       <c r="B185" t="n">
-        <v>95576</v>
+        <v>102836</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22370,26 +22370,30 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -22398,10 +22402,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471213</v>
+        <v>471315</v>
       </c>
       <c r="R185" t="n">
-        <v>6609721</v>
+        <v>6609388</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22428,12 +22432,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22445,6 +22449,11 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
@@ -22461,10 +22470,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125693315</v>
+        <v>125691772</v>
       </c>
       <c r="B186" t="n">
-        <v>95685</v>
+        <v>102836</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22472,28 +22481,32 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2819</v>
+        <v>222002</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -22504,10 +22517,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471315</v>
+        <v>471330</v>
       </c>
       <c r="R186" t="n">
-        <v>6609611</v>
+        <v>6609444</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -22551,19 +22564,6 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN186" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Stump # murken stubbe</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
@@ -22583,7 +22583,7 @@
         <v>125691671</v>
       </c>
       <c r="B187" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>125691752</v>
       </c>
       <c r="B188" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22808,10 +22808,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125691775</v>
+        <v>125691504</v>
       </c>
       <c r="B189" t="n">
-        <v>106702</v>
+        <v>100516</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22819,36 +22819,28 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>219686</v>
+        <v>222498</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
@@ -22859,10 +22851,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471330</v>
+        <v>471256</v>
       </c>
       <c r="R189" t="n">
-        <v>6609444</v>
+        <v>6609375</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22895,11 +22887,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>under gran</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22927,10 +22914,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125691504</v>
+        <v>125691545</v>
       </c>
       <c r="B190" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22970,10 +22957,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471256</v>
+        <v>471275</v>
       </c>
       <c r="R190" t="n">
-        <v>6609375</v>
+        <v>6609399</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -23033,10 +23020,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125691545</v>
+        <v>125691775</v>
       </c>
       <c r="B191" t="n">
-        <v>100513</v>
+        <v>106705</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23044,28 +23031,36 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -23076,10 +23071,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471275</v>
+        <v>471330</v>
       </c>
       <c r="R191" t="n">
-        <v>6609399</v>
+        <v>6609444</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -23112,6 +23107,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>under gran</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -23142,7 +23142,7 @@
         <v>125692480</v>
       </c>
       <c r="B192" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>125692234</v>
       </c>
       <c r="B193" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>125692324</v>
       </c>
       <c r="B194" t="n">
-        <v>106702</v>
+        <v>106705</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23470,10 +23470,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125691650</v>
+        <v>125692303</v>
       </c>
       <c r="B195" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23498,13 +23498,13 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
@@ -23513,10 +23513,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471309</v>
+        <v>471447</v>
       </c>
       <c r="R195" t="n">
-        <v>6609409</v>
+        <v>6609354</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23560,6 +23560,11 @@
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
@@ -23576,10 +23581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125692303</v>
+        <v>125691650</v>
       </c>
       <c r="B196" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23604,13 +23609,13 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
@@ -23619,10 +23624,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>471447</v>
+        <v>471309</v>
       </c>
       <c r="R196" t="n">
-        <v>6609354</v>
+        <v>6609409</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23666,11 +23671,6 @@
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
@@ -23687,10 +23687,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125693289</v>
+        <v>125691655</v>
       </c>
       <c r="B197" t="n">
-        <v>100513</v>
+        <v>102836</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23698,28 +23698,24 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -23734,10 +23730,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471315</v>
+        <v>471309</v>
       </c>
       <c r="R197" t="n">
-        <v>6609611</v>
+        <v>6609409</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23800,7 +23796,7 @@
         <v>125692378</v>
       </c>
       <c r="B198" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23906,7 +23902,7 @@
         <v>125691756</v>
       </c>
       <c r="B199" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -24009,10 +24005,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125691655</v>
+        <v>125693289</v>
       </c>
       <c r="B200" t="n">
-        <v>102833</v>
+        <v>100516</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24020,24 +24016,28 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
@@ -24052,10 +24052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471309</v>
+        <v>471315</v>
       </c>
       <c r="R200" t="n">
-        <v>6609409</v>
+        <v>6609611</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24115,10 +24115,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125694447</v>
+        <v>125692924</v>
       </c>
       <c r="B201" t="n">
-        <v>100513</v>
+        <v>95579</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24126,30 +24126,26 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -24158,10 +24154,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471315</v>
+        <v>471200</v>
       </c>
       <c r="R201" t="n">
-        <v>6609388</v>
+        <v>6609727</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24188,12 +24184,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24205,11 +24201,6 @@
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -24226,10 +24217,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125691940</v>
+        <v>125694447</v>
       </c>
       <c r="B202" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24269,10 +24260,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>471421</v>
+        <v>471315</v>
       </c>
       <c r="R202" t="n">
-        <v>6609338</v>
+        <v>6609388</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24299,12 +24290,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -24316,6 +24307,11 @@
       <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
@@ -24332,10 +24328,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125692924</v>
+        <v>125691940</v>
       </c>
       <c r="B203" t="n">
-        <v>95576</v>
+        <v>100516</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24343,26 +24339,30 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
@@ -24371,10 +24371,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>471200</v>
+        <v>471421</v>
       </c>
       <c r="R203" t="n">
-        <v>6609727</v>
+        <v>6609338</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24437,7 +24437,7 @@
         <v>125691675</v>
       </c>
       <c r="B204" t="n">
-        <v>102833</v>
+        <v>102836</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24540,10 +24540,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125691724</v>
+        <v>125691555</v>
       </c>
       <c r="B205" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -24591,10 +24591,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471295</v>
+        <v>471277</v>
       </c>
       <c r="R205" t="n">
-        <v>6609415</v>
+        <v>6609410</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24654,10 +24654,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>125691555</v>
+        <v>125693221</v>
       </c>
       <c r="B206" t="n">
-        <v>101417</v>
+        <v>100516</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24665,36 +24665,28 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
@@ -24705,10 +24697,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>471277</v>
+        <v>471325</v>
       </c>
       <c r="R206" t="n">
-        <v>6609410</v>
+        <v>6609612</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24768,10 +24760,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>125693221</v>
+        <v>125691724</v>
       </c>
       <c r="B207" t="n">
-        <v>100513</v>
+        <v>101420</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24779,28 +24771,36 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -24811,10 +24811,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>471325</v>
+        <v>471295</v>
       </c>
       <c r="R207" t="n">
-        <v>6609612</v>
+        <v>6609415</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24874,10 +24874,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>125691701</v>
+        <v>125694704</v>
       </c>
       <c r="B208" t="n">
-        <v>100513</v>
+        <v>95567</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24885,34 +24885,26 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
@@ -24921,10 +24913,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>471323</v>
+        <v>471383</v>
       </c>
       <c r="R208" t="n">
-        <v>6609406</v>
+        <v>6609437</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24951,12 +24943,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24968,6 +24960,21 @@
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>blockrik kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
@@ -24984,10 +24991,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>125692746</v>
+        <v>125692901</v>
       </c>
       <c r="B209" t="n">
-        <v>95576</v>
+        <v>95579</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25023,10 +25030,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471175</v>
+        <v>471195</v>
       </c>
       <c r="R209" t="n">
-        <v>6609737</v>
+        <v>6609738</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25086,10 +25093,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125692901</v>
+        <v>125692746</v>
       </c>
       <c r="B210" t="n">
-        <v>95576</v>
+        <v>95579</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25125,10 +25132,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471195</v>
+        <v>471175</v>
       </c>
       <c r="R210" t="n">
-        <v>6609738</v>
+        <v>6609737</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25188,10 +25195,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125694704</v>
+        <v>125691701</v>
       </c>
       <c r="B211" t="n">
-        <v>95564</v>
+        <v>100516</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25199,26 +25206,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
@@ -25227,10 +25242,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471383</v>
+        <v>471323</v>
       </c>
       <c r="R211" t="n">
-        <v>6609437</v>
+        <v>6609406</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25257,12 +25272,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25274,21 +25289,6 @@
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>blockrik kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
@@ -25305,10 +25305,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>125692396</v>
+        <v>125688737</v>
       </c>
       <c r="B212" t="n">
-        <v>95564</v>
+        <v>101420</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25316,21 +25316,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -25344,10 +25344,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471375</v>
+        <v>471312</v>
       </c>
       <c r="R212" t="n">
-        <v>6609431</v>
+        <v>6609616</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25391,16 +25391,6 @@
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
@@ -25417,10 +25407,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>125693046</v>
+        <v>125693203</v>
       </c>
       <c r="B213" t="n">
-        <v>97209</v>
+        <v>103765</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25428,16 +25418,16 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221945</v>
+        <v>222412</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -25445,9 +25435,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
@@ -25456,10 +25458,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471207</v>
+        <v>471315</v>
       </c>
       <c r="R213" t="n">
-        <v>6609720</v>
+        <v>6609562</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25519,10 +25521,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125688737</v>
+        <v>125692396</v>
       </c>
       <c r="B214" t="n">
-        <v>101417</v>
+        <v>95567</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25530,21 +25532,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -25558,10 +25560,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471312</v>
+        <v>471375</v>
       </c>
       <c r="R214" t="n">
-        <v>6609616</v>
+        <v>6609431</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25605,6 +25607,16 @@
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
@@ -25624,7 +25636,7 @@
         <v>125691532</v>
       </c>
       <c r="B215" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25731,10 +25743,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>125693203</v>
+        <v>125693046</v>
       </c>
       <c r="B216" t="n">
-        <v>103762</v>
+        <v>97212</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25742,16 +25754,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -25759,21 +25771,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -25782,10 +25782,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471315</v>
+        <v>471207</v>
       </c>
       <c r="R216" t="n">
-        <v>6609562</v>
+        <v>6609720</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25845,32 +25845,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>125694805</v>
+        <v>125691883</v>
       </c>
       <c r="B217" t="n">
-        <v>102560</v>
+        <v>103765</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>223246</v>
+        <v>222412</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -25896,10 +25896,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471442</v>
+        <v>471342</v>
       </c>
       <c r="R217" t="n">
-        <v>6609507</v>
+        <v>6609418</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25926,17 +25926,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>klent träd</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25964,10 +25959,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>125691883</v>
+        <v>125693113</v>
       </c>
       <c r="B218" t="n">
-        <v>103762</v>
+        <v>106705</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25975,16 +25970,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>222412</v>
+        <v>219686</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -25994,7 +25989,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -26004,7 +25999,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -26015,10 +26010,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471342</v>
+        <v>471338</v>
       </c>
       <c r="R218" t="n">
-        <v>6609418</v>
+        <v>6609551</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -26078,37 +26073,37 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>125693113</v>
+        <v>125694805</v>
       </c>
       <c r="B219" t="n">
-        <v>106702</v>
+        <v>102563</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>219686</v>
+        <v>223246</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -26118,7 +26113,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -26129,10 +26124,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471338</v>
+        <v>471442</v>
       </c>
       <c r="R219" t="n">
-        <v>6609551</v>
+        <v>6609507</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -26159,12 +26154,17 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>klent träd</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26195,7 +26195,7 @@
         <v>125692474</v>
       </c>
       <c r="B220" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>125692169</v>
       </c>
       <c r="B221" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>125691678</v>
       </c>
       <c r="B222" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>125691689</v>
       </c>
       <c r="B223" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>125694768</v>
       </c>
       <c r="B224" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>125692758</v>
       </c>
       <c r="B225" t="n">
-        <v>95576</v>
+        <v>95579</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26854,10 +26854,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>125691768</v>
+        <v>125692269</v>
       </c>
       <c r="B226" t="n">
-        <v>102833</v>
+        <v>100516</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26865,21 +26865,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -26897,10 +26897,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>471316</v>
+        <v>471437</v>
       </c>
       <c r="R226" t="n">
-        <v>6609440</v>
+        <v>6609338</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26960,10 +26960,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>125692269</v>
+        <v>125692655</v>
       </c>
       <c r="B227" t="n">
-        <v>100513</v>
+        <v>95688</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26971,28 +26971,28 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>222498</v>
+        <v>2819</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -27003,10 +27003,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>471437</v>
+        <v>471404</v>
       </c>
       <c r="R227" t="n">
-        <v>6609338</v>
+        <v>6609514</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -27050,6 +27050,19 @@
       <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -27066,10 +27079,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>125692655</v>
+        <v>125691768</v>
       </c>
       <c r="B228" t="n">
-        <v>95685</v>
+        <v>102836</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27077,28 +27090,28 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2819</v>
+        <v>222002</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -27109,10 +27122,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>471404</v>
+        <v>471316</v>
       </c>
       <c r="R228" t="n">
-        <v>6609514</v>
+        <v>6609440</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -27156,19 +27169,6 @@
       <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN228" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Stump # murken stubbe</t>
-        </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
@@ -27188,7 +27188,7 @@
         <v>125693086</v>
       </c>
       <c r="B229" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>125694224</v>
       </c>
       <c r="B230" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>125691600</v>
       </c>
       <c r="B231" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>125692503</v>
       </c>
       <c r="B232" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>125691592</v>
       </c>
       <c r="B233" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27752,10 +27752,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>125691658</v>
+        <v>125691551</v>
       </c>
       <c r="B234" t="n">
-        <v>101417</v>
+        <v>100516</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27763,36 +27763,32 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -27803,10 +27799,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>471309</v>
+        <v>471277</v>
       </c>
       <c r="R234" t="n">
-        <v>6609409</v>
+        <v>6609410</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27869,7 +27865,7 @@
         <v>125691824</v>
       </c>
       <c r="B235" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27975,7 +27971,7 @@
         <v>125693090</v>
       </c>
       <c r="B236" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28078,10 +28074,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>125691551</v>
+        <v>125691658</v>
       </c>
       <c r="B237" t="n">
-        <v>100513</v>
+        <v>101420</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28089,32 +28085,36 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -28125,10 +28125,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>471277</v>
+        <v>471309</v>
       </c>
       <c r="R237" t="n">
-        <v>6609410</v>
+        <v>6609409</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -28191,7 +28191,7 @@
         <v>125693283</v>
       </c>
       <c r="B238" t="n">
-        <v>95684</v>
+        <v>95687</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>125691487</v>
       </c>
       <c r="B239" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -13666,10 +13666,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125457759</v>
+        <v>125450472</v>
       </c>
       <c r="B110" t="n">
-        <v>106705</v>
+        <v>95687</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13677,36 +13677,28 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219686</v>
+        <v>2818</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -13717,10 +13709,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471362</v>
+        <v>471370</v>
       </c>
       <c r="R110" t="n">
-        <v>6609461</v>
+        <v>6609456</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13750,9 +13742,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13768,6 +13770,29 @@
       <c r="AI110" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13785,10 +13810,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125450472</v>
+        <v>125457759</v>
       </c>
       <c r="B111" t="n">
-        <v>95687</v>
+        <v>106705</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13796,28 +13821,36 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2818</v>
+        <v>219686</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13828,10 +13861,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471370</v>
+        <v>471362</v>
       </c>
       <c r="R111" t="n">
-        <v>6609456</v>
+        <v>6609461</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13861,19 +13894,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13889,29 +13912,6 @@
       <c r="AI111" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN111" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>3 substratenheter # Horizontal, dead with ground contact # två klena murkna lågor och en murken stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -17765,10 +17765,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125638893</v>
+        <v>125638825</v>
       </c>
       <c r="B145" t="n">
-        <v>101420</v>
+        <v>102836</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17776,36 +17776,28 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -17816,10 +17808,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471306</v>
+        <v>471334</v>
       </c>
       <c r="R145" t="n">
-        <v>6609456</v>
+        <v>6609447</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17854,6 +17846,11 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -17866,7 +17863,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17884,10 +17881,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125638865</v>
+        <v>125638893</v>
       </c>
       <c r="B146" t="n">
-        <v>100423</v>
+        <v>101420</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17895,21 +17892,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -17935,10 +17932,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471319</v>
+        <v>471306</v>
       </c>
       <c r="R146" t="n">
-        <v>6609451</v>
+        <v>6609456</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18003,10 +18000,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125639167</v>
+        <v>125638865</v>
       </c>
       <c r="B147" t="n">
-        <v>100516</v>
+        <v>100423</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18014,28 +18011,36 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -18046,10 +18051,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471265</v>
+        <v>471319</v>
       </c>
       <c r="R147" t="n">
-        <v>6609407</v>
+        <v>6609451</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18093,6 +18098,11 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18109,10 +18119,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125638825</v>
+        <v>125639167</v>
       </c>
       <c r="B148" t="n">
-        <v>102836</v>
+        <v>100516</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18120,21 +18130,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18152,10 +18162,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471334</v>
+        <v>471265</v>
       </c>
       <c r="R148" t="n">
-        <v>6609447</v>
+        <v>6609407</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18190,11 +18200,6 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -18204,11 +18209,6 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18225,61 +18225,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125638785</v>
+        <v>125647918</v>
       </c>
       <c r="B149" t="n">
-        <v>102836</v>
+        <v>96812</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222002</v>
+        <v>231</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blå säckmossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Calypogeia azurea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Stotler &amp; Crotz</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471336</v>
+        <v>471286</v>
       </c>
       <c r="R149" t="n">
-        <v>6609447</v>
+        <v>6609621</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18306,12 +18294,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18324,69 +18312,76 @@
       <c r="AG149" t="b">
         <v>0</v>
       </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125647918</v>
+        <v>125638785</v>
       </c>
       <c r="B150" t="n">
-        <v>96812</v>
+        <v>102836</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>231</v>
+        <v>222002</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blå säckmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Calypogeia azurea</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Stotler &amp; Crotz</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471286</v>
+        <v>471336</v>
       </c>
       <c r="R150" t="n">
-        <v>6609621</v>
+        <v>6609447</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18413,12 +18408,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18431,15 +18426,20 @@
       <c r="AG150" t="b">
         <v>0</v>
       </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -19976,10 +19976,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125639036</v>
+        <v>125638908</v>
       </c>
       <c r="B164" t="n">
-        <v>95579</v>
+        <v>102836</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19987,26 +19987,30 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -20015,10 +20019,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471281</v>
+        <v>471306</v>
       </c>
       <c r="R164" t="n">
-        <v>6609438</v>
+        <v>6609456</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20065,7 +20069,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -20083,10 +20087,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125638375</v>
+        <v>125639036</v>
       </c>
       <c r="B165" t="n">
-        <v>95567</v>
+        <v>95579</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20094,21 +20098,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20122,10 +20126,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471329</v>
+        <v>471281</v>
       </c>
       <c r="R165" t="n">
-        <v>6609462</v>
+        <v>6609438</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20166,12 +20170,13 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20189,10 +20194,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125638908</v>
+        <v>125638375</v>
       </c>
       <c r="B166" t="n">
-        <v>102836</v>
+        <v>95567</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20200,30 +20205,26 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222002</v>
+        <v>2809</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -20232,10 +20233,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471306</v>
+        <v>471329</v>
       </c>
       <c r="R166" t="n">
-        <v>6609456</v>
+        <v>6609462</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20276,13 +20277,12 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -20300,49 +20300,61 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125647825</v>
+        <v>125638771</v>
       </c>
       <c r="B167" t="n">
-        <v>96587</v>
+        <v>101420</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471311</v>
+        <v>471336</v>
       </c>
       <c r="R167" t="n">
-        <v>6609467</v>
+        <v>6609447</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20369,12 +20381,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20387,20 +20399,20 @@
       <c r="AG167" t="b">
         <v>0</v>
       </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -20525,61 +20537,49 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125638771</v>
+        <v>125647825</v>
       </c>
       <c r="B169" t="n">
-        <v>101420</v>
+        <v>96587</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471336</v>
+        <v>471311</v>
       </c>
       <c r="R169" t="n">
-        <v>6609447</v>
+        <v>6609467</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20606,12 +20606,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20624,20 +20624,20 @@
       <c r="AG169" t="b">
         <v>0</v>
       </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -21242,10 +21242,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125692508</v>
+        <v>125691817</v>
       </c>
       <c r="B175" t="n">
-        <v>100423</v>
+        <v>101420</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21253,26 +21253,26 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -21293,10 +21293,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471352</v>
+        <v>471334</v>
       </c>
       <c r="R175" t="n">
-        <v>6609490</v>
+        <v>6609428</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21356,10 +21356,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125691817</v>
+        <v>125691568</v>
       </c>
       <c r="B176" t="n">
-        <v>101420</v>
+        <v>100516</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21367,26 +21367,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -21407,10 +21407,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471334</v>
+        <v>471299</v>
       </c>
       <c r="R176" t="n">
-        <v>6609428</v>
+        <v>6609407</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -21470,10 +21470,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125691568</v>
+        <v>125692508</v>
       </c>
       <c r="B177" t="n">
-        <v>100516</v>
+        <v>100423</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21481,21 +21481,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -21521,10 +21521,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471299</v>
+        <v>471352</v>
       </c>
       <c r="R177" t="n">
-        <v>6609407</v>
+        <v>6609490</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -23899,7 +23899,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125691756</v>
+        <v>125693289</v>
       </c>
       <c r="B199" t="n">
         <v>100516</v>
@@ -23927,7 +23927,11 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
@@ -23942,10 +23946,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471316</v>
+        <v>471315</v>
       </c>
       <c r="R199" t="n">
-        <v>6609440</v>
+        <v>6609611</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24005,7 +24009,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125693289</v>
+        <v>125691756</v>
       </c>
       <c r="B200" t="n">
         <v>100516</v>
@@ -24033,11 +24037,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
@@ -24052,10 +24052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471315</v>
+        <v>471316</v>
       </c>
       <c r="R200" t="n">
-        <v>6609611</v>
+        <v>6609440</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -25305,10 +25305,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>125688737</v>
+        <v>125691532</v>
       </c>
       <c r="B212" t="n">
-        <v>101420</v>
+        <v>100516</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25316,26 +25316,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
@@ -25344,10 +25352,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471312</v>
+        <v>471263</v>
       </c>
       <c r="R212" t="n">
-        <v>6609616</v>
+        <v>6609389</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25407,10 +25415,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>125693203</v>
+        <v>125688737</v>
       </c>
       <c r="B213" t="n">
-        <v>103765</v>
+        <v>101420</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25418,38 +25426,26 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
@@ -25458,10 +25454,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471315</v>
+        <v>471312</v>
       </c>
       <c r="R213" t="n">
-        <v>6609562</v>
+        <v>6609616</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25521,10 +25517,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125692396</v>
+        <v>125693046</v>
       </c>
       <c r="B214" t="n">
-        <v>95567</v>
+        <v>97212</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25532,21 +25528,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2809</v>
+        <v>221945</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -25560,10 +25556,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471375</v>
+        <v>471207</v>
       </c>
       <c r="R214" t="n">
-        <v>6609431</v>
+        <v>6609720</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25607,16 +25603,6 @@
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
@@ -25633,10 +25619,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>125691532</v>
+        <v>125692396</v>
       </c>
       <c r="B215" t="n">
-        <v>100516</v>
+        <v>95567</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25644,34 +25630,26 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
@@ -25680,10 +25658,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471263</v>
+        <v>471375</v>
       </c>
       <c r="R215" t="n">
-        <v>6609389</v>
+        <v>6609431</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25727,6 +25705,16 @@
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -25743,10 +25731,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>125693046</v>
+        <v>125693203</v>
       </c>
       <c r="B216" t="n">
-        <v>97212</v>
+        <v>103765</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25754,16 +25742,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221945</v>
+        <v>222412</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -25771,9 +25759,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -25782,10 +25782,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471207</v>
+        <v>471315</v>
       </c>
       <c r="R216" t="n">
-        <v>6609720</v>
+        <v>6609562</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -26306,10 +26306,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>125692169</v>
+        <v>125692758</v>
       </c>
       <c r="B221" t="n">
-        <v>98357</v>
+        <v>95579</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26317,38 +26317,26 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>219847</v>
+        <v>2813</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
@@ -26357,10 +26345,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471438</v>
+        <v>471191</v>
       </c>
       <c r="R221" t="n">
-        <v>6609315</v>
+        <v>6609737</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26401,13 +26389,9 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>Källkärr</t>
-        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
@@ -26424,10 +26408,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>125691678</v>
+        <v>125692169</v>
       </c>
       <c r="B222" t="n">
-        <v>100516</v>
+        <v>98357</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26435,25 +26419,33 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K222" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -26467,10 +26459,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>471307</v>
+        <v>471438</v>
       </c>
       <c r="R222" t="n">
-        <v>6609405</v>
+        <v>6609315</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26511,9 +26503,13 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>Källkärr</t>
+        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
@@ -26530,7 +26526,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>125691689</v>
+        <v>125691678</v>
       </c>
       <c r="B223" t="n">
         <v>100516</v>
@@ -26573,10 +26569,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471315</v>
+        <v>471307</v>
       </c>
       <c r="R223" t="n">
-        <v>6609406</v>
+        <v>6609405</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26636,7 +26632,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>125694768</v>
+        <v>125691689</v>
       </c>
       <c r="B224" t="n">
         <v>100516</v>
@@ -26679,10 +26675,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>471450</v>
+        <v>471315</v>
       </c>
       <c r="R224" t="n">
-        <v>6609501</v>
+        <v>6609406</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26709,12 +26705,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26726,16 +26722,6 @@
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>surdråg</t>
-        </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
@@ -26752,10 +26738,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>125692758</v>
+        <v>125694768</v>
       </c>
       <c r="B225" t="n">
-        <v>95579</v>
+        <v>100516</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26763,26 +26749,30 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
@@ -26791,10 +26781,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>471191</v>
+        <v>471450</v>
       </c>
       <c r="R225" t="n">
-        <v>6609737</v>
+        <v>6609501</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26821,12 +26811,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26838,6 +26828,16 @@
       <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>surdråg</t>
+        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
@@ -26854,10 +26854,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>125692269</v>
+        <v>125692655</v>
       </c>
       <c r="B226" t="n">
-        <v>100516</v>
+        <v>95688</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26865,28 +26865,28 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>222498</v>
+        <v>2819</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -26897,10 +26897,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>471437</v>
+        <v>471404</v>
       </c>
       <c r="R226" t="n">
-        <v>6609338</v>
+        <v>6609514</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26944,6 +26944,19 @@
       <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AN226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Stump # murken stubbe</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -26960,10 +26973,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>125692655</v>
+        <v>125691768</v>
       </c>
       <c r="B227" t="n">
-        <v>95688</v>
+        <v>102836</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26971,28 +26984,28 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2819</v>
+        <v>222002</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -27003,10 +27016,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>471404</v>
+        <v>471316</v>
       </c>
       <c r="R227" t="n">
-        <v>6609514</v>
+        <v>6609440</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -27050,19 +27063,6 @@
       <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AN227" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Stump # murken stubbe</t>
-        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -27079,10 +27079,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>125691768</v>
+        <v>125692269</v>
       </c>
       <c r="B228" t="n">
-        <v>102836</v>
+        <v>100516</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27090,21 +27090,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -27122,10 +27122,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>471316</v>
+        <v>471437</v>
       </c>
       <c r="R228" t="n">
-        <v>6609440</v>
+        <v>6609338</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -27409,10 +27409,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>125691600</v>
+        <v>125691592</v>
       </c>
       <c r="B231" t="n">
-        <v>101420</v>
+        <v>100423</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27420,26 +27420,26 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
@@ -27523,7 +27523,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>125692503</v>
+        <v>125691600</v>
       </c>
       <c r="B232" t="n">
         <v>101420</v>
@@ -27553,13 +27553,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
@@ -27570,10 +27574,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>471352</v>
+        <v>471299</v>
       </c>
       <c r="R232" t="n">
-        <v>6609490</v>
+        <v>6609407</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27606,11 +27610,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>många</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -27638,10 +27637,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>125691592</v>
+        <v>125692503</v>
       </c>
       <c r="B233" t="n">
-        <v>100423</v>
+        <v>101420</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27649,36 +27648,32 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
@@ -27689,10 +27684,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>471299</v>
+        <v>471352</v>
       </c>
       <c r="R233" t="n">
-        <v>6609407</v>
+        <v>6609490</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27725,6 +27720,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>många</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -8894,7 +8894,7 @@
         <v>121698315</v>
       </c>
       <c r="B70" t="n">
-        <v>97206</v>
+        <v>97210</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>121698287</v>
       </c>
       <c r="B73" t="n">
-        <v>97206</v>
+        <v>97210</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>121698313</v>
       </c>
       <c r="B74" t="n">
-        <v>97206</v>
+        <v>97210</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>125457870</v>
       </c>
       <c r="B108" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>125457776</v>
       </c>
       <c r="B109" t="n">
-        <v>95579</v>
+        <v>95583</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>125450472</v>
       </c>
       <c r="B110" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>125457759</v>
       </c>
       <c r="B111" t="n">
-        <v>106705</v>
+        <v>106709</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>125457972</v>
       </c>
       <c r="B112" t="n">
-        <v>102563</v>
+        <v>102567</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>125450450</v>
       </c>
       <c r="B113" t="n">
-        <v>95783</v>
+        <v>95787</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>125457874</v>
       </c>
       <c r="B114" t="n">
-        <v>95567</v>
+        <v>95571</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>125547926</v>
       </c>
       <c r="B115" t="n">
-        <v>95688</v>
+        <v>95692</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>125556037</v>
       </c>
       <c r="B117" t="n">
-        <v>95783</v>
+        <v>95787</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>125557853</v>
       </c>
       <c r="B118" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>125555995</v>
       </c>
       <c r="B119" t="n">
-        <v>95579</v>
+        <v>95583</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>125556666</v>
       </c>
       <c r="B120" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>125580232</v>
       </c>
       <c r="B121" t="n">
-        <v>102563</v>
+        <v>102567</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15152,10 +15152,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125556711</v>
+        <v>125580133</v>
       </c>
       <c r="B122" t="n">
-        <v>80106</v>
+        <v>100520</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15163,37 +15163,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471311</v>
+        <v>471456</v>
       </c>
       <c r="R122" t="n">
-        <v>6609624</v>
+        <v>6609465</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15238,30 +15243,30 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Asp.</t>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>grov kalkgranskog</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125580133</v>
+        <v>125556711</v>
       </c>
       <c r="B123" t="n">
-        <v>100516</v>
+        <v>80110</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15269,42 +15274,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471456</v>
+        <v>471311</v>
       </c>
       <c r="R123" t="n">
-        <v>6609465</v>
+        <v>6609624</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15349,20 +15349,20 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>grov kalkgranskog</t>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Asp.</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -15372,7 +15372,7 @@
         <v>125556114</v>
       </c>
       <c r="B124" t="n">
-        <v>80006</v>
+        <v>80010</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>125580376</v>
       </c>
       <c r="B125" t="n">
-        <v>102563</v>
+        <v>102567</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125639241</v>
+        <v>125639232</v>
       </c>
       <c r="B126" t="n">
-        <v>98357</v>
+        <v>100520</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15629,33 +15629,25 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -15732,10 +15724,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125638955</v>
+        <v>125639241</v>
       </c>
       <c r="B127" t="n">
-        <v>101420</v>
+        <v>98361</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15743,26 +15735,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15772,7 +15764,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -15783,10 +15775,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471281</v>
+        <v>471252</v>
       </c>
       <c r="R127" t="n">
-        <v>6609438</v>
+        <v>6609379</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15830,11 +15822,6 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -15851,10 +15838,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125639232</v>
+        <v>125638955</v>
       </c>
       <c r="B128" t="n">
-        <v>100516</v>
+        <v>101424</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15862,28 +15849,36 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -15894,10 +15889,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471252</v>
+        <v>471281</v>
       </c>
       <c r="R128" t="n">
-        <v>6609379</v>
+        <v>6609438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15941,6 +15936,11 @@
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
@@ -15960,7 +15960,7 @@
         <v>125639216</v>
       </c>
       <c r="B129" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>125638580</v>
       </c>
       <c r="B130" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>125638819</v>
       </c>
       <c r="B131" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>125638940</v>
       </c>
       <c r="B132" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>125639081</v>
       </c>
       <c r="B133" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16535,10 +16535,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125638551</v>
+        <v>125639177</v>
       </c>
       <c r="B134" t="n">
-        <v>95567</v>
+        <v>101424</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16546,26 +16546,38 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -16574,10 +16586,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>471386</v>
+        <v>471265</v>
       </c>
       <c r="R134" t="n">
-        <v>6609448</v>
+        <v>6609407</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16621,21 +16633,6 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -16652,10 +16649,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125647849</v>
+        <v>125638915</v>
       </c>
       <c r="B135" t="n">
-        <v>95191</v>
+        <v>100520</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16663,38 +16660,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2387</v>
+        <v>222498</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471232</v>
+        <v>471306</v>
       </c>
       <c r="R135" t="n">
-        <v>6609657</v>
+        <v>6609456</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16721,12 +16722,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16739,25 +16740,30 @@
       <c r="AG135" t="b">
         <v>0</v>
       </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125639177</v>
+        <v>125638551</v>
       </c>
       <c r="B136" t="n">
-        <v>101420</v>
+        <v>95571</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16765,38 +16771,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -16805,10 +16799,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471265</v>
+        <v>471386</v>
       </c>
       <c r="R136" t="n">
-        <v>6609407</v>
+        <v>6609448</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16852,6 +16846,21 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -16868,10 +16877,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125638915</v>
+        <v>125647849</v>
       </c>
       <c r="B137" t="n">
-        <v>100516</v>
+        <v>95195</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16879,42 +16888,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222498</v>
+        <v>2387</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471306</v>
+        <v>471232</v>
       </c>
       <c r="R137" t="n">
-        <v>6609456</v>
+        <v>6609657</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16941,12 +16946,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16959,20 +16964,15 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
         <v>125638871</v>
       </c>
       <c r="B138" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17098,10 +17098,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125638618</v>
+        <v>125638457</v>
       </c>
       <c r="B139" t="n">
-        <v>101420</v>
+        <v>95571</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17109,38 +17109,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221235</v>
+        <v>2809</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -17149,10 +17137,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471408</v>
+        <v>471350</v>
       </c>
       <c r="R139" t="n">
-        <v>6609463</v>
+        <v>6609454</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17182,19 +17170,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17209,7 +17187,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -17227,10 +17205,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125638457</v>
+        <v>125638618</v>
       </c>
       <c r="B140" t="n">
-        <v>95567</v>
+        <v>101424</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17238,26 +17216,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2809</v>
+        <v>221235</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -17266,10 +17256,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>471350</v>
+        <v>471408</v>
       </c>
       <c r="R140" t="n">
-        <v>6609454</v>
+        <v>6609463</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17299,9 +17289,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -17334,49 +17334,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125647908</v>
+        <v>125639406</v>
       </c>
       <c r="B141" t="n">
-        <v>97073</v>
+        <v>100520</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2617</v>
+        <v>222498</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471286</v>
+        <v>471294</v>
       </c>
       <c r="R141" t="n">
-        <v>6609621</v>
+        <v>6609352</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17403,12 +17407,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17421,25 +17425,30 @@
       <c r="AG141" t="b">
         <v>0</v>
       </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125638455</v>
+        <v>125638876</v>
       </c>
       <c r="B142" t="n">
-        <v>95579</v>
+        <v>102840</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17447,26 +17456,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2813</v>
+        <v>222002</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -17475,10 +17488,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471350</v>
+        <v>471319</v>
       </c>
       <c r="R142" t="n">
-        <v>6609454</v>
+        <v>6609451</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17525,7 +17538,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -17543,53 +17556,49 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125638876</v>
+        <v>125647908</v>
       </c>
       <c r="B143" t="n">
-        <v>102836</v>
+        <v>97077</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222002</v>
+        <v>2617</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471319</v>
+        <v>471286</v>
       </c>
       <c r="R143" t="n">
-        <v>6609451</v>
+        <v>6609621</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17616,12 +17625,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17634,30 +17643,25 @@
       <c r="AG143" t="b">
         <v>0</v>
       </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
-      </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125639406</v>
+        <v>125638455</v>
       </c>
       <c r="B144" t="n">
-        <v>100516</v>
+        <v>95583</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17665,30 +17669,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471294</v>
+        <v>471350</v>
       </c>
       <c r="R144" t="n">
-        <v>6609352</v>
+        <v>6609454</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17765,10 +17765,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125638825</v>
+        <v>125638893</v>
       </c>
       <c r="B145" t="n">
-        <v>102836</v>
+        <v>101424</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17776,28 +17776,36 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>222002</v>
+        <v>221235</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -17808,10 +17816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471334</v>
+        <v>471306</v>
       </c>
       <c r="R145" t="n">
-        <v>6609447</v>
+        <v>6609456</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17846,11 +17854,6 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -17863,7 +17866,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17881,10 +17884,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125638893</v>
+        <v>125638865</v>
       </c>
       <c r="B146" t="n">
-        <v>101420</v>
+        <v>100427</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17892,21 +17895,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -17932,10 +17935,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471306</v>
+        <v>471319</v>
       </c>
       <c r="R146" t="n">
-        <v>6609456</v>
+        <v>6609451</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18000,10 +18003,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125638865</v>
+        <v>125639167</v>
       </c>
       <c r="B147" t="n">
-        <v>100423</v>
+        <v>100520</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18011,36 +18014,28 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -18051,10 +18046,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471319</v>
+        <v>471265</v>
       </c>
       <c r="R147" t="n">
-        <v>6609451</v>
+        <v>6609407</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18098,11 +18093,6 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>kalkgranskog</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18119,10 +18109,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125639167</v>
+        <v>125638825</v>
       </c>
       <c r="B148" t="n">
-        <v>100516</v>
+        <v>102840</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18130,21 +18120,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18162,10 +18152,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471265</v>
+        <v>471334</v>
       </c>
       <c r="R148" t="n">
-        <v>6609407</v>
+        <v>6609447</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18200,6 +18190,11 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -18209,6 +18204,11 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18228,7 +18228,7 @@
         <v>125647918</v>
       </c>
       <c r="B149" t="n">
-        <v>96812</v>
+        <v>96816</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18327,10 +18327,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125638785</v>
+        <v>125638527</v>
       </c>
       <c r="B150" t="n">
-        <v>102836</v>
+        <v>100427</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18338,16 +18338,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -18378,10 +18378,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471336</v>
+        <v>471371</v>
       </c>
       <c r="R150" t="n">
-        <v>6609447</v>
+        <v>6609452</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18446,10 +18446,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125638527</v>
+        <v>125638785</v>
       </c>
       <c r="B151" t="n">
-        <v>100423</v>
+        <v>102840</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18457,16 +18457,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>222771</v>
+        <v>222002</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -18497,10 +18497,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471371</v>
+        <v>471336</v>
       </c>
       <c r="R151" t="n">
-        <v>6609452</v>
+        <v>6609447</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18565,10 +18565,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125638600</v>
+        <v>125638867</v>
       </c>
       <c r="B152" t="n">
-        <v>100423</v>
+        <v>100520</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18576,33 +18576,25 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18616,10 +18608,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>471393</v>
+        <v>471319</v>
       </c>
       <c r="R152" t="n">
-        <v>6609458</v>
+        <v>6609451</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18649,19 +18641,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18694,10 +18676,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125638867</v>
+        <v>125638600</v>
       </c>
       <c r="B153" t="n">
-        <v>100516</v>
+        <v>100427</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18705,25 +18687,33 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18737,10 +18727,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471319</v>
+        <v>471393</v>
       </c>
       <c r="R153" t="n">
-        <v>6609451</v>
+        <v>6609458</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18770,9 +18760,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18808,7 +18808,7 @@
         <v>125639147</v>
       </c>
       <c r="B154" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>125647784</v>
       </c>
       <c r="B155" t="n">
-        <v>96907</v>
+        <v>96911</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19026,10 +19026,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125638320</v>
+        <v>125638438</v>
       </c>
       <c r="B156" t="n">
-        <v>101420</v>
+        <v>98361</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19037,26 +19037,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221235</v>
+        <v>219847</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -19077,10 +19077,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471329</v>
+        <v>471350</v>
       </c>
       <c r="R156" t="n">
-        <v>6609462</v>
+        <v>6609454</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19121,12 +19121,13 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -19144,10 +19145,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125638438</v>
+        <v>125638320</v>
       </c>
       <c r="B157" t="n">
-        <v>98357</v>
+        <v>101424</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19155,26 +19156,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -19184,7 +19185,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -19195,10 +19196,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471350</v>
+        <v>471329</v>
       </c>
       <c r="R157" t="n">
-        <v>6609454</v>
+        <v>6609462</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19239,13 +19240,12 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -19266,7 +19266,7 @@
         <v>125638823</v>
       </c>
       <c r="B158" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>125638903</v>
       </c>
       <c r="B159" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>125638625</v>
       </c>
       <c r="B160" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>125638720</v>
       </c>
       <c r="B161" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19751,10 +19751,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125638831</v>
+        <v>125639134</v>
       </c>
       <c r="B162" t="n">
-        <v>98357</v>
+        <v>100520</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19762,33 +19762,25 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19802,10 +19794,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471334</v>
+        <v>471271</v>
       </c>
       <c r="R162" t="n">
-        <v>6609447</v>
+        <v>6609429</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19849,11 +19841,6 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -19870,10 +19857,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125639134</v>
+        <v>125638831</v>
       </c>
       <c r="B163" t="n">
-        <v>100516</v>
+        <v>98361</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19881,25 +19868,33 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -19913,10 +19908,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471271</v>
+        <v>471334</v>
       </c>
       <c r="R163" t="n">
-        <v>6609429</v>
+        <v>6609447</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19960,6 +19955,11 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalgång</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19979,7 +19979,7 @@
         <v>125638908</v>
       </c>
       <c r="B164" t="n">
-        <v>102836</v>
+        <v>102840</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20087,10 +20087,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125639036</v>
+        <v>125638375</v>
       </c>
       <c r="B165" t="n">
-        <v>95579</v>
+        <v>95571</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20098,21 +20098,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20126,10 +20126,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471281</v>
+        <v>471329</v>
       </c>
       <c r="R165" t="n">
-        <v>6609438</v>
+        <v>6609462</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20170,13 +20170,12 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>kalkblandskog: gran och gråal</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20194,10 +20193,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125638375</v>
+        <v>125639036</v>
       </c>
       <c r="B166" t="n">
-        <v>95567</v>
+        <v>95583</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20205,21 +20204,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20233,10 +20232,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471329</v>
+        <v>471281</v>
       </c>
       <c r="R166" t="n">
-        <v>6609462</v>
+        <v>6609438</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20277,12 +20276,13 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkblandskog: gran och gråal</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -20300,61 +20300,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125638771</v>
+        <v>125647825</v>
       </c>
       <c r="B167" t="n">
-        <v>101420</v>
+        <v>96591</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Tebroängen, Västgötetorp, Vstm</t>
+          <t>Tebroängen, Vstm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471336</v>
+        <v>471311</v>
       </c>
       <c r="R167" t="n">
-        <v>6609447</v>
+        <v>6609467</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20381,12 +20369,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20399,30 +20387,30 @@
       <c r="AG167" t="b">
         <v>0</v>
       </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>kalkgranskog, dalgång</t>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125638348</v>
+        <v>125638771</v>
       </c>
       <c r="B168" t="n">
-        <v>98357</v>
+        <v>101424</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20430,26 +20418,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>219847</v>
+        <v>221235</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -20459,7 +20447,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -20470,10 +20458,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471329</v>
+        <v>471336</v>
       </c>
       <c r="R168" t="n">
-        <v>6609462</v>
+        <v>6609447</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20514,12 +20502,13 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalgång</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
@@ -20537,49 +20526,61 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125647825</v>
+        <v>125638348</v>
       </c>
       <c r="B169" t="n">
-        <v>96587</v>
+        <v>98361</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>53</v>
+        <v>219847</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Tebroängen, Vstm</t>
+          <t>Tebroängen, Västgötetorp, Vstm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471311</v>
+        <v>471329</v>
       </c>
       <c r="R169" t="n">
-        <v>6609467</v>
+        <v>6609462</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20606,12 +20607,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20620,34 +20621,33 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125638463</v>
+        <v>125638361</v>
       </c>
       <c r="B170" t="n">
-        <v>101420</v>
+        <v>102840</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20655,21 +20655,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -20682,7 +20682,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
@@ -20691,10 +20695,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471350</v>
+        <v>471329</v>
       </c>
       <c r="R170" t="n">
-        <v>6609454</v>
+        <v>6609462</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20735,13 +20739,12 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten</t>
+          <t>kalkgranskog, dalbotten med surdråg</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -20759,10 +20762,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125638511</v>
+        <v>125638917</v>
       </c>
       <c r="B171" t="n">
-        <v>95567</v>
+        <v>103769</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20770,26 +20773,38 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2809</v>
+        <v>222412</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -20798,10 +20813,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471371</v>
+        <v>471306</v>
       </c>
       <c r="R171" t="n">
-        <v>6609452</v>
+        <v>6609456</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20848,17 +20863,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalgång</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -20876,10 +20881,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125638361</v>
+        <v>125638463</v>
       </c>
       <c r="B172" t="n">
-        <v>102836</v>
+        <v>101424</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20887,21 +20892,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222002</v>
+        <v>221235</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -20914,11 +20919,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
@@ -20927,10 +20928,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471329</v>
+        <v>471350</v>
       </c>
       <c r="R172" t="n">
-        <v>6609462</v>
+        <v>6609454</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20971,12 +20972,13 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>kalkgranskog, dalbotten med surdråg</t>
+          <t>kalkgranskog, dalbotten</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -20994,10 +20996,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125638917</v>
+        <v>125638511</v>
       </c>
       <c r="B173" t="n">
-        <v>103765</v>
+        <v>95571</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21005,38 +21007,26 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>222412</v>
+        <v>2809</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -21045,10 +21035,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471306</v>
+        <v>471371</v>
       </c>
       <c r="R173" t="n">
-        <v>6609456</v>
+        <v>6609452</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -21095,7 +21085,17 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>kalkgranskog, dalgång</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -21242,10 +21242,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125691817</v>
+        <v>125691568</v>
       </c>
       <c r="B175" t="n">
-        <v>101420</v>
+        <v>100520</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21253,26 +21253,26 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21293,10 +21293,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471334</v>
+        <v>471299</v>
       </c>
       <c r="R175" t="n">
-        <v>6609428</v>
+        <v>6609407</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21356,10 +21356,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125691568</v>
+        <v>125692508</v>
       </c>
       <c r="B176" t="n">
-        <v>100516</v>
+        <v>100427</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21367,21 +21367,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -2140